--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -7250,6 +7250,11 @@
       <c r="J168" t="n">
         <v>9</v>
       </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>tuna,taunt,attune,attuned,unbatted,debutante</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -927,7 +927,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>an,ann,anon,anion,nation</t>
+          <t>an,nan,anon,anion,nation</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>is,sip,pies,poise,poised,depoist,despotic</t>
+          <t>is,sip,pies,poise,poised,deposit,despotic</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>me</t>
+          <t>mi</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>me,erm,mire,prime,empire,premier</t>
+          <t>mi,rim,mire,prime,empire,premier</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>tuna,taunt,attune,attuned,unbatted,debutante</t>
+          <t>tuna,taunt,attune,attuned,debutant,debutante</t>
         </is>
       </c>
     </row>

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -5431,11 +5431,11 @@
         <v>2.054</v>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>novice</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6644,7 +6644,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>trounce</t>
+          <t>cornet</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6675,14 +6675,14 @@
         <v>168</v>
       </c>
       <c r="I154" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J154" t="n">
         <v>11</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>trounce,counters,countries,discounter,countryside</t>
+          <t>cornet,trounce,counters,countries,discounter,countryside</t>
         </is>
       </c>
     </row>

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K284"/>
+  <dimension ref="A1:L284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,6 +475,11 @@
           <t>Solution</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Computed_Level (auto)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -515,6 +520,10 @@
       <c r="J2" t="n">
         <v>7</v>
       </c>
+      <c r="L2">
+        <f>IF(C2="","Excluded (no APD)",IF(C2&lt;1.25,"Easy",IF(C2&lt;=2.8,"Medium",IF(C2&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -555,6 +564,10 @@
       <c r="J3" t="n">
         <v>6</v>
       </c>
+      <c r="L3">
+        <f>IF(C3="","Excluded (no APD)",IF(C3&lt;1.25,"Easy",IF(C3&lt;=2.8,"Medium",IF(C3&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -595,6 +608,10 @@
       <c r="J4" t="n">
         <v>7</v>
       </c>
+      <c r="L4">
+        <f>IF(C4="","Excluded (no APD)",IF(C4&lt;1.25,"Easy",IF(C4&lt;=2.8,"Medium",IF(C4&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -640,6 +657,10 @@
           <t>by,boy,bony,ebony,bygone</t>
         </is>
       </c>
+      <c r="L5">
+        <f>IF(C5="","Excluded (no APD)",IF(C5&lt;1.25,"Easy",IF(C5&lt;=2.8,"Medium",IF(C5&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -680,11 +701,15 @@
       <c r="J6" t="n">
         <v>9</v>
       </c>
+      <c r="L6">
+        <f>IF(C6="","Excluded (no APD)",IF(C6&lt;1.25,"Easy",IF(C6&lt;=2.8,"Medium",IF(C6&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>teal</t>
+          <t>et</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -693,7 +718,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -715,11 +740,20 @@
         <v>17</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>8</v>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>et,net,nest,tines,instep,panties,plainest</t>
+        </is>
+      </c>
+      <c r="L7">
+        <f>IF(C7="","Excluded (no APD)",IF(C7&lt;1.25,"Easy",IF(C7&lt;=2.8,"Medium",IF(C7&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -760,6 +794,10 @@
       <c r="J8" t="n">
         <v>9</v>
       </c>
+      <c r="L8">
+        <f>IF(C8="","Excluded (no APD)",IF(C8&lt;1.25,"Easy",IF(C8&lt;=2.8,"Medium",IF(C8&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -800,6 +838,10 @@
       <c r="J9" t="n">
         <v>8</v>
       </c>
+      <c r="L9">
+        <f>IF(C9="","Excluded (no APD)",IF(C9&lt;1.25,"Easy",IF(C9&lt;=2.8,"Medium",IF(C9&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -845,6 +887,10 @@
           <t>pi,pie,pier,price,recipe,pierced,decipher</t>
         </is>
       </c>
+      <c r="L10">
+        <f>IF(C10="","Excluded (no APD)",IF(C10&lt;1.25,"Easy",IF(C10&lt;=2.8,"Medium",IF(C10&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -885,6 +931,10 @@
       <c r="J11" t="n">
         <v>6</v>
       </c>
+      <c r="L11">
+        <f>IF(C11="","Excluded (no APD)",IF(C11&lt;1.25,"Easy",IF(C11&lt;=2.8,"Medium",IF(C11&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -930,6 +980,10 @@
           <t>an,nan,anon,anion,nation</t>
         </is>
       </c>
+      <c r="L12">
+        <f>IF(C12="","Excluded (no APD)",IF(C12&lt;1.25,"Easy",IF(C12&lt;=2.8,"Medium",IF(C12&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -975,6 +1029,10 @@
           <t>is,sip,pies,poise,poised,deposit,despotic</t>
         </is>
       </c>
+      <c r="L13">
+        <f>IF(C13="","Excluded (no APD)",IF(C13&lt;1.25,"Easy",IF(C13&lt;=2.8,"Medium",IF(C13&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1020,6 +1078,10 @@
           <t>go,ego,gore,rogue,grouse,gougers,gorgeous</t>
         </is>
       </c>
+      <c r="L14">
+        <f>IF(C14="","Excluded (no APD)",IF(C14&lt;1.25,"Easy",IF(C14&lt;=2.8,"Medium",IF(C14&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1060,6 +1122,10 @@
       <c r="J15" t="n">
         <v>9</v>
       </c>
+      <c r="L15">
+        <f>IF(C15="","Excluded (no APD)",IF(C15&lt;1.25,"Easy",IF(C15&lt;=2.8,"Medium",IF(C15&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1100,11 +1166,15 @@
       <c r="J16" t="n">
         <v>9</v>
       </c>
+      <c r="L16">
+        <f>IF(C16="","Excluded (no APD)",IF(C16&lt;1.25,"Easy",IF(C16&lt;=2.8,"Medium",IF(C16&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>an</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1140,6 +1210,15 @@
       <c r="J17" t="n">
         <v>8</v>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>an,ran,rang,anger,manger,manager,bargeman</t>
+        </is>
+      </c>
+      <c r="L17">
+        <f>IF(C17="","Excluded (no APD)",IF(C17&lt;1.25,"Easy",IF(C17&lt;=2.8,"Medium",IF(C17&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1180,6 +1259,10 @@
       <c r="J18" t="n">
         <v>9</v>
       </c>
+      <c r="L18">
+        <f>IF(C18="","Excluded (no APD)",IF(C18&lt;1.25,"Easy",IF(C18&lt;=2.8,"Medium",IF(C18&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1220,6 +1303,10 @@
       <c r="J19" t="n">
         <v>8</v>
       </c>
+      <c r="L19">
+        <f>IF(C19="","Excluded (no APD)",IF(C19&lt;1.25,"Easy",IF(C19&lt;=2.8,"Medium",IF(C19&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1260,6 +1347,10 @@
       <c r="J20" t="n">
         <v>11</v>
       </c>
+      <c r="L20">
+        <f>IF(C20="","Excluded (no APD)",IF(C20&lt;1.25,"Easy",IF(C20&lt;=2.8,"Medium",IF(C20&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1300,6 +1391,10 @@
       <c r="J21" t="n">
         <v>9</v>
       </c>
+      <c r="L21">
+        <f>IF(C21="","Excluded (no APD)",IF(C21&lt;1.25,"Easy",IF(C21&lt;=2.8,"Medium",IF(C21&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1340,6 +1435,10 @@
       <c r="J22" t="n">
         <v>8</v>
       </c>
+      <c r="L22">
+        <f>IF(C22="","Excluded (no APD)",IF(C22&lt;1.25,"Easy",IF(C22&lt;=2.8,"Medium",IF(C22&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1380,6 +1479,10 @@
       <c r="J23" t="n">
         <v>11</v>
       </c>
+      <c r="L23">
+        <f>IF(C23="","Excluded (no APD)",IF(C23&lt;1.25,"Easy",IF(C23&lt;=2.8,"Medium",IF(C23&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1420,6 +1523,10 @@
       <c r="J24" t="n">
         <v>8</v>
       </c>
+      <c r="L24">
+        <f>IF(C24="","Excluded (no APD)",IF(C24&lt;1.25,"Easy",IF(C24&lt;=2.8,"Medium",IF(C24&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1460,6 +1567,10 @@
       <c r="J25" t="n">
         <v>10</v>
       </c>
+      <c r="L25">
+        <f>IF(C25="","Excluded (no APD)",IF(C25&lt;1.25,"Easy",IF(C25&lt;=2.8,"Medium",IF(C25&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1500,6 +1611,10 @@
       <c r="J26" t="n">
         <v>8</v>
       </c>
+      <c r="L26">
+        <f>IF(C26="","Excluded (no APD)",IF(C26&lt;1.25,"Easy",IF(C26&lt;=2.8,"Medium",IF(C26&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1540,6 +1655,10 @@
       <c r="J27" t="n">
         <v>10</v>
       </c>
+      <c r="L27">
+        <f>IF(C27="","Excluded (no APD)",IF(C27&lt;1.25,"Easy",IF(C27&lt;=2.8,"Medium",IF(C27&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1580,6 +1699,10 @@
       <c r="J28" t="n">
         <v>11</v>
       </c>
+      <c r="L28">
+        <f>IF(C28="","Excluded (no APD)",IF(C28&lt;1.25,"Easy",IF(C28&lt;=2.8,"Medium",IF(C28&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1620,6 +1743,10 @@
       <c r="J29" t="n">
         <v>8</v>
       </c>
+      <c r="L29">
+        <f>IF(C29="","Excluded (no APD)",IF(C29&lt;1.25,"Easy",IF(C29&lt;=2.8,"Medium",IF(C29&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1660,6 +1787,10 @@
       <c r="J30" t="n">
         <v>9</v>
       </c>
+      <c r="L30">
+        <f>IF(C30="","Excluded (no APD)",IF(C30&lt;1.25,"Easy",IF(C30&lt;=2.8,"Medium",IF(C30&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1700,6 +1831,10 @@
       <c r="J31" t="n">
         <v>10</v>
       </c>
+      <c r="L31">
+        <f>IF(C31="","Excluded (no APD)",IF(C31&lt;1.25,"Easy",IF(C31&lt;=2.8,"Medium",IF(C31&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1740,6 +1875,10 @@
       <c r="J32" t="n">
         <v>12</v>
       </c>
+      <c r="L32">
+        <f>IF(C32="","Excluded (no APD)",IF(C32&lt;1.25,"Easy",IF(C32&lt;=2.8,"Medium",IF(C32&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1780,6 +1919,10 @@
       <c r="J33" t="n">
         <v>9</v>
       </c>
+      <c r="L33">
+        <f>IF(C33="","Excluded (no APD)",IF(C33&lt;1.25,"Easy",IF(C33&lt;=2.8,"Medium",IF(C33&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1820,6 +1963,10 @@
       <c r="J34" t="n">
         <v>7</v>
       </c>
+      <c r="L34">
+        <f>IF(C34="","Excluded (no APD)",IF(C34&lt;1.25,"Easy",IF(C34&lt;=2.8,"Medium",IF(C34&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1860,6 +2007,10 @@
       <c r="J35" t="n">
         <v>11</v>
       </c>
+      <c r="L35">
+        <f>IF(C35="","Excluded (no APD)",IF(C35&lt;1.25,"Easy",IF(C35&lt;=2.8,"Medium",IF(C35&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1900,6 +2051,10 @@
       <c r="J36" t="n">
         <v>9</v>
       </c>
+      <c r="L36">
+        <f>IF(C36="","Excluded (no APD)",IF(C36&lt;1.25,"Easy",IF(C36&lt;=2.8,"Medium",IF(C36&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1940,6 +2095,10 @@
       <c r="J37" t="n">
         <v>8</v>
       </c>
+      <c r="L37">
+        <f>IF(C37="","Excluded (no APD)",IF(C37&lt;1.25,"Easy",IF(C37&lt;=2.8,"Medium",IF(C37&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1980,6 +2139,10 @@
       <c r="J38" t="n">
         <v>9</v>
       </c>
+      <c r="L38">
+        <f>IF(C38="","Excluded (no APD)",IF(C38&lt;1.25,"Easy",IF(C38&lt;=2.8,"Medium",IF(C38&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2020,6 +2183,10 @@
       <c r="J39" t="n">
         <v>8</v>
       </c>
+      <c r="L39">
+        <f>IF(C39="","Excluded (no APD)",IF(C39&lt;1.25,"Easy",IF(C39&lt;=2.8,"Medium",IF(C39&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2060,6 +2227,10 @@
       <c r="J40" t="n">
         <v>7</v>
       </c>
+      <c r="L40">
+        <f>IF(C40="","Excluded (no APD)",IF(C40&lt;1.25,"Easy",IF(C40&lt;=2.8,"Medium",IF(C40&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2100,6 +2271,10 @@
       <c r="J41" t="n">
         <v>7</v>
       </c>
+      <c r="L41">
+        <f>IF(C41="","Excluded (no APD)",IF(C41&lt;1.25,"Easy",IF(C41&lt;=2.8,"Medium",IF(C41&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2140,6 +2315,10 @@
       <c r="J42" t="n">
         <v>6</v>
       </c>
+      <c r="L42">
+        <f>IF(C42="","Excluded (no APD)",IF(C42&lt;1.25,"Easy",IF(C42&lt;=2.8,"Medium",IF(C42&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2180,6 +2359,10 @@
       <c r="J43" t="n">
         <v>9</v>
       </c>
+      <c r="L43">
+        <f>IF(C43="","Excluded (no APD)",IF(C43&lt;1.25,"Easy",IF(C43&lt;=2.8,"Medium",IF(C43&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2220,6 +2403,10 @@
       <c r="J44" t="n">
         <v>7</v>
       </c>
+      <c r="L44">
+        <f>IF(C44="","Excluded (no APD)",IF(C44&lt;1.25,"Easy",IF(C44&lt;=2.8,"Medium",IF(C44&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2260,6 +2447,10 @@
       <c r="J45" t="n">
         <v>6</v>
       </c>
+      <c r="L45">
+        <f>IF(C45="","Excluded (no APD)",IF(C45&lt;1.25,"Easy",IF(C45&lt;=2.8,"Medium",IF(C45&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2300,6 +2491,10 @@
       <c r="J46" t="n">
         <v>11</v>
       </c>
+      <c r="L46">
+        <f>IF(C46="","Excluded (no APD)",IF(C46&lt;1.25,"Easy",IF(C46&lt;=2.8,"Medium",IF(C46&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2340,6 +2535,10 @@
       <c r="J47" t="n">
         <v>7</v>
       </c>
+      <c r="L47">
+        <f>IF(C47="","Excluded (no APD)",IF(C47&lt;1.25,"Easy",IF(C47&lt;=2.8,"Medium",IF(C47&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2380,6 +2579,10 @@
       <c r="J48" t="n">
         <v>7</v>
       </c>
+      <c r="L48">
+        <f>IF(C48="","Excluded (no APD)",IF(C48&lt;1.25,"Easy",IF(C48&lt;=2.8,"Medium",IF(C48&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2420,6 +2623,10 @@
       <c r="J49" t="n">
         <v>9</v>
       </c>
+      <c r="L49">
+        <f>IF(C49="","Excluded (no APD)",IF(C49&lt;1.25,"Easy",IF(C49&lt;=2.8,"Medium",IF(C49&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2460,6 +2667,10 @@
       <c r="J50" t="n">
         <v>7</v>
       </c>
+      <c r="L50">
+        <f>IF(C50="","Excluded (no APD)",IF(C50&lt;1.25,"Easy",IF(C50&lt;=2.8,"Medium",IF(C50&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2500,6 +2711,10 @@
       <c r="J51" t="n">
         <v>7</v>
       </c>
+      <c r="L51">
+        <f>IF(C51="","Excluded (no APD)",IF(C51&lt;1.25,"Easy",IF(C51&lt;=2.8,"Medium",IF(C51&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2545,6 +2760,10 @@
           <t>in,tin,tins,stein,tennis,intents,sentient</t>
         </is>
       </c>
+      <c r="L52">
+        <f>IF(C52="","Excluded (no APD)",IF(C52&lt;1.25,"Easy",IF(C52&lt;=2.8,"Medium",IF(C52&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2590,6 +2809,10 @@
           <t>an,can,cane,crane,dancer,dancers</t>
         </is>
       </c>
+      <c r="L53">
+        <f>IF(C53="","Excluded (no APD)",IF(C53&lt;1.25,"Easy",IF(C53&lt;=2.8,"Medium",IF(C53&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2630,6 +2853,10 @@
       <c r="J54" t="n">
         <v>7</v>
       </c>
+      <c r="L54">
+        <f>IF(C54="","Excluded (no APD)",IF(C54&lt;1.25,"Easy",IF(C54&lt;=2.8,"Medium",IF(C54&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2670,6 +2897,10 @@
       <c r="J55" t="n">
         <v>9</v>
       </c>
+      <c r="L55">
+        <f>IF(C55="","Excluded (no APD)",IF(C55&lt;1.25,"Easy",IF(C55&lt;=2.8,"Medium",IF(C55&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2710,6 +2941,10 @@
       <c r="J56" t="n">
         <v>9</v>
       </c>
+      <c r="L56">
+        <f>IF(C56="","Excluded (no APD)",IF(C56&lt;1.25,"Easy",IF(C56&lt;=2.8,"Medium",IF(C56&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2750,6 +2985,10 @@
       <c r="J57" t="n">
         <v>9</v>
       </c>
+      <c r="L57">
+        <f>IF(C57="","Excluded (no APD)",IF(C57&lt;1.25,"Easy",IF(C57&lt;=2.8,"Medium",IF(C57&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2790,6 +3029,10 @@
       <c r="J58" t="n">
         <v>8</v>
       </c>
+      <c r="L58">
+        <f>IF(C58="","Excluded (no APD)",IF(C58&lt;1.25,"Easy",IF(C58&lt;=2.8,"Medium",IF(C58&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2830,6 +3073,10 @@
       <c r="J59" t="n">
         <v>6</v>
       </c>
+      <c r="L59">
+        <f>IF(C59="","Excluded (no APD)",IF(C59&lt;1.25,"Easy",IF(C59&lt;=2.8,"Medium",IF(C59&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2870,6 +3117,10 @@
       <c r="J60" t="n">
         <v>8</v>
       </c>
+      <c r="L60">
+        <f>IF(C60="","Excluded (no APD)",IF(C60&lt;1.25,"Easy",IF(C60&lt;=2.8,"Medium",IF(C60&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2910,6 +3161,10 @@
       <c r="J61" t="n">
         <v>7</v>
       </c>
+      <c r="L61">
+        <f>IF(C61="","Excluded (no APD)",IF(C61&lt;1.25,"Easy",IF(C61&lt;=2.8,"Medium",IF(C61&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2950,6 +3205,10 @@
       <c r="J62" t="n">
         <v>8</v>
       </c>
+      <c r="L62">
+        <f>IF(C62="","Excluded (no APD)",IF(C62&lt;1.25,"Easy",IF(C62&lt;=2.8,"Medium",IF(C62&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2995,6 +3254,10 @@
           <t>ace,care,crate,traced,reacted,decorate,relocated,correlated</t>
         </is>
       </c>
+      <c r="L63">
+        <f>IF(C63="","Excluded (no APD)",IF(C63&lt;1.25,"Easy",IF(C63&lt;=2.8,"Medium",IF(C63&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3035,6 +3298,10 @@
       <c r="J64" t="n">
         <v>7</v>
       </c>
+      <c r="L64">
+        <f>IF(C64="","Excluded (no APD)",IF(C64&lt;1.25,"Easy",IF(C64&lt;=2.8,"Medium",IF(C64&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3075,6 +3342,10 @@
       <c r="J65" t="n">
         <v>9</v>
       </c>
+      <c r="L65">
+        <f>IF(C65="","Excluded (no APD)",IF(C65&lt;1.25,"Easy",IF(C65&lt;=2.8,"Medium",IF(C65&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3115,6 +3386,10 @@
       <c r="J66" t="n">
         <v>9</v>
       </c>
+      <c r="L66">
+        <f>IF(C66="","Excluded (no APD)",IF(C66&lt;1.25,"Easy",IF(C66&lt;=2.8,"Medium",IF(C66&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3155,6 +3430,10 @@
       <c r="J67" t="n">
         <v>7</v>
       </c>
+      <c r="L67">
+        <f>IF(C67="","Excluded (no APD)",IF(C67&lt;1.25,"Easy",IF(C67&lt;=2.8,"Medium",IF(C67&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3195,6 +3474,10 @@
       <c r="J68" t="n">
         <v>8</v>
       </c>
+      <c r="L68">
+        <f>IF(C68="","Excluded (no APD)",IF(C68&lt;1.25,"Easy",IF(C68&lt;=2.8,"Medium",IF(C68&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3235,6 +3518,10 @@
       <c r="J69" t="n">
         <v>8</v>
       </c>
+      <c r="L69">
+        <f>IF(C69="","Excluded (no APD)",IF(C69&lt;1.25,"Easy",IF(C69&lt;=2.8,"Medium",IF(C69&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3280,6 +3567,10 @@
           <t>mi,rim,mire,prime,empire,premier</t>
         </is>
       </c>
+      <c r="L70">
+        <f>IF(C70="","Excluded (no APD)",IF(C70&lt;1.25,"Easy",IF(C70&lt;=2.8,"Medium",IF(C70&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3320,6 +3611,10 @@
       <c r="J71" t="n">
         <v>8</v>
       </c>
+      <c r="L71">
+        <f>IF(C71="","Excluded (no APD)",IF(C71&lt;1.25,"Easy",IF(C71&lt;=2.8,"Medium",IF(C71&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3360,6 +3655,10 @@
       <c r="J72" t="n">
         <v>9</v>
       </c>
+      <c r="L72">
+        <f>IF(C72="","Excluded (no APD)",IF(C72&lt;1.25,"Easy",IF(C72&lt;=2.8,"Medium",IF(C72&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3400,6 +3699,10 @@
       <c r="J73" t="n">
         <v>7</v>
       </c>
+      <c r="L73">
+        <f>IF(C73="","Excluded (no APD)",IF(C73&lt;1.25,"Easy",IF(C73&lt;=2.8,"Medium",IF(C73&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3440,6 +3743,10 @@
       <c r="J74" t="n">
         <v>6</v>
       </c>
+      <c r="L74">
+        <f>IF(C74="","Excluded (no APD)",IF(C74&lt;1.25,"Easy",IF(C74&lt;=2.8,"Medium",IF(C74&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3480,6 +3787,10 @@
       <c r="J75" t="n">
         <v>7</v>
       </c>
+      <c r="L75">
+        <f>IF(C75="","Excluded (no APD)",IF(C75&lt;1.25,"Easy",IF(C75&lt;=2.8,"Medium",IF(C75&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3520,6 +3831,10 @@
       <c r="J76" t="n">
         <v>10</v>
       </c>
+      <c r="L76">
+        <f>IF(C76="","Excluded (no APD)",IF(C76&lt;1.25,"Easy",IF(C76&lt;=2.8,"Medium",IF(C76&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3560,6 +3875,10 @@
       <c r="J77" t="n">
         <v>8</v>
       </c>
+      <c r="L77">
+        <f>IF(C77="","Excluded (no APD)",IF(C77&lt;1.25,"Easy",IF(C77&lt;=2.8,"Medium",IF(C77&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3600,6 +3919,10 @@
       <c r="J78" t="n">
         <v>7</v>
       </c>
+      <c r="L78">
+        <f>IF(C78="","Excluded (no APD)",IF(C78&lt;1.25,"Easy",IF(C78&lt;=2.8,"Medium",IF(C78&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3640,6 +3963,10 @@
       <c r="J79" t="n">
         <v>6</v>
       </c>
+      <c r="L79">
+        <f>IF(C79="","Excluded (no APD)",IF(C79&lt;1.25,"Easy",IF(C79&lt;=2.8,"Medium",IF(C79&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3680,6 +4007,10 @@
       <c r="J80" t="n">
         <v>8</v>
       </c>
+      <c r="L80">
+        <f>IF(C80="","Excluded (no APD)",IF(C80&lt;1.25,"Easy",IF(C80&lt;=2.8,"Medium",IF(C80&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3720,6 +4051,10 @@
       <c r="J81" t="n">
         <v>8</v>
       </c>
+      <c r="L81">
+        <f>IF(C81="","Excluded (no APD)",IF(C81&lt;1.25,"Easy",IF(C81&lt;=2.8,"Medium",IF(C81&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3760,6 +4095,10 @@
       <c r="J82" t="n">
         <v>8</v>
       </c>
+      <c r="L82">
+        <f>IF(C82="","Excluded (no APD)",IF(C82&lt;1.25,"Easy",IF(C82&lt;=2.8,"Medium",IF(C82&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3800,6 +4139,10 @@
       <c r="J83" t="n">
         <v>7</v>
       </c>
+      <c r="L83">
+        <f>IF(C83="","Excluded (no APD)",IF(C83&lt;1.25,"Easy",IF(C83&lt;=2.8,"Medium",IF(C83&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3840,6 +4183,10 @@
       <c r="J84" t="n">
         <v>7</v>
       </c>
+      <c r="L84">
+        <f>IF(C84="","Excluded (no APD)",IF(C84&lt;1.25,"Easy",IF(C84&lt;=2.8,"Medium",IF(C84&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3880,6 +4227,10 @@
       <c r="J85" t="n">
         <v>8</v>
       </c>
+      <c r="L85">
+        <f>IF(C85="","Excluded (no APD)",IF(C85&lt;1.25,"Easy",IF(C85&lt;=2.8,"Medium",IF(C85&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3920,6 +4271,10 @@
       <c r="J86" t="n">
         <v>8</v>
       </c>
+      <c r="L86">
+        <f>IF(C86="","Excluded (no APD)",IF(C86&lt;1.25,"Easy",IF(C86&lt;=2.8,"Medium",IF(C86&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3960,6 +4315,10 @@
       <c r="J87" t="n">
         <v>8</v>
       </c>
+      <c r="L87">
+        <f>IF(C87="","Excluded (no APD)",IF(C87&lt;1.25,"Easy",IF(C87&lt;=2.8,"Medium",IF(C87&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4000,6 +4359,10 @@
       <c r="J88" t="n">
         <v>8</v>
       </c>
+      <c r="L88">
+        <f>IF(C88="","Excluded (no APD)",IF(C88&lt;1.25,"Easy",IF(C88&lt;=2.8,"Medium",IF(C88&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4040,6 +4403,10 @@
       <c r="J89" t="n">
         <v>8</v>
       </c>
+      <c r="L89">
+        <f>IF(C89="","Excluded (no APD)",IF(C89&lt;1.25,"Easy",IF(C89&lt;=2.8,"Medium",IF(C89&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4080,6 +4447,10 @@
       <c r="J90" t="n">
         <v>7</v>
       </c>
+      <c r="L90">
+        <f>IF(C90="","Excluded (no APD)",IF(C90&lt;1.25,"Easy",IF(C90&lt;=2.8,"Medium",IF(C90&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4120,6 +4491,10 @@
       <c r="J91" t="n">
         <v>9</v>
       </c>
+      <c r="L91">
+        <f>IF(C91="","Excluded (no APD)",IF(C91&lt;1.25,"Easy",IF(C91&lt;=2.8,"Medium",IF(C91&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4160,6 +4535,10 @@
       <c r="J92" t="n">
         <v>7</v>
       </c>
+      <c r="L92">
+        <f>IF(C92="","Excluded (no APD)",IF(C92&lt;1.25,"Easy",IF(C92&lt;=2.8,"Medium",IF(C92&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4200,6 +4579,10 @@
       <c r="J93" t="n">
         <v>8</v>
       </c>
+      <c r="L93">
+        <f>IF(C93="","Excluded (no APD)",IF(C93&lt;1.25,"Easy",IF(C93&lt;=2.8,"Medium",IF(C93&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4240,6 +4623,10 @@
       <c r="J94" t="n">
         <v>7</v>
       </c>
+      <c r="L94">
+        <f>IF(C94="","Excluded (no APD)",IF(C94&lt;1.25,"Easy",IF(C94&lt;=2.8,"Medium",IF(C94&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4280,6 +4667,10 @@
       <c r="J95" t="n">
         <v>6</v>
       </c>
+      <c r="L95">
+        <f>IF(C95="","Excluded (no APD)",IF(C95&lt;1.25,"Easy",IF(C95&lt;=2.8,"Medium",IF(C95&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4320,6 +4711,10 @@
       <c r="J96" t="n">
         <v>10</v>
       </c>
+      <c r="L96">
+        <f>IF(C96="","Excluded (no APD)",IF(C96&lt;1.25,"Easy",IF(C96&lt;=2.8,"Medium",IF(C96&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4360,6 +4755,10 @@
       <c r="J97" t="n">
         <v>9</v>
       </c>
+      <c r="L97">
+        <f>IF(C97="","Excluded (no APD)",IF(C97&lt;1.25,"Easy",IF(C97&lt;=2.8,"Medium",IF(C97&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4400,6 +4799,10 @@
       <c r="J98" t="n">
         <v>9</v>
       </c>
+      <c r="L98">
+        <f>IF(C98="","Excluded (no APD)",IF(C98&lt;1.25,"Easy",IF(C98&lt;=2.8,"Medium",IF(C98&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4440,6 +4843,10 @@
       <c r="J99" t="n">
         <v>9</v>
       </c>
+      <c r="L99">
+        <f>IF(C99="","Excluded (no APD)",IF(C99&lt;1.25,"Easy",IF(C99&lt;=2.8,"Medium",IF(C99&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4480,6 +4887,10 @@
       <c r="J100" t="n">
         <v>7</v>
       </c>
+      <c r="L100">
+        <f>IF(C100="","Excluded (no APD)",IF(C100&lt;1.25,"Easy",IF(C100&lt;=2.8,"Medium",IF(C100&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4520,6 +4931,10 @@
       <c r="J101" t="n">
         <v>8</v>
       </c>
+      <c r="L101">
+        <f>IF(C101="","Excluded (no APD)",IF(C101&lt;1.25,"Easy",IF(C101&lt;=2.8,"Medium",IF(C101&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4560,6 +4975,10 @@
       <c r="J102" t="n">
         <v>8</v>
       </c>
+      <c r="L102">
+        <f>IF(C102="","Excluded (no APD)",IF(C102&lt;1.25,"Easy",IF(C102&lt;=2.8,"Medium",IF(C102&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4600,6 +5019,10 @@
       <c r="J103" t="n">
         <v>10</v>
       </c>
+      <c r="L103">
+        <f>IF(C103="","Excluded (no APD)",IF(C103&lt;1.25,"Easy",IF(C103&lt;=2.8,"Medium",IF(C103&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4640,6 +5063,10 @@
       <c r="J104" t="n">
         <v>8</v>
       </c>
+      <c r="L104">
+        <f>IF(C104="","Excluded (no APD)",IF(C104&lt;1.25,"Easy",IF(C104&lt;=2.8,"Medium",IF(C104&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4680,6 +5107,10 @@
       <c r="J105" t="n">
         <v>7</v>
       </c>
+      <c r="L105">
+        <f>IF(C105="","Excluded (no APD)",IF(C105&lt;1.25,"Easy",IF(C105&lt;=2.8,"Medium",IF(C105&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4720,6 +5151,10 @@
       <c r="J106" t="n">
         <v>8</v>
       </c>
+      <c r="L106">
+        <f>IF(C106="","Excluded (no APD)",IF(C106&lt;1.25,"Easy",IF(C106&lt;=2.8,"Medium",IF(C106&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4760,6 +5195,10 @@
       <c r="J107" t="n">
         <v>7</v>
       </c>
+      <c r="L107">
+        <f>IF(C107="","Excluded (no APD)",IF(C107&lt;1.25,"Easy",IF(C107&lt;=2.8,"Medium",IF(C107&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4800,6 +5239,10 @@
       <c r="J108" t="n">
         <v>6</v>
       </c>
+      <c r="L108">
+        <f>IF(C108="","Excluded (no APD)",IF(C108&lt;1.25,"Easy",IF(C108&lt;=2.8,"Medium",IF(C108&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4845,6 +5288,10 @@
           <t>nut,unto,count,toucan,caution</t>
         </is>
       </c>
+      <c r="L109">
+        <f>IF(C109="","Excluded (no APD)",IF(C109&lt;1.25,"Easy",IF(C109&lt;=2.8,"Medium",IF(C109&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4885,6 +5332,10 @@
       <c r="J110" t="n">
         <v>7</v>
       </c>
+      <c r="L110">
+        <f>IF(C110="","Excluded (no APD)",IF(C110&lt;1.25,"Easy",IF(C110&lt;=2.8,"Medium",IF(C110&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4925,6 +5376,10 @@
       <c r="J111" t="n">
         <v>8</v>
       </c>
+      <c r="L111">
+        <f>IF(C111="","Excluded (no APD)",IF(C111&lt;1.25,"Easy",IF(C111&lt;=2.8,"Medium",IF(C111&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4965,6 +5420,10 @@
       <c r="J112" t="n">
         <v>7</v>
       </c>
+      <c r="L112">
+        <f>IF(C112="","Excluded (no APD)",IF(C112&lt;1.25,"Easy",IF(C112&lt;=2.8,"Medium",IF(C112&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5005,6 +5464,10 @@
       <c r="J113" t="n">
         <v>10</v>
       </c>
+      <c r="L113">
+        <f>IF(C113="","Excluded (no APD)",IF(C113&lt;1.25,"Easy",IF(C113&lt;=2.8,"Medium",IF(C113&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5045,6 +5508,10 @@
       <c r="J114" t="n">
         <v>9</v>
       </c>
+      <c r="L114">
+        <f>IF(C114="","Excluded (no APD)",IF(C114&lt;1.25,"Easy",IF(C114&lt;=2.8,"Medium",IF(C114&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5085,6 +5552,10 @@
       <c r="J115" t="n">
         <v>9</v>
       </c>
+      <c r="L115">
+        <f>IF(C115="","Excluded (no APD)",IF(C115&lt;1.25,"Easy",IF(C115&lt;=2.8,"Medium",IF(C115&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5125,6 +5596,10 @@
       <c r="J116" t="n">
         <v>8</v>
       </c>
+      <c r="L116">
+        <f>IF(C116="","Excluded (no APD)",IF(C116&lt;1.25,"Easy",IF(C116&lt;=2.8,"Medium",IF(C116&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5165,6 +5640,10 @@
       <c r="J117" t="n">
         <v>10</v>
       </c>
+      <c r="L117">
+        <f>IF(C117="","Excluded (no APD)",IF(C117&lt;1.25,"Easy",IF(C117&lt;=2.8,"Medium",IF(C117&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5210,6 +5689,10 @@
           <t>deform,freedom,reformed,performed</t>
         </is>
       </c>
+      <c r="L118">
+        <f>IF(C118="","Excluded (no APD)",IF(C118&lt;1.25,"Easy",IF(C118&lt;=2.8,"Medium",IF(C118&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5250,6 +5733,10 @@
       <c r="J119" t="n">
         <v>6</v>
       </c>
+      <c r="L119">
+        <f>IF(C119="","Excluded (no APD)",IF(C119&lt;1.25,"Easy",IF(C119&lt;=2.8,"Medium",IF(C119&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5290,6 +5777,10 @@
       <c r="J120" t="n">
         <v>6</v>
       </c>
+      <c r="L120">
+        <f>IF(C120="","Excluded (no APD)",IF(C120&lt;1.25,"Easy",IF(C120&lt;=2.8,"Medium",IF(C120&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5330,6 +5821,10 @@
       <c r="J121" t="n">
         <v>10</v>
       </c>
+      <c r="L121">
+        <f>IF(C121="","Excluded (no APD)",IF(C121&lt;1.25,"Easy",IF(C121&lt;=2.8,"Medium",IF(C121&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5370,6 +5865,10 @@
       <c r="J122" t="n">
         <v>8</v>
       </c>
+      <c r="L122">
+        <f>IF(C122="","Excluded (no APD)",IF(C122&lt;1.25,"Easy",IF(C122&lt;=2.8,"Medium",IF(C122&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5415,6 +5914,10 @@
           <t>act,cart,cater,canter,central,clarinet</t>
         </is>
       </c>
+      <c r="L123">
+        <f>IF(C123="","Excluded (no APD)",IF(C123&lt;1.25,"Easy",IF(C123&lt;=2.8,"Medium",IF(C123&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5428,14 +5931,14 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2.054</v>
+        <v>3.5</v>
       </c>
       <c r="D124" t="n">
         <v>3</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>hard</t>
+          <t>expert</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5460,6 +5963,10 @@
           <t>ear,tear,irate,retain,tearing,gradient,denigrate,dewatering</t>
         </is>
       </c>
+      <c r="L124">
+        <f>IF(C124="","Excluded (no APD)",IF(C124&lt;1.25,"Easy",IF(C124&lt;=2.8,"Medium",IF(C124&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5476,11 +5983,11 @@
         <v>1.8</v>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>beginner</t>
+          <t>novice</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5500,6 +6007,10 @@
       <c r="J125" t="n">
         <v>8</v>
       </c>
+      <c r="L125">
+        <f>IF(C125="","Excluded (no APD)",IF(C125&lt;1.25,"Easy",IF(C125&lt;=2.8,"Medium",IF(C125&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5540,6 +6051,10 @@
       <c r="J126" t="n">
         <v>10</v>
       </c>
+      <c r="L126">
+        <f>IF(C126="","Excluded (no APD)",IF(C126&lt;1.25,"Easy",IF(C126&lt;=2.8,"Medium",IF(C126&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5580,6 +6095,10 @@
       <c r="J127" t="n">
         <v>9</v>
       </c>
+      <c r="L127">
+        <f>IF(C127="","Excluded (no APD)",IF(C127&lt;1.25,"Easy",IF(C127&lt;=2.8,"Medium",IF(C127&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5620,6 +6139,10 @@
       <c r="J128" t="n">
         <v>10</v>
       </c>
+      <c r="L128">
+        <f>IF(C128="","Excluded (no APD)",IF(C128&lt;1.25,"Easy",IF(C128&lt;=2.8,"Medium",IF(C128&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5660,6 +6183,10 @@
       <c r="J129" t="n">
         <v>11</v>
       </c>
+      <c r="L129">
+        <f>IF(C129="","Excluded (no APD)",IF(C129&lt;1.25,"Easy",IF(C129&lt;=2.8,"Medium",IF(C129&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5700,6 +6227,10 @@
       <c r="J130" t="n">
         <v>8</v>
       </c>
+      <c r="L130">
+        <f>IF(C130="","Excluded (no APD)",IF(C130&lt;1.25,"Easy",IF(C130&lt;=2.8,"Medium",IF(C130&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5740,6 +6271,10 @@
       <c r="J131" t="n">
         <v>8</v>
       </c>
+      <c r="L131">
+        <f>IF(C131="","Excluded (no APD)",IF(C131&lt;1.25,"Easy",IF(C131&lt;=2.8,"Medium",IF(C131&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5780,6 +6315,10 @@
       <c r="J132" t="n">
         <v>8</v>
       </c>
+      <c r="L132">
+        <f>IF(C132="","Excluded (no APD)",IF(C132&lt;1.25,"Easy",IF(C132&lt;=2.8,"Medium",IF(C132&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5820,6 +6359,10 @@
       <c r="J133" t="n">
         <v>7</v>
       </c>
+      <c r="L133">
+        <f>IF(C133="","Excluded (no APD)",IF(C133&lt;1.25,"Easy",IF(C133&lt;=2.8,"Medium",IF(C133&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5860,6 +6403,10 @@
       <c r="J134" t="n">
         <v>7</v>
       </c>
+      <c r="L134">
+        <f>IF(C134="","Excluded (no APD)",IF(C134&lt;1.25,"Easy",IF(C134&lt;=2.8,"Medium",IF(C134&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5900,6 +6447,10 @@
       <c r="J135" t="n">
         <v>7</v>
       </c>
+      <c r="L135">
+        <f>IF(C135="","Excluded (no APD)",IF(C135&lt;1.25,"Easy",IF(C135&lt;=2.8,"Medium",IF(C135&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5940,6 +6491,10 @@
       <c r="J136" t="n">
         <v>7</v>
       </c>
+      <c r="L136">
+        <f>IF(C136="","Excluded (no APD)",IF(C136&lt;1.25,"Easy",IF(C136&lt;=2.8,"Medium",IF(C136&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5980,6 +6535,10 @@
       <c r="J137" t="n">
         <v>7</v>
       </c>
+      <c r="L137">
+        <f>IF(C137="","Excluded (no APD)",IF(C137&lt;1.25,"Easy",IF(C137&lt;=2.8,"Medium",IF(C137&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6020,6 +6579,10 @@
       <c r="J138" t="n">
         <v>10</v>
       </c>
+      <c r="L138">
+        <f>IF(C138="","Excluded (no APD)",IF(C138&lt;1.25,"Easy",IF(C138&lt;=2.8,"Medium",IF(C138&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6060,6 +6623,10 @@
       <c r="J139" t="n">
         <v>8</v>
       </c>
+      <c r="L139">
+        <f>IF(C139="","Excluded (no APD)",IF(C139&lt;1.25,"Easy",IF(C139&lt;=2.8,"Medium",IF(C139&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6100,6 +6667,10 @@
       <c r="J140" t="n">
         <v>8</v>
       </c>
+      <c r="L140">
+        <f>IF(C140="","Excluded (no APD)",IF(C140&lt;1.25,"Easy",IF(C140&lt;=2.8,"Medium",IF(C140&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6140,6 +6711,10 @@
       <c r="J141" t="n">
         <v>8</v>
       </c>
+      <c r="L141">
+        <f>IF(C141="","Excluded (no APD)",IF(C141&lt;1.25,"Easy",IF(C141&lt;=2.8,"Medium",IF(C141&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6180,6 +6755,10 @@
       <c r="J142" t="n">
         <v>7</v>
       </c>
+      <c r="L142">
+        <f>IF(C142="","Excluded (no APD)",IF(C142&lt;1.25,"Easy",IF(C142&lt;=2.8,"Medium",IF(C142&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6220,6 +6799,10 @@
       <c r="J143" t="n">
         <v>8</v>
       </c>
+      <c r="L143">
+        <f>IF(C143="","Excluded (no APD)",IF(C143&lt;1.25,"Easy",IF(C143&lt;=2.8,"Medium",IF(C143&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6265,6 +6848,10 @@
           <t>elf,flea,leafy,fealty</t>
         </is>
       </c>
+      <c r="L144">
+        <f>IF(C144="","Excluded (no APD)",IF(C144&lt;1.25,"Easy",IF(C144&lt;=2.8,"Medium",IF(C144&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6305,6 +6892,10 @@
       <c r="J145" t="n">
         <v>9</v>
       </c>
+      <c r="L145">
+        <f>IF(C145="","Excluded (no APD)",IF(C145&lt;1.25,"Easy",IF(C145&lt;=2.8,"Medium",IF(C145&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6345,6 +6936,10 @@
       <c r="J146" t="n">
         <v>8</v>
       </c>
+      <c r="L146">
+        <f>IF(C146="","Excluded (no APD)",IF(C146&lt;1.25,"Easy",IF(C146&lt;=2.8,"Medium",IF(C146&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6390,6 +6985,10 @@
           <t>drag,grade,garden,angered,renegade,generated</t>
         </is>
       </c>
+      <c r="L147">
+        <f>IF(C147="","Excluded (no APD)",IF(C147&lt;1.25,"Easy",IF(C147&lt;=2.8,"Medium",IF(C147&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6435,6 +7034,10 @@
           <t>entice,genetic,erecting,secreting,respecting</t>
         </is>
       </c>
+      <c r="L148">
+        <f>IF(C148="","Excluded (no APD)",IF(C148&lt;1.25,"Easy",IF(C148&lt;=2.8,"Medium",IF(C148&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6475,6 +7078,10 @@
       <c r="J149" t="n">
         <v>8</v>
       </c>
+      <c r="L149">
+        <f>IF(C149="","Excluded (no APD)",IF(C149&lt;1.25,"Easy",IF(C149&lt;=2.8,"Medium",IF(C149&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6515,6 +7122,10 @@
       <c r="J150" t="n">
         <v>10</v>
       </c>
+      <c r="L150">
+        <f>IF(C150="","Excluded (no APD)",IF(C150&lt;1.25,"Easy",IF(C150&lt;=2.8,"Medium",IF(C150&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6560,6 +7171,10 @@
           <t>dame,medal,calmed,medical,climaxed,exclaimed</t>
         </is>
       </c>
+      <c r="L151">
+        <f>IF(C151="","Excluded (no APD)",IF(C151&lt;1.25,"Easy",IF(C151&lt;=2.8,"Medium",IF(C151&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6600,6 +7215,10 @@
       <c r="J152" t="n">
         <v>8</v>
       </c>
+      <c r="L152">
+        <f>IF(C152="","Excluded (no APD)",IF(C152&lt;1.25,"Easy",IF(C152&lt;=2.8,"Medium",IF(C152&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6640,6 +7259,10 @@
       <c r="J153" t="n">
         <v>8</v>
       </c>
+      <c r="L153">
+        <f>IF(C153="","Excluded (no APD)",IF(C153&lt;1.25,"Easy",IF(C153&lt;=2.8,"Medium",IF(C153&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6685,6 +7308,10 @@
           <t>cornet,trounce,counters,countries,discounter,countryside</t>
         </is>
       </c>
+      <c r="L154">
+        <f>IF(C154="","Excluded (no APD)",IF(C154&lt;1.25,"Easy",IF(C154&lt;=2.8,"Medium",IF(C154&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6725,6 +7352,10 @@
       <c r="J155" t="n">
         <v>10</v>
       </c>
+      <c r="L155">
+        <f>IF(C155="","Excluded (no APD)",IF(C155&lt;1.25,"Easy",IF(C155&lt;=2.8,"Medium",IF(C155&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6765,6 +7396,10 @@
       <c r="J156" t="n">
         <v>7</v>
       </c>
+      <c r="L156">
+        <f>IF(C156="","Excluded (no APD)",IF(C156&lt;1.25,"Easy",IF(C156&lt;=2.8,"Medium",IF(C156&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6805,6 +7440,10 @@
       <c r="J157" t="n">
         <v>10</v>
       </c>
+      <c r="L157">
+        <f>IF(C157="","Excluded (no APD)",IF(C157&lt;1.25,"Easy",IF(C157&lt;=2.8,"Medium",IF(C157&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6845,6 +7484,10 @@
       <c r="J158" t="n">
         <v>10</v>
       </c>
+      <c r="L158">
+        <f>IF(C158="","Excluded (no APD)",IF(C158&lt;1.25,"Easy",IF(C158&lt;=2.8,"Medium",IF(C158&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6885,6 +7528,10 @@
       <c r="J159" t="n">
         <v>7</v>
       </c>
+      <c r="L159">
+        <f>IF(C159="","Excluded (no APD)",IF(C159&lt;1.25,"Easy",IF(C159&lt;=2.8,"Medium",IF(C159&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6925,6 +7572,10 @@
       <c r="J160" t="n">
         <v>8</v>
       </c>
+      <c r="L160">
+        <f>IF(C160="","Excluded (no APD)",IF(C160&lt;1.25,"Easy",IF(C160&lt;=2.8,"Medium",IF(C160&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6965,6 +7616,10 @@
       <c r="J161" t="n">
         <v>6</v>
       </c>
+      <c r="L161">
+        <f>IF(C161="","Excluded (no APD)",IF(C161&lt;1.25,"Easy",IF(C161&lt;=2.8,"Medium",IF(C161&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7010,6 +7665,10 @@
           <t>grid,ridge,bridge,brigade,breading,badgering</t>
         </is>
       </c>
+      <c r="L162">
+        <f>IF(C162="","Excluded (no APD)",IF(C162&lt;1.25,"Easy",IF(C162&lt;=2.8,"Medium",IF(C162&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7050,6 +7709,10 @@
       <c r="J163" t="n">
         <v>9</v>
       </c>
+      <c r="L163">
+        <f>IF(C163="","Excluded (no APD)",IF(C163&lt;1.25,"Easy",IF(C163&lt;=2.8,"Medium",IF(C163&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7090,6 +7753,10 @@
       <c r="J164" t="n">
         <v>7</v>
       </c>
+      <c r="L164">
+        <f>IF(C164="","Excluded (no APD)",IF(C164&lt;1.25,"Easy",IF(C164&lt;=2.8,"Medium",IF(C164&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7130,6 +7797,10 @@
       <c r="J165" t="n">
         <v>8</v>
       </c>
+      <c r="L165">
+        <f>IF(C165="","Excluded (no APD)",IF(C165&lt;1.25,"Easy",IF(C165&lt;=2.8,"Medium",IF(C165&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7170,6 +7841,10 @@
       <c r="J166" t="n">
         <v>6</v>
       </c>
+      <c r="L166">
+        <f>IF(C166="","Excluded (no APD)",IF(C166&lt;1.25,"Easy",IF(C166&lt;=2.8,"Medium",IF(C166&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7210,6 +7885,10 @@
       <c r="J167" t="n">
         <v>7</v>
       </c>
+      <c r="L167">
+        <f>IF(C167="","Excluded (no APD)",IF(C167&lt;1.25,"Easy",IF(C167&lt;=2.8,"Medium",IF(C167&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7255,6 +7934,10 @@
           <t>tuna,taunt,attune,attuned,debutant,debutante</t>
         </is>
       </c>
+      <c r="L168">
+        <f>IF(C168="","Excluded (no APD)",IF(C168&lt;1.25,"Easy",IF(C168&lt;=2.8,"Medium",IF(C168&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7295,6 +7978,10 @@
       <c r="J169" t="n">
         <v>7</v>
       </c>
+      <c r="L169">
+        <f>IF(C169="","Excluded (no APD)",IF(C169&lt;1.25,"Easy",IF(C169&lt;=2.8,"Medium",IF(C169&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7335,6 +8022,10 @@
       <c r="J170" t="n">
         <v>11</v>
       </c>
+      <c r="L170">
+        <f>IF(C170="","Excluded (no APD)",IF(C170&lt;1.25,"Easy",IF(C170&lt;=2.8,"Medium",IF(C170&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7375,6 +8066,10 @@
       <c r="J171" t="n">
         <v>9</v>
       </c>
+      <c r="L171">
+        <f>IF(C171="","Excluded (no APD)",IF(C171&lt;1.25,"Easy",IF(C171&lt;=2.8,"Medium",IF(C171&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7415,6 +8110,10 @@
       <c r="J172" t="n">
         <v>9</v>
       </c>
+      <c r="L172">
+        <f>IF(C172="","Excluded (no APD)",IF(C172&lt;1.25,"Easy",IF(C172&lt;=2.8,"Medium",IF(C172&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7455,6 +8154,10 @@
       <c r="J173" t="n">
         <v>9</v>
       </c>
+      <c r="L173">
+        <f>IF(C173="","Excluded (no APD)",IF(C173&lt;1.25,"Easy",IF(C173&lt;=2.8,"Medium",IF(C173&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7500,6 +8203,10 @@
           <t>sine,dines,diners,insured,sideburn,burnished</t>
         </is>
       </c>
+      <c r="L174">
+        <f>IF(C174="","Excluded (no APD)",IF(C174&lt;1.25,"Easy",IF(C174&lt;=2.8,"Medium",IF(C174&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7540,6 +8247,10 @@
       <c r="J175" t="n">
         <v>9</v>
       </c>
+      <c r="L175">
+        <f>IF(C175="","Excluded (no APD)",IF(C175&lt;1.25,"Easy",IF(C175&lt;=2.8,"Medium",IF(C175&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7580,6 +8291,10 @@
       <c r="J176" t="n">
         <v>8</v>
       </c>
+      <c r="L176">
+        <f>IF(C176="","Excluded (no APD)",IF(C176&lt;1.25,"Easy",IF(C176&lt;=2.8,"Medium",IF(C176&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7620,6 +8335,10 @@
       <c r="J177" t="n">
         <v>8</v>
       </c>
+      <c r="L177">
+        <f>IF(C177="","Excluded (no APD)",IF(C177&lt;1.25,"Easy",IF(C177&lt;=2.8,"Medium",IF(C177&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7660,6 +8379,10 @@
       <c r="J178" t="n">
         <v>11</v>
       </c>
+      <c r="L178">
+        <f>IF(C178="","Excluded (no APD)",IF(C178&lt;1.25,"Easy",IF(C178&lt;=2.8,"Medium",IF(C178&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7700,6 +8423,10 @@
       <c r="J179" t="n">
         <v>8</v>
       </c>
+      <c r="L179">
+        <f>IF(C179="","Excluded (no APD)",IF(C179&lt;1.25,"Easy",IF(C179&lt;=2.8,"Medium",IF(C179&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7740,6 +8467,10 @@
       <c r="J180" t="n">
         <v>11</v>
       </c>
+      <c r="L180">
+        <f>IF(C180="","Excluded (no APD)",IF(C180&lt;1.25,"Easy",IF(C180&lt;=2.8,"Medium",IF(C180&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7780,6 +8511,10 @@
       <c r="J181" t="n">
         <v>9</v>
       </c>
+      <c r="L181">
+        <f>IF(C181="","Excluded (no APD)",IF(C181&lt;1.25,"Easy",IF(C181&lt;=2.8,"Medium",IF(C181&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7820,6 +8555,10 @@
       <c r="J182" t="n">
         <v>7</v>
       </c>
+      <c r="L182">
+        <f>IF(C182="","Excluded (no APD)",IF(C182&lt;1.25,"Easy",IF(C182&lt;=2.8,"Medium",IF(C182&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7860,6 +8599,10 @@
       <c r="J183" t="n">
         <v>10</v>
       </c>
+      <c r="L183">
+        <f>IF(C183="","Excluded (no APD)",IF(C183&lt;1.25,"Easy",IF(C183&lt;=2.8,"Medium",IF(C183&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7900,6 +8643,10 @@
       <c r="J184" t="n">
         <v>9</v>
       </c>
+      <c r="L184">
+        <f>IF(C184="","Excluded (no APD)",IF(C184&lt;1.25,"Easy",IF(C184&lt;=2.8,"Medium",IF(C184&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7940,6 +8687,10 @@
       <c r="J185" t="n">
         <v>8</v>
       </c>
+      <c r="L185">
+        <f>IF(C185="","Excluded (no APD)",IF(C185&lt;1.25,"Easy",IF(C185&lt;=2.8,"Medium",IF(C185&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7980,6 +8731,10 @@
       <c r="J186" t="n">
         <v>9</v>
       </c>
+      <c r="L186">
+        <f>IF(C186="","Excluded (no APD)",IF(C186&lt;1.25,"Easy",IF(C186&lt;=2.8,"Medium",IF(C186&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8020,6 +8775,10 @@
       <c r="J187" t="n">
         <v>8</v>
       </c>
+      <c r="L187">
+        <f>IF(C187="","Excluded (no APD)",IF(C187&lt;1.25,"Easy",IF(C187&lt;=2.8,"Medium",IF(C187&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8060,6 +8819,10 @@
       <c r="J188" t="n">
         <v>8</v>
       </c>
+      <c r="L188">
+        <f>IF(C188="","Excluded (no APD)",IF(C188&lt;1.25,"Easy",IF(C188&lt;=2.8,"Medium",IF(C188&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8100,6 +8863,10 @@
       <c r="J189" t="n">
         <v>8</v>
       </c>
+      <c r="L189">
+        <f>IF(C189="","Excluded (no APD)",IF(C189&lt;1.25,"Easy",IF(C189&lt;=2.8,"Medium",IF(C189&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8140,6 +8907,10 @@
       <c r="J190" t="n">
         <v>8</v>
       </c>
+      <c r="L190">
+        <f>IF(C190="","Excluded (no APD)",IF(C190&lt;1.25,"Easy",IF(C190&lt;=2.8,"Medium",IF(C190&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8180,6 +8951,10 @@
       <c r="J191" t="n">
         <v>11</v>
       </c>
+      <c r="L191">
+        <f>IF(C191="","Excluded (no APD)",IF(C191&lt;1.25,"Easy",IF(C191&lt;=2.8,"Medium",IF(C191&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8220,6 +8995,10 @@
       <c r="J192" t="n">
         <v>10</v>
       </c>
+      <c r="L192">
+        <f>IF(C192="","Excluded (no APD)",IF(C192&lt;1.25,"Easy",IF(C192&lt;=2.8,"Medium",IF(C192&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -8260,6 +9039,10 @@
       <c r="J193" t="n">
         <v>9</v>
       </c>
+      <c r="L193">
+        <f>IF(C193="","Excluded (no APD)",IF(C193&lt;1.25,"Easy",IF(C193&lt;=2.8,"Medium",IF(C193&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8300,6 +9083,10 @@
       <c r="J194" t="n">
         <v>9</v>
       </c>
+      <c r="L194">
+        <f>IF(C194="","Excluded (no APD)",IF(C194&lt;1.25,"Easy",IF(C194&lt;=2.8,"Medium",IF(C194&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -8340,6 +9127,10 @@
       <c r="J195" t="n">
         <v>9</v>
       </c>
+      <c r="L195">
+        <f>IF(C195="","Excluded (no APD)",IF(C195&lt;1.25,"Easy",IF(C195&lt;=2.8,"Medium",IF(C195&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -8380,6 +9171,10 @@
       <c r="J196" t="n">
         <v>7</v>
       </c>
+      <c r="L196">
+        <f>IF(C196="","Excluded (no APD)",IF(C196&lt;1.25,"Easy",IF(C196&lt;=2.8,"Medium",IF(C196&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -8420,6 +9215,10 @@
       <c r="J197" t="n">
         <v>8</v>
       </c>
+      <c r="L197">
+        <f>IF(C197="","Excluded (no APD)",IF(C197&lt;1.25,"Easy",IF(C197&lt;=2.8,"Medium",IF(C197&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8460,6 +9259,10 @@
       <c r="J198" t="n">
         <v>8</v>
       </c>
+      <c r="L198">
+        <f>IF(C198="","Excluded (no APD)",IF(C198&lt;1.25,"Easy",IF(C198&lt;=2.8,"Medium",IF(C198&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8500,6 +9303,10 @@
       <c r="J199" t="n">
         <v>8</v>
       </c>
+      <c r="L199">
+        <f>IF(C199="","Excluded (no APD)",IF(C199&lt;1.25,"Easy",IF(C199&lt;=2.8,"Medium",IF(C199&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8540,6 +9347,10 @@
       <c r="J200" t="n">
         <v>11</v>
       </c>
+      <c r="L200">
+        <f>IF(C200="","Excluded (no APD)",IF(C200&lt;1.25,"Easy",IF(C200&lt;=2.8,"Medium",IF(C200&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8580,6 +9391,10 @@
       <c r="J201" t="n">
         <v>10</v>
       </c>
+      <c r="L201">
+        <f>IF(C201="","Excluded (no APD)",IF(C201&lt;1.25,"Easy",IF(C201&lt;=2.8,"Medium",IF(C201&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8620,6 +9435,10 @@
       <c r="J202" t="n">
         <v>9</v>
       </c>
+      <c r="L202">
+        <f>IF(C202="","Excluded (no APD)",IF(C202&lt;1.25,"Easy",IF(C202&lt;=2.8,"Medium",IF(C202&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -8660,6 +9479,10 @@
       <c r="J203" t="n">
         <v>10</v>
       </c>
+      <c r="L203">
+        <f>IF(C203="","Excluded (no APD)",IF(C203&lt;1.25,"Easy",IF(C203&lt;=2.8,"Medium",IF(C203&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -8700,6 +9523,10 @@
       <c r="J204" t="n">
         <v>9</v>
       </c>
+      <c r="L204">
+        <f>IF(C204="","Excluded (no APD)",IF(C204&lt;1.25,"Easy",IF(C204&lt;=2.8,"Medium",IF(C204&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -8740,6 +9567,10 @@
       <c r="J205" t="n">
         <v>7</v>
       </c>
+      <c r="L205">
+        <f>IF(C205="","Excluded (no APD)",IF(C205&lt;1.25,"Easy",IF(C205&lt;=2.8,"Medium",IF(C205&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -8780,6 +9611,10 @@
       <c r="J206" t="n">
         <v>7</v>
       </c>
+      <c r="L206">
+        <f>IF(C206="","Excluded (no APD)",IF(C206&lt;1.25,"Easy",IF(C206&lt;=2.8,"Medium",IF(C206&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -8820,6 +9655,10 @@
       <c r="J207" t="n">
         <v>8</v>
       </c>
+      <c r="L207">
+        <f>IF(C207="","Excluded (no APD)",IF(C207&lt;1.25,"Easy",IF(C207&lt;=2.8,"Medium",IF(C207&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -8860,6 +9699,10 @@
       <c r="J208" t="n">
         <v>8</v>
       </c>
+      <c r="L208">
+        <f>IF(C208="","Excluded (no APD)",IF(C208&lt;1.25,"Easy",IF(C208&lt;=2.8,"Medium",IF(C208&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8900,6 +9743,10 @@
       <c r="J209" t="n">
         <v>8</v>
       </c>
+      <c r="L209">
+        <f>IF(C209="","Excluded (no APD)",IF(C209&lt;1.25,"Easy",IF(C209&lt;=2.8,"Medium",IF(C209&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -8940,6 +9787,10 @@
       <c r="J210" t="n">
         <v>12</v>
       </c>
+      <c r="L210">
+        <f>IF(C210="","Excluded (no APD)",IF(C210&lt;1.25,"Easy",IF(C210&lt;=2.8,"Medium",IF(C210&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8980,6 +9831,10 @@
       <c r="J211" t="n">
         <v>9</v>
       </c>
+      <c r="L211">
+        <f>IF(C211="","Excluded (no APD)",IF(C211&lt;1.25,"Easy",IF(C211&lt;=2.8,"Medium",IF(C211&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -9020,6 +9875,10 @@
       <c r="J212" t="n">
         <v>9</v>
       </c>
+      <c r="L212">
+        <f>IF(C212="","Excluded (no APD)",IF(C212&lt;1.25,"Easy",IF(C212&lt;=2.8,"Medium",IF(C212&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -9060,6 +9919,10 @@
       <c r="J213" t="n">
         <v>8</v>
       </c>
+      <c r="L213">
+        <f>IF(C213="","Excluded (no APD)",IF(C213&lt;1.25,"Easy",IF(C213&lt;=2.8,"Medium",IF(C213&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -9100,6 +9963,10 @@
       <c r="J214" t="n">
         <v>10</v>
       </c>
+      <c r="L214">
+        <f>IF(C214="","Excluded (no APD)",IF(C214&lt;1.25,"Easy",IF(C214&lt;=2.8,"Medium",IF(C214&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -9140,6 +10007,10 @@
       <c r="J215" t="n">
         <v>9</v>
       </c>
+      <c r="L215">
+        <f>IF(C215="","Excluded (no APD)",IF(C215&lt;1.25,"Easy",IF(C215&lt;=2.8,"Medium",IF(C215&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -9180,6 +10051,10 @@
       <c r="J216" t="n">
         <v>9</v>
       </c>
+      <c r="L216">
+        <f>IF(C216="","Excluded (no APD)",IF(C216&lt;1.25,"Easy",IF(C216&lt;=2.8,"Medium",IF(C216&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -9220,6 +10095,10 @@
       <c r="J217" t="n">
         <v>9</v>
       </c>
+      <c r="L217">
+        <f>IF(C217="","Excluded (no APD)",IF(C217&lt;1.25,"Easy",IF(C217&lt;=2.8,"Medium",IF(C217&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -9260,6 +10139,10 @@
       <c r="J218" t="n">
         <v>8</v>
       </c>
+      <c r="L218">
+        <f>IF(C218="","Excluded (no APD)",IF(C218&lt;1.25,"Easy",IF(C218&lt;=2.8,"Medium",IF(C218&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -9300,6 +10183,10 @@
       <c r="J219" t="n">
         <v>9</v>
       </c>
+      <c r="L219">
+        <f>IF(C219="","Excluded (no APD)",IF(C219&lt;1.25,"Easy",IF(C219&lt;=2.8,"Medium",IF(C219&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -9340,6 +10227,10 @@
       <c r="J220" t="n">
         <v>9</v>
       </c>
+      <c r="L220">
+        <f>IF(C220="","Excluded (no APD)",IF(C220&lt;1.25,"Easy",IF(C220&lt;=2.8,"Medium",IF(C220&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -9380,6 +10271,10 @@
       <c r="J221" t="n">
         <v>8</v>
       </c>
+      <c r="L221">
+        <f>IF(C221="","Excluded (no APD)",IF(C221&lt;1.25,"Easy",IF(C221&lt;=2.8,"Medium",IF(C221&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -9420,6 +10315,10 @@
       <c r="J222" t="n">
         <v>9</v>
       </c>
+      <c r="L222">
+        <f>IF(C222="","Excluded (no APD)",IF(C222&lt;1.25,"Easy",IF(C222&lt;=2.8,"Medium",IF(C222&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -9460,6 +10359,10 @@
       <c r="J223" t="n">
         <v>9</v>
       </c>
+      <c r="L223">
+        <f>IF(C223="","Excluded (no APD)",IF(C223&lt;1.25,"Easy",IF(C223&lt;=2.8,"Medium",IF(C223&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -9500,6 +10403,10 @@
       <c r="J224" t="n">
         <v>9</v>
       </c>
+      <c r="L224">
+        <f>IF(C224="","Excluded (no APD)",IF(C224&lt;1.25,"Easy",IF(C224&lt;=2.8,"Medium",IF(C224&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -9540,6 +10447,10 @@
       <c r="J225" t="n">
         <v>9</v>
       </c>
+      <c r="L225">
+        <f>IF(C225="","Excluded (no APD)",IF(C225&lt;1.25,"Easy",IF(C225&lt;=2.8,"Medium",IF(C225&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -9580,6 +10491,10 @@
       <c r="J226" t="n">
         <v>8</v>
       </c>
+      <c r="L226">
+        <f>IF(C226="","Excluded (no APD)",IF(C226&lt;1.25,"Easy",IF(C226&lt;=2.8,"Medium",IF(C226&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -9620,6 +10535,10 @@
       <c r="J227" t="n">
         <v>8</v>
       </c>
+      <c r="L227">
+        <f>IF(C227="","Excluded (no APD)",IF(C227&lt;1.25,"Easy",IF(C227&lt;=2.8,"Medium",IF(C227&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -9660,6 +10579,10 @@
       <c r="J228" t="n">
         <v>8</v>
       </c>
+      <c r="L228">
+        <f>IF(C228="","Excluded (no APD)",IF(C228&lt;1.25,"Easy",IF(C228&lt;=2.8,"Medium",IF(C228&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -9700,6 +10623,10 @@
       <c r="J229" t="n">
         <v>10</v>
       </c>
+      <c r="L229">
+        <f>IF(C229="","Excluded (no APD)",IF(C229&lt;1.25,"Easy",IF(C229&lt;=2.8,"Medium",IF(C229&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -9740,6 +10667,10 @@
       <c r="J230" t="n">
         <v>11</v>
       </c>
+      <c r="L230">
+        <f>IF(C230="","Excluded (no APD)",IF(C230&lt;1.25,"Easy",IF(C230&lt;=2.8,"Medium",IF(C230&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -9780,6 +10711,10 @@
       <c r="J231" t="n">
         <v>7</v>
       </c>
+      <c r="L231">
+        <f>IF(C231="","Excluded (no APD)",IF(C231&lt;1.25,"Easy",IF(C231&lt;=2.8,"Medium",IF(C231&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -9820,6 +10755,10 @@
       <c r="J232" t="n">
         <v>7</v>
       </c>
+      <c r="L232">
+        <f>IF(C232="","Excluded (no APD)",IF(C232&lt;1.25,"Easy",IF(C232&lt;=2.8,"Medium",IF(C232&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -9860,6 +10799,10 @@
       <c r="J233" t="n">
         <v>8</v>
       </c>
+      <c r="L233">
+        <f>IF(C233="","Excluded (no APD)",IF(C233&lt;1.25,"Easy",IF(C233&lt;=2.8,"Medium",IF(C233&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -9900,6 +10843,10 @@
       <c r="J234" t="n">
         <v>8</v>
       </c>
+      <c r="L234">
+        <f>IF(C234="","Excluded (no APD)",IF(C234&lt;1.25,"Easy",IF(C234&lt;=2.8,"Medium",IF(C234&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -9940,6 +10887,10 @@
       <c r="J235" t="n">
         <v>8</v>
       </c>
+      <c r="L235">
+        <f>IF(C235="","Excluded (no APD)",IF(C235&lt;1.25,"Easy",IF(C235&lt;=2.8,"Medium",IF(C235&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -9980,6 +10931,10 @@
       <c r="J236" t="n">
         <v>8</v>
       </c>
+      <c r="L236">
+        <f>IF(C236="","Excluded (no APD)",IF(C236&lt;1.25,"Easy",IF(C236&lt;=2.8,"Medium",IF(C236&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -10020,6 +10975,10 @@
       <c r="J237" t="n">
         <v>8</v>
       </c>
+      <c r="L237">
+        <f>IF(C237="","Excluded (no APD)",IF(C237&lt;1.25,"Easy",IF(C237&lt;=2.8,"Medium",IF(C237&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -10060,6 +11019,10 @@
       <c r="J238" t="n">
         <v>9</v>
       </c>
+      <c r="L238">
+        <f>IF(C238="","Excluded (no APD)",IF(C238&lt;1.25,"Easy",IF(C238&lt;=2.8,"Medium",IF(C238&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -10100,6 +11063,10 @@
       <c r="J239" t="n">
         <v>7</v>
       </c>
+      <c r="L239">
+        <f>IF(C239="","Excluded (no APD)",IF(C239&lt;1.25,"Easy",IF(C239&lt;=2.8,"Medium",IF(C239&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -10140,6 +11107,10 @@
       <c r="J240" t="n">
         <v>7</v>
       </c>
+      <c r="L240">
+        <f>IF(C240="","Excluded (no APD)",IF(C240&lt;1.25,"Easy",IF(C240&lt;=2.8,"Medium",IF(C240&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -10180,6 +11151,10 @@
       <c r="J241" t="n">
         <v>6</v>
       </c>
+      <c r="L241">
+        <f>IF(C241="","Excluded (no APD)",IF(C241&lt;1.25,"Easy",IF(C241&lt;=2.8,"Medium",IF(C241&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -10220,6 +11195,10 @@
       <c r="J242" t="n">
         <v>7</v>
       </c>
+      <c r="L242">
+        <f>IF(C242="","Excluded (no APD)",IF(C242&lt;1.25,"Easy",IF(C242&lt;=2.8,"Medium",IF(C242&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -10260,6 +11239,10 @@
       <c r="J243" t="n">
         <v>7</v>
       </c>
+      <c r="L243">
+        <f>IF(C243="","Excluded (no APD)",IF(C243&lt;1.25,"Easy",IF(C243&lt;=2.8,"Medium",IF(C243&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -10300,6 +11283,10 @@
       <c r="J244" t="n">
         <v>9</v>
       </c>
+      <c r="L244">
+        <f>IF(C244="","Excluded (no APD)",IF(C244&lt;1.25,"Easy",IF(C244&lt;=2.8,"Medium",IF(C244&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -10340,6 +11327,10 @@
       <c r="J245" t="n">
         <v>7</v>
       </c>
+      <c r="L245">
+        <f>IF(C245="","Excluded (no APD)",IF(C245&lt;1.25,"Easy",IF(C245&lt;=2.8,"Medium",IF(C245&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -10380,6 +11371,10 @@
       <c r="J246" t="n">
         <v>8</v>
       </c>
+      <c r="L246">
+        <f>IF(C246="","Excluded (no APD)",IF(C246&lt;1.25,"Easy",IF(C246&lt;=2.8,"Medium",IF(C246&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -10420,6 +11415,10 @@
       <c r="J247" t="n">
         <v>9</v>
       </c>
+      <c r="L247">
+        <f>IF(C247="","Excluded (no APD)",IF(C247&lt;1.25,"Easy",IF(C247&lt;=2.8,"Medium",IF(C247&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -10460,6 +11459,10 @@
       <c r="J248" t="n">
         <v>9</v>
       </c>
+      <c r="L248">
+        <f>IF(C248="","Excluded (no APD)",IF(C248&lt;1.25,"Easy",IF(C248&lt;=2.8,"Medium",IF(C248&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -10500,6 +11503,10 @@
       <c r="J249" t="n">
         <v>7</v>
       </c>
+      <c r="L249">
+        <f>IF(C249="","Excluded (no APD)",IF(C249&lt;1.25,"Easy",IF(C249&lt;=2.8,"Medium",IF(C249&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -10540,6 +11547,10 @@
       <c r="J250" t="n">
         <v>8</v>
       </c>
+      <c r="L250">
+        <f>IF(C250="","Excluded (no APD)",IF(C250&lt;1.25,"Easy",IF(C250&lt;=2.8,"Medium",IF(C250&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -10580,6 +11591,10 @@
       <c r="J251" t="n">
         <v>7</v>
       </c>
+      <c r="L251">
+        <f>IF(C251="","Excluded (no APD)",IF(C251&lt;1.25,"Easy",IF(C251&lt;=2.8,"Medium",IF(C251&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -10620,6 +11635,10 @@
       <c r="J252" t="n">
         <v>7</v>
       </c>
+      <c r="L252">
+        <f>IF(C252="","Excluded (no APD)",IF(C252&lt;1.25,"Easy",IF(C252&lt;=2.8,"Medium",IF(C252&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -10660,6 +11679,10 @@
       <c r="J253" t="n">
         <v>10</v>
       </c>
+      <c r="L253">
+        <f>IF(C253="","Excluded (no APD)",IF(C253&lt;1.25,"Easy",IF(C253&lt;=2.8,"Medium",IF(C253&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -10700,6 +11723,10 @@
       <c r="J254" t="n">
         <v>8</v>
       </c>
+      <c r="L254">
+        <f>IF(C254="","Excluded (no APD)",IF(C254&lt;1.25,"Easy",IF(C254&lt;=2.8,"Medium",IF(C254&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -10740,6 +11767,10 @@
       <c r="J255" t="n">
         <v>7</v>
       </c>
+      <c r="L255">
+        <f>IF(C255="","Excluded (no APD)",IF(C255&lt;1.25,"Easy",IF(C255&lt;=2.8,"Medium",IF(C255&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -10780,6 +11811,10 @@
       <c r="J256" t="n">
         <v>8</v>
       </c>
+      <c r="L256">
+        <f>IF(C256="","Excluded (no APD)",IF(C256&lt;1.25,"Easy",IF(C256&lt;=2.8,"Medium",IF(C256&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -10820,6 +11855,10 @@
       <c r="J257" t="n">
         <v>8</v>
       </c>
+      <c r="L257">
+        <f>IF(C257="","Excluded (no APD)",IF(C257&lt;1.25,"Easy",IF(C257&lt;=2.8,"Medium",IF(C257&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -10860,6 +11899,10 @@
       <c r="J258" t="n">
         <v>9</v>
       </c>
+      <c r="L258">
+        <f>IF(C258="","Excluded (no APD)",IF(C258&lt;1.25,"Easy",IF(C258&lt;=2.8,"Medium",IF(C258&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -10900,6 +11943,10 @@
       <c r="J259" t="n">
         <v>8</v>
       </c>
+      <c r="L259">
+        <f>IF(C259="","Excluded (no APD)",IF(C259&lt;1.25,"Easy",IF(C259&lt;=2.8,"Medium",IF(C259&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -10940,6 +11987,10 @@
       <c r="J260" t="n">
         <v>10</v>
       </c>
+      <c r="L260">
+        <f>IF(C260="","Excluded (no APD)",IF(C260&lt;1.25,"Easy",IF(C260&lt;=2.8,"Medium",IF(C260&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -10980,6 +12031,10 @@
       <c r="J261" t="n">
         <v>9</v>
       </c>
+      <c r="L261">
+        <f>IF(C261="","Excluded (no APD)",IF(C261&lt;1.25,"Easy",IF(C261&lt;=2.8,"Medium",IF(C261&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -11020,6 +12075,10 @@
       <c r="J262" t="n">
         <v>9</v>
       </c>
+      <c r="L262">
+        <f>IF(C262="","Excluded (no APD)",IF(C262&lt;1.25,"Easy",IF(C262&lt;=2.8,"Medium",IF(C262&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -11060,6 +12119,10 @@
       <c r="J263" t="n">
         <v>9</v>
       </c>
+      <c r="L263">
+        <f>IF(C263="","Excluded (no APD)",IF(C263&lt;1.25,"Easy",IF(C263&lt;=2.8,"Medium",IF(C263&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -11100,6 +12163,10 @@
       <c r="J264" t="n">
         <v>8</v>
       </c>
+      <c r="L264">
+        <f>IF(C264="","Excluded (no APD)",IF(C264&lt;1.25,"Easy",IF(C264&lt;=2.8,"Medium",IF(C264&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -11140,6 +12207,10 @@
       <c r="J265" t="n">
         <v>8</v>
       </c>
+      <c r="L265">
+        <f>IF(C265="","Excluded (no APD)",IF(C265&lt;1.25,"Easy",IF(C265&lt;=2.8,"Medium",IF(C265&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -11180,6 +12251,10 @@
       <c r="J266" t="n">
         <v>9</v>
       </c>
+      <c r="L266">
+        <f>IF(C266="","Excluded (no APD)",IF(C266&lt;1.25,"Easy",IF(C266&lt;=2.8,"Medium",IF(C266&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -11220,6 +12295,10 @@
       <c r="J267" t="n">
         <v>8</v>
       </c>
+      <c r="L267">
+        <f>IF(C267="","Excluded (no APD)",IF(C267&lt;1.25,"Easy",IF(C267&lt;=2.8,"Medium",IF(C267&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -11260,6 +12339,10 @@
       <c r="J268" t="n">
         <v>11</v>
       </c>
+      <c r="L268">
+        <f>IF(C268="","Excluded (no APD)",IF(C268&lt;1.25,"Easy",IF(C268&lt;=2.8,"Medium",IF(C268&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -11300,6 +12383,10 @@
       <c r="J269" t="n">
         <v>8</v>
       </c>
+      <c r="L269">
+        <f>IF(C269="","Excluded (no APD)",IF(C269&lt;1.25,"Easy",IF(C269&lt;=2.8,"Medium",IF(C269&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -11342,6 +12429,10 @@
           <t>sea,seal,stale</t>
         </is>
       </c>
+      <c r="L270">
+        <f>IF(C270="","Excluded (no APD)",IF(C270&lt;1.25,"Easy",IF(C270&lt;=2.8,"Medium",IF(C270&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -11384,6 +12475,10 @@
           <t>ice,nice,since</t>
         </is>
       </c>
+      <c r="L271">
+        <f>IF(C271="","Excluded (no APD)",IF(C271&lt;1.25,"Easy",IF(C271&lt;=2.8,"Medium",IF(C271&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -11426,6 +12521,10 @@
           <t>ar,are,care,racer</t>
         </is>
       </c>
+      <c r="L272">
+        <f>IF(C272="","Excluded (no APD)",IF(C272&lt;1.25,"Easy",IF(C272&lt;=2.8,"Medium",IF(C272&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -11468,6 +12567,10 @@
           <t>in,din,rind,diner</t>
         </is>
       </c>
+      <c r="L273">
+        <f>IF(C273="","Excluded (no APD)",IF(C273&lt;1.25,"Easy",IF(C273&lt;=2.8,"Medium",IF(C273&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -11510,6 +12613,10 @@
           <t>it,hit,thin,think</t>
         </is>
       </c>
+      <c r="L274">
+        <f>IF(C274="","Excluded (no APD)",IF(C274&lt;1.25,"Easy",IF(C274&lt;=2.8,"Medium",IF(C274&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -11552,6 +12659,10 @@
           <t>oh,hot,moth,mouth</t>
         </is>
       </c>
+      <c r="L275">
+        <f>IF(C275="","Excluded (no APD)",IF(C275&lt;1.25,"Easy",IF(C275&lt;=2.8,"Medium",IF(C275&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -11594,6 +12705,10 @@
           <t>sip,rips,spire</t>
         </is>
       </c>
+      <c r="L276">
+        <f>IF(C276="","Excluded (no APD)",IF(C276&lt;1.25,"Easy",IF(C276&lt;=2.8,"Medium",IF(C276&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -11636,6 +12751,10 @@
           <t>us,bus,busy,bushy</t>
         </is>
       </c>
+      <c r="L277">
+        <f>IF(C277="","Excluded (no APD)",IF(C277&lt;1.25,"Easy",IF(C277&lt;=2.8,"Medium",IF(C277&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -11678,6 +12797,10 @@
           <t>as,sea,sear,scare,scared</t>
         </is>
       </c>
+      <c r="L278">
+        <f>IF(C278="","Excluded (no APD)",IF(C278&lt;1.25,"Easy",IF(C278&lt;=2.8,"Medium",IF(C278&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -11720,6 +12843,10 @@
           <t>at,rat,rate,crate,crater</t>
         </is>
       </c>
+      <c r="L279">
+        <f>IF(C279="","Excluded (no APD)",IF(C279&lt;1.25,"Easy",IF(C279&lt;=2.8,"Medium",IF(C279&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -11757,6 +12884,10 @@
       <c r="J280" t="n">
         <v>6</v>
       </c>
+      <c r="L280">
+        <f>IF(C280="","Excluded (no APD)",IF(C280&lt;1.25,"Easy",IF(C280&lt;=2.8,"Medium",IF(C280&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -11794,6 +12925,10 @@
       <c r="J281" t="n">
         <v>6</v>
       </c>
+      <c r="L281">
+        <f>IF(C281="","Excluded (no APD)",IF(C281&lt;1.25,"Easy",IF(C281&lt;=2.8,"Medium",IF(C281&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -11831,6 +12966,10 @@
       <c r="J282" t="n">
         <v>6</v>
       </c>
+      <c r="L282">
+        <f>IF(C282="","Excluded (no APD)",IF(C282&lt;1.25,"Easy",IF(C282&lt;=2.8,"Medium",IF(C282&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -11868,6 +13007,10 @@
       <c r="J283" t="n">
         <v>7</v>
       </c>
+      <c r="L283">
+        <f>IF(C283="","Excluded (no APD)",IF(C283&lt;1.25,"Easy",IF(C283&lt;=2.8,"Medium",IF(C283&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -11904,6 +13047,10 @@
       </c>
       <c r="J284" t="n">
         <v>6</v>
+      </c>
+      <c r="L284">
+        <f>IF(C284="","Excluded (no APD)",IF(C284&lt;1.25,"Easy",IF(C284&lt;=2.8,"Medium",IF(C284&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -7267,7 +7267,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>cornet</t>
+          <t>toner</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7298,14 +7298,14 @@
         <v>168</v>
       </c>
       <c r="I154" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J154" t="n">
         <v>11</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>cornet,trounce,counters,countries,discounter,countryside</t>
+          <t>toner,cornet,trounce,counters,countries,discounter,countryside</t>
         </is>
       </c>
       <c r="L154">

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L284"/>
+  <dimension ref="A1:L285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7130,7 +7130,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>dame</t>
+          <t>ma</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -7161,14 +7161,14 @@
         <v>165</v>
       </c>
       <c r="I151" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J151" t="n">
         <v>9</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>dame,medal,calmed,medical,climaxed,exclaimed</t>
+          <t>ma,mad,dame,medal,calmed,medical,climaxed,exclaimed</t>
         </is>
       </c>
       <c r="L151">
@@ -7276,7 +7276,7 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>3.111</v>
+        <v>3.05</v>
       </c>
       <c r="D154" t="n">
         <v>3</v>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>toner,cornet,trounce,counters,countries,discounter,countryside</t>
+          <t>toner,cornet,trounce,counters,countries,introduces,countryside</t>
         </is>
       </c>
       <c r="L154">
@@ -13050,6 +13050,44 @@
       </c>
       <c r="L284">
         <f>IF(C284="","Excluded (no APD)",IF(C284&lt;1.25,"Easy",IF(C284&lt;=2.8,"Medium",IF(C284&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>selecting</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D285" t="n">
+        <v>3</v>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="I285" t="n">
+        <v>4</v>
+      </c>
+      <c r="J285" t="n">
+        <v>9</v>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>nice,niece,entice,genetic,electing,selecting</t>
+        </is>
+      </c>
+      <c r="L285">
+        <f>IF(C285="","Excluded (no APD)",IF(C285&lt;1.25,"Easy",IF(C285&lt;=2.8,"Medium",IF(C285&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
         <v/>
       </c>
     </row>

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -3213,7 +3213,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ace</t>
+          <t>rad</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>ace,care,crate,traced,reacted,decorate,relocated,correlated</t>
+          <t>rad,card,cared,traced,reacted,decorate,relocated,correlated</t>
         </is>
       </c>
       <c r="L63">

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L285"/>
+  <dimension ref="A1:L287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="D74" t="n">
         <v>2</v>
@@ -3743,6 +3743,11 @@
       <c r="J74" t="n">
         <v>6</v>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>at,rat,cart,carat,tarmac</t>
+        </is>
+      </c>
       <c r="L74">
         <f>IF(C74="","Excluded (no APD)",IF(C74&lt;1.25,"Easy",IF(C74&lt;=2.8,"Medium",IF(C74&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
         <v/>
@@ -13088,6 +13093,82 @@
       </c>
       <c r="L285">
         <f>IF(C285="","Excluded (no APD)",IF(C285&lt;1.25,"Easy",IF(C285&lt;=2.8,"Medium",IF(C285&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>tires</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D286" t="n">
+        <v>1</v>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>rookie</t>
+        </is>
+      </c>
+      <c r="I286" t="n">
+        <v>2</v>
+      </c>
+      <c r="J286" t="n">
+        <v>5</v>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>it,sit,ties,tires</t>
+        </is>
+      </c>
+      <c r="L286">
+        <f>IF(C286="","Excluded (no APD)",IF(C286&lt;1.25,"Easy",IF(C286&lt;=2.8,"Medium",IF(C286&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>undertows</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="D287" t="n">
+        <v>3</v>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="I287" t="n">
+        <v>2</v>
+      </c>
+      <c r="J287" t="n">
+        <v>9</v>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>to,toe,note,tones,stoner,snorted,roundest,undertows</t>
+        </is>
+      </c>
+      <c r="L287">
+        <f>IF(C287="","Excluded (no APD)",IF(C287&lt;1.25,"Easy",IF(C287&lt;=2.8,"Medium",IF(C287&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
         <v/>
       </c>
     </row>

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3.1</v>
+        <v>3.095</v>
       </c>
       <c r="D63" t="n">
         <v>3</v>
@@ -7144,7 +7144,7 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="D151" t="n">
         <v>3</v>

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L288"/>
+  <dimension ref="A1:L303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4.52</v>
+        <v>3.1004625</v>
       </c>
       <c r="D32" t="n">
         <v>4</v>
@@ -1875,6 +1875,11 @@
       <c r="J32" t="n">
         <v>9</v>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>on,one,once,coned,coined,demonic,comedian,dominance</t>
+        </is>
+      </c>
       <c r="L32">
         <f>IF(C33="","Excluded (no APD)",IF(C33&lt;1.25,"Easy",IF(C33&lt;=2.8,"Medium",IF(C33&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
         <v/>
@@ -2552,7 +2557,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2.5</v>
+        <v>3.0994875</v>
       </c>
       <c r="D48" t="n">
         <v>2</v>
@@ -2579,6 +2584,11 @@
       <c r="J48" t="n">
         <v>9</v>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>an,ran,rain,train,martin,martian,animator,laminator</t>
+        </is>
+      </c>
       <c r="L48">
         <f>IF(C49="","Excluded (no APD)",IF(C49&lt;1.25,"Easy",IF(C49&lt;=2.8,"Medium",IF(C49&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
         <v/>
@@ -5799,7 +5809,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1.95</v>
+        <v>2.0975</v>
       </c>
       <c r="D121" t="n">
         <v>1</v>
@@ -5826,6 +5836,11 @@
       <c r="J121" t="n">
         <v>8</v>
       </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>raptor,prorate,parroted</t>
+        </is>
+      </c>
       <c r="L121">
         <f>IF(C122="","Excluded (no APD)",IF(C122&lt;1.25,"Easy",IF(C122&lt;=2.8,"Medium",IF(C122&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
         <v/>
@@ -5941,7 +5956,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1.8</v>
+        <v>2.085</v>
       </c>
       <c r="D124" t="n">
         <v>2</v>
@@ -5968,6 +5983,11 @@
       <c r="J124" t="n">
         <v>8</v>
       </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>is,sir,rise,cries,cruise,curries,scurried</t>
+        </is>
+      </c>
       <c r="L124">
         <f>IF(C125="","Excluded (no APD)",IF(C125&lt;1.25,"Easy",IF(C125&lt;=2.8,"Medium",IF(C125&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
         <v/>
@@ -8533,7 +8553,7 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>999.0005999999998</v>
+        <v>3.099975</v>
       </c>
       <c r="D182" t="n">
         <v>999</v>
@@ -8560,6 +8580,11 @@
       <c r="J182" t="n">
         <v>10</v>
       </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>teal,leant,entail,elation,oriental,rationale,relational</t>
+        </is>
+      </c>
       <c r="L182">
         <f>IF(C183="","Excluded (no APD)",IF(C183&lt;1.25,"Easy",IF(C183&lt;=2.8,"Medium",IF(C183&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
         <v/>
@@ -11217,7 +11242,7 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>999.0067999999983</v>
+        <v>3.101925</v>
       </c>
       <c r="D243" t="n">
         <v>999</v>
@@ -11244,6 +11269,11 @@
       <c r="J243" t="n">
         <v>9</v>
       </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>rots,store,toners,monster,monstera,ornaments</t>
+        </is>
+      </c>
       <c r="L243">
         <f>IF(C244="","Excluded (no APD)",IF(C244&lt;1.25,"Easy",IF(C244&lt;=2.8,"Medium",IF(C244&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
         <v/>
@@ -13206,6 +13236,576 @@
       </c>
       <c r="L288">
         <f>IF(C289="","Excluded (no APD)",IF(C289&lt;1.25,"Easy",IF(C289&lt;=2.8,"Medium",IF(C289&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>he</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="D289" t="n">
+        <v>1</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>rookie</t>
+        </is>
+      </c>
+      <c r="I289" t="n">
+        <v>2</v>
+      </c>
+      <c r="J289" t="n">
+        <v>5</v>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>he,she,shoe,house</t>
+        </is>
+      </c>
+      <c r="L289">
+        <f>IF(C289="","Excluded (no APD)",IF(C289&lt;1.25,"Easy",IF(C289&lt;=2.8,"Medium",IF(C289&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>despotic</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>2.0825</v>
+      </c>
+      <c r="D290" t="n">
+        <v>2</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="I290" t="n">
+        <v>2</v>
+      </c>
+      <c r="J290" t="n">
+        <v>8</v>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>is,sip,pies,poise,poised,deposit,despotic</t>
+        </is>
+      </c>
+      <c r="L290">
+        <f>IF(C290="","Excluded (no APD)",IF(C290&lt;1.25,"Easy",IF(C290&lt;=2.8,"Medium",IF(C290&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="D291" t="n">
+        <v>1</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>rookie</t>
+        </is>
+      </c>
+      <c r="I291" t="n">
+        <v>2</v>
+      </c>
+      <c r="J291" t="n">
+        <v>5</v>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>no,now,worn,brown</t>
+        </is>
+      </c>
+      <c r="L291">
+        <f>IF(C291="","Excluded (no APD)",IF(C291&lt;1.25,"Easy",IF(C291&lt;=2.8,"Medium",IF(C291&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="D292" t="n">
+        <v>1</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>rookie</t>
+        </is>
+      </c>
+      <c r="I292" t="n">
+        <v>3</v>
+      </c>
+      <c r="J292" t="n">
+        <v>6</v>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>sat,teas,baste,tables</t>
+        </is>
+      </c>
+      <c r="L292">
+        <f>IF(C292="","Excluded (no APD)",IF(C292&lt;1.25,"Easy",IF(C292&lt;=2.8,"Medium",IF(C292&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>gee</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>enlarge</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>2.0875</v>
+      </c>
+      <c r="D293" t="n">
+        <v>2</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="I293" t="n">
+        <v>3</v>
+      </c>
+      <c r="J293" t="n">
+        <v>7</v>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>gee,glee,eagle,regale,enlarge</t>
+        </is>
+      </c>
+      <c r="L293">
+        <f>IF(C293="","Excluded (no APD)",IF(C293&lt;1.25,"Easy",IF(C293&lt;=2.8,"Medium",IF(C293&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>tuners</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="D294" t="n">
+        <v>1</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>rookie</t>
+        </is>
+      </c>
+      <c r="I294" t="n">
+        <v>3</v>
+      </c>
+      <c r="J294" t="n">
+        <v>6</v>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>sun,nuts,tunes,tuners</t>
+        </is>
+      </c>
+      <c r="L294">
+        <f>IF(C294="","Excluded (no APD)",IF(C294&lt;1.25,"Easy",IF(C294&lt;=2.8,"Medium",IF(C294&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>grandiose</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="D295" t="n">
+        <v>2</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="I295" t="n">
+        <v>3</v>
+      </c>
+      <c r="J295" t="n">
+        <v>9</v>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>air,rain,grain,regain,searing,readings,grandiose</t>
+        </is>
+      </c>
+      <c r="L295">
+        <f>IF(C295="","Excluded (no APD)",IF(C295&lt;1.25,"Easy",IF(C295&lt;=2.8,"Medium",IF(C295&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>sine</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>cremations</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>3.10095</v>
+      </c>
+      <c r="D296" t="n">
+        <v>3</v>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="I296" t="n">
+        <v>4</v>
+      </c>
+      <c r="J296" t="n">
+        <v>10</v>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>sine,mines,inseam,inmates,semantic,miscreant,cremations</t>
+        </is>
+      </c>
+      <c r="L296">
+        <f>IF(C296="","Excluded (no APD)",IF(C296&lt;1.25,"Easy",IF(C296&lt;=2.8,"Medium",IF(C296&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>pa</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>rapid</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="D297" t="n">
+        <v>1</v>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>rookie</t>
+        </is>
+      </c>
+      <c r="I297" t="n">
+        <v>2</v>
+      </c>
+      <c r="J297" t="n">
+        <v>5</v>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>pa,rap,pair,rapid</t>
+        </is>
+      </c>
+      <c r="L297">
+        <f>IF(C297="","Excluded (no APD)",IF(C297&lt;1.25,"Easy",IF(C297&lt;=2.8,"Medium",IF(C297&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>diet</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>insulated</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>2.0925</v>
+      </c>
+      <c r="D298" t="n">
+        <v>2</v>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="I298" t="n">
+        <v>4</v>
+      </c>
+      <c r="J298" t="n">
+        <v>9</v>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>diet,tiled,listed,duelist,insulted,insulated</t>
+        </is>
+      </c>
+      <c r="L298">
+        <f>IF(C298="","Excluded (no APD)",IF(C298&lt;1.25,"Easy",IF(C298&lt;=2.8,"Medium",IF(C298&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>archives</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>3.1014375</v>
+      </c>
+      <c r="D299" t="n">
+        <v>3</v>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="I299" t="n">
+        <v>3</v>
+      </c>
+      <c r="J299" t="n">
+        <v>8</v>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>sea,save,caves,craves,viscera,archives</t>
+        </is>
+      </c>
+      <c r="L299">
+        <f>IF(C299="","Excluded (no APD)",IF(C299&lt;1.25,"Easy",IF(C299&lt;=2.8,"Medium",IF(C299&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>mar</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>camper</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="D300" t="n">
+        <v>1</v>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>rookie</t>
+        </is>
+      </c>
+      <c r="I300" t="n">
+        <v>3</v>
+      </c>
+      <c r="J300" t="n">
+        <v>6</v>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>mar,ramp,cramp,camper</t>
+        </is>
+      </c>
+      <c r="L300">
+        <f>IF(C300="","Excluded (no APD)",IF(C300&lt;1.25,"Easy",IF(C300&lt;=2.8,"Medium",IF(C300&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>gem</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>magenta</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>2.095</v>
+      </c>
+      <c r="D301" t="n">
+        <v>2</v>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="I301" t="n">
+        <v>3</v>
+      </c>
+      <c r="J301" t="n">
+        <v>7</v>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>gem,mage,mange,magnet,magenta</t>
+        </is>
+      </c>
+      <c r="L301">
+        <f>IF(C301="","Excluded (no APD)",IF(C301&lt;1.25,"Easy",IF(C301&lt;=2.8,"Medium",IF(C301&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>remind</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="D302" t="n">
+        <v>1</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>rookie</t>
+        </is>
+      </c>
+      <c r="I302" t="n">
+        <v>3</v>
+      </c>
+      <c r="J302" t="n">
+        <v>6</v>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>mid,dime,denim,remind</t>
+        </is>
+      </c>
+      <c r="L302">
+        <f>IF(C302="","Excluded (no APD)",IF(C302&lt;1.25,"Easy",IF(C302&lt;=2.8,"Medium",IF(C302&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>lab</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>arboreal</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>3.1024125</v>
+      </c>
+      <c r="D303" t="n">
+        <v>3</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="I303" t="n">
+        <v>3</v>
+      </c>
+      <c r="J303" t="n">
+        <v>8</v>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>lab,bale,blare,barrel,laborer,arboreal</t>
+        </is>
+      </c>
+      <c r="L303">
+        <f>IF(C303="","Excluded (no APD)",IF(C303&lt;1.25,"Easy",IF(C303&lt;=2.8,"Medium",IF(C303&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
         <v/>
       </c>
     </row>

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -508,9 +508,7 @@
           <t>Trial Version</t>
         </is>
       </c>
-      <c r="G2" s="1" t="n">
-        <v>45820</v>
-      </c>
+      <c r="G2" s="1" t="n"/>
       <c r="H2" t="n">
         <v>21</v>
       </c>
@@ -552,9 +550,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G3" s="1" t="n">
-        <v>45821</v>
-      </c>
+      <c r="G3" s="1" t="n"/>
       <c r="H3" t="n">
         <v>13</v>
       </c>
@@ -596,9 +592,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G4" s="1" t="n">
-        <v>45822</v>
-      </c>
+      <c r="G4" s="1" t="n"/>
       <c r="H4" t="n">
         <v>14</v>
       </c>
@@ -641,7 +635,7 @@
         </is>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45823</v>
+        <v>46232</v>
       </c>
       <c r="H5" t="n">
         <v>15</v>
@@ -689,9 +683,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G6" s="1" t="n">
-        <v>45824</v>
-      </c>
+      <c r="G6" s="1" t="n"/>
       <c r="H6" t="n">
         <v>16</v>
       </c>
@@ -733,9 +725,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G7" s="1" t="n">
-        <v>45825</v>
-      </c>
+      <c r="G7" s="1" t="n"/>
       <c r="H7" t="n">
         <v>17</v>
       </c>
@@ -782,9 +772,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G8" s="1" t="n">
-        <v>45826</v>
-      </c>
+      <c r="G8" s="1" t="n"/>
       <c r="H8" t="n">
         <v>18</v>
       </c>
@@ -826,9 +814,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G9" s="1" t="n">
-        <v>45827</v>
-      </c>
+      <c r="G9" s="1" t="n"/>
       <c r="H9" t="n">
         <v>189</v>
       </c>
@@ -870,9 +856,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G10" s="1" t="n">
-        <v>45828</v>
-      </c>
+      <c r="G10" s="1" t="n"/>
       <c r="H10" t="n">
         <v>20</v>
       </c>
@@ -919,9 +903,7 @@
           <t>Trial Version</t>
         </is>
       </c>
-      <c r="G11" s="1" t="n">
-        <v>45829</v>
-      </c>
+      <c r="G11" s="1" t="n"/>
       <c r="H11" t="n">
         <v>12</v>
       </c>
@@ -964,7 +946,7 @@
         </is>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45830</v>
+        <v>46230</v>
       </c>
       <c r="H12" t="n">
         <v>22</v>
@@ -1012,9 +994,7 @@
           <t>Trial Version</t>
         </is>
       </c>
-      <c r="G13" s="1" t="n">
-        <v>45831</v>
-      </c>
+      <c r="G13" s="1" t="n"/>
       <c r="H13" t="n">
         <v>23</v>
       </c>
@@ -1062,7 +1042,7 @@
         </is>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45832</v>
+        <v>46233</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -1110,9 +1090,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G15" s="1" t="n">
-        <v>45834</v>
-      </c>
+      <c r="G15" s="1" t="n"/>
       <c r="H15" t="n">
         <v>26</v>
       </c>
@@ -1154,9 +1132,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G16" s="1" t="n">
-        <v>45835</v>
-      </c>
+      <c r="G16" s="1" t="n"/>
       <c r="H16" t="n">
         <v>27</v>
       </c>
@@ -1203,9 +1179,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G17" s="1" t="n">
-        <v>45836</v>
-      </c>
+      <c r="G17" s="1" t="n"/>
       <c r="H17" t="n">
         <v>28</v>
       </c>
@@ -1247,9 +1221,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G18" s="1" t="n">
-        <v>45837</v>
-      </c>
+      <c r="G18" s="1" t="n"/>
       <c r="H18" t="n">
         <v>29</v>
       </c>
@@ -1291,9 +1263,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G19" s="1" t="n">
-        <v>45838</v>
-      </c>
+      <c r="G19" s="1" t="n"/>
       <c r="H19" t="n">
         <v>30</v>
       </c>
@@ -1335,9 +1305,7 @@
           <t>Trial Version</t>
         </is>
       </c>
-      <c r="G20" s="1" t="n">
-        <v>45839</v>
-      </c>
+      <c r="G20" s="1" t="n"/>
       <c r="H20" t="n">
         <v>31</v>
       </c>
@@ -1379,9 +1347,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G21" s="1" t="n">
-        <v>45840</v>
-      </c>
+      <c r="G21" s="1" t="n"/>
       <c r="H21" t="n">
         <v>32</v>
       </c>
@@ -1423,9 +1389,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G22" s="1" t="n">
-        <v>45841</v>
-      </c>
+      <c r="G22" s="1" t="n"/>
       <c r="H22" t="n">
         <v>33</v>
       </c>
@@ -1467,9 +1431,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G23" s="1" t="n">
-        <v>45842</v>
-      </c>
+      <c r="G23" s="1" t="n"/>
       <c r="H23" t="n">
         <v>34</v>
       </c>
@@ -1511,9 +1473,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G24" s="1" t="n">
-        <v>45843</v>
-      </c>
+      <c r="G24" s="1" t="n"/>
       <c r="H24" t="n">
         <v>35</v>
       </c>
@@ -1555,9 +1515,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G25" s="1" t="n">
-        <v>45844</v>
-      </c>
+      <c r="G25" s="1" t="n"/>
       <c r="H25" t="n">
         <v>36</v>
       </c>
@@ -1599,9 +1557,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G26" s="1" t="n">
-        <v>45845</v>
-      </c>
+      <c r="G26" s="1" t="n"/>
       <c r="H26" t="n">
         <v>37</v>
       </c>
@@ -1643,9 +1599,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G27" s="1" t="n">
-        <v>45846</v>
-      </c>
+      <c r="G27" s="1" t="n"/>
       <c r="H27" t="n">
         <v>38</v>
       </c>
@@ -1687,9 +1641,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G28" s="1" t="n">
-        <v>45847</v>
-      </c>
+      <c r="G28" s="1" t="n"/>
       <c r="H28" t="n">
         <v>39</v>
       </c>
@@ -1731,9 +1683,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G29" s="1" t="n">
-        <v>45848</v>
-      </c>
+      <c r="G29" s="1" t="n"/>
       <c r="H29" t="n">
         <v>40</v>
       </c>
@@ -1775,9 +1725,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G30" s="1" t="n">
-        <v>45849</v>
-      </c>
+      <c r="G30" s="1" t="n"/>
       <c r="H30" t="n">
         <v>41</v>
       </c>
@@ -1819,9 +1767,7 @@
           <t>Trial Version</t>
         </is>
       </c>
-      <c r="G31" s="1" t="n">
-        <v>45850</v>
-      </c>
+      <c r="G31" s="1" t="n"/>
       <c r="H31" t="n">
         <v>42</v>
       </c>
@@ -1864,7 +1810,7 @@
         </is>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45851</v>
+        <v>46242</v>
       </c>
       <c r="H32" t="n">
         <v>43</v>
@@ -1912,9 +1858,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G33" s="1" t="n">
-        <v>45852</v>
-      </c>
+      <c r="G33" s="1" t="n"/>
       <c r="H33" t="n">
         <v>44</v>
       </c>
@@ -1956,9 +1900,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G34" s="1" t="n">
-        <v>45853</v>
-      </c>
+      <c r="G34" s="1" t="n"/>
       <c r="H34" t="n">
         <v>45</v>
       </c>
@@ -2000,9 +1942,7 @@
           <t>Trial Version</t>
         </is>
       </c>
-      <c r="G35" s="1" t="n">
-        <v>45854</v>
-      </c>
+      <c r="G35" s="1" t="n"/>
       <c r="H35" t="n">
         <v>46</v>
       </c>
@@ -2044,9 +1984,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G36" s="1" t="n">
-        <v>45855</v>
-      </c>
+      <c r="G36" s="1" t="n"/>
       <c r="H36" t="n">
         <v>47</v>
       </c>
@@ -2088,9 +2026,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G37" s="1" t="n">
-        <v>45856</v>
-      </c>
+      <c r="G37" s="1" t="n"/>
       <c r="H37" t="n">
         <v>48</v>
       </c>
@@ -2132,9 +2068,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G38" s="1" t="n">
-        <v>45857</v>
-      </c>
+      <c r="G38" s="1" t="n"/>
       <c r="H38" t="n">
         <v>49</v>
       </c>
@@ -2176,9 +2110,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G39" s="1" t="n">
-        <v>45858</v>
-      </c>
+      <c r="G39" s="1" t="n"/>
       <c r="H39" t="n">
         <v>50</v>
       </c>
@@ -2220,9 +2152,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G40" s="1" t="n">
-        <v>45859</v>
-      </c>
+      <c r="G40" s="1" t="n"/>
       <c r="H40" t="n">
         <v>51</v>
       </c>
@@ -2264,9 +2194,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G41" s="1" t="n">
-        <v>45860</v>
-      </c>
+      <c r="G41" s="1" t="n"/>
       <c r="H41" t="n">
         <v>52</v>
       </c>
@@ -2308,9 +2236,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G42" s="1" t="n">
-        <v>45861</v>
-      </c>
+      <c r="G42" s="1" t="n"/>
       <c r="H42" t="n">
         <v>53</v>
       </c>
@@ -2352,9 +2278,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G43" s="1" t="n">
-        <v>45862</v>
-      </c>
+      <c r="G43" s="1" t="n"/>
       <c r="H43" t="n">
         <v>55</v>
       </c>
@@ -2396,9 +2320,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G44" s="1" t="n">
-        <v>45863</v>
-      </c>
+      <c r="G44" s="1" t="n"/>
       <c r="H44" t="n">
         <v>56</v>
       </c>
@@ -2440,9 +2362,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G45" s="1" t="n">
-        <v>45864</v>
-      </c>
+      <c r="G45" s="1" t="n"/>
       <c r="H45" t="n">
         <v>57</v>
       </c>
@@ -2484,9 +2404,7 @@
           <t>Trial Version</t>
         </is>
       </c>
-      <c r="G46" s="1" t="n">
-        <v>45865</v>
-      </c>
+      <c r="G46" s="1" t="n"/>
       <c r="H46" t="n">
         <v>58</v>
       </c>
@@ -2528,9 +2446,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G47" s="1" t="n">
-        <v>45866</v>
-      </c>
+      <c r="G47" s="1" t="n"/>
       <c r="H47" t="n">
         <v>59</v>
       </c>
@@ -2573,7 +2489,7 @@
         </is>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45867</v>
+        <v>46240</v>
       </c>
       <c r="H48" t="n">
         <v>60</v>
@@ -2621,9 +2537,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G49" s="1" t="n">
-        <v>45868</v>
-      </c>
+      <c r="G49" s="1" t="n"/>
       <c r="H49" t="n">
         <v>61</v>
       </c>
@@ -2665,9 +2579,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G50" s="1" t="n">
-        <v>45869</v>
-      </c>
+      <c r="G50" s="1" t="n"/>
       <c r="H50" t="n">
         <v>62</v>
       </c>
@@ -2710,7 +2622,7 @@
         </is>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45870</v>
+        <v>46234</v>
       </c>
       <c r="H51" t="n">
         <v>63</v>
@@ -2759,7 +2671,7 @@
         </is>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45871</v>
+        <v>46231</v>
       </c>
       <c r="H52" t="n">
         <v>64</v>
@@ -2807,9 +2719,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G53" s="1" t="n">
-        <v>45872</v>
-      </c>
+      <c r="G53" s="1" t="n"/>
       <c r="H53" t="n">
         <v>65</v>
       </c>
@@ -2851,9 +2761,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G54" s="1" t="n">
-        <v>45873</v>
-      </c>
+      <c r="G54" s="1" t="n"/>
       <c r="H54" t="n">
         <v>66</v>
       </c>
@@ -2895,9 +2803,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G55" s="1" t="n">
-        <v>45874</v>
-      </c>
+      <c r="G55" s="1" t="n"/>
       <c r="H55" t="n">
         <v>67</v>
       </c>
@@ -2939,9 +2845,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G56" s="1" t="n">
-        <v>45875</v>
-      </c>
+      <c r="G56" s="1" t="n"/>
       <c r="H56" t="n">
         <v>68</v>
       </c>
@@ -2983,9 +2887,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G57" s="1" t="n">
-        <v>45876</v>
-      </c>
+      <c r="G57" s="1" t="n"/>
       <c r="H57" t="n">
         <v>69</v>
       </c>
@@ -3027,9 +2929,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G58" s="1" t="n">
-        <v>45877</v>
-      </c>
+      <c r="G58" s="1" t="n"/>
       <c r="H58" t="n">
         <v>70</v>
       </c>
@@ -3071,9 +2971,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G59" s="1" t="n">
-        <v>45878</v>
-      </c>
+      <c r="G59" s="1" t="n"/>
       <c r="H59" t="n">
         <v>71</v>
       </c>
@@ -3115,9 +3013,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G60" s="1" t="n">
-        <v>45879</v>
-      </c>
+      <c r="G60" s="1" t="n"/>
       <c r="H60" t="n">
         <v>72</v>
       </c>
@@ -3159,9 +3055,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G61" s="1" t="n">
-        <v>45880</v>
-      </c>
+      <c r="G61" s="1" t="n"/>
       <c r="H61" t="n">
         <v>73</v>
       </c>
@@ -3204,7 +3098,7 @@
         </is>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45881</v>
+        <v>46237</v>
       </c>
       <c r="H62" t="n">
         <v>74</v>
@@ -3252,9 +3146,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G63" s="1" t="n">
-        <v>45882</v>
-      </c>
+      <c r="G63" s="1" t="n"/>
       <c r="H63" t="n">
         <v>75</v>
       </c>
@@ -3296,9 +3188,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G64" s="1" t="n">
-        <v>45883</v>
-      </c>
+      <c r="G64" s="1" t="n"/>
       <c r="H64" t="n">
         <v>76</v>
       </c>
@@ -3340,9 +3230,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G65" s="1" t="n">
-        <v>45884</v>
-      </c>
+      <c r="G65" s="1" t="n"/>
       <c r="H65" t="n">
         <v>77</v>
       </c>
@@ -3384,9 +3272,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G66" s="1" t="n">
-        <v>45885</v>
-      </c>
+      <c r="G66" s="1" t="n"/>
       <c r="H66" t="n">
         <v>78</v>
       </c>
@@ -3428,9 +3314,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G67" s="1" t="n">
-        <v>45886</v>
-      </c>
+      <c r="G67" s="1" t="n"/>
       <c r="H67" t="n">
         <v>79</v>
       </c>
@@ -3472,9 +3356,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G68" s="1" t="n">
-        <v>45887</v>
-      </c>
+      <c r="G68" s="1" t="n"/>
       <c r="H68" t="n">
         <v>80</v>
       </c>
@@ -3517,7 +3399,7 @@
         </is>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45888</v>
+        <v>46238</v>
       </c>
       <c r="H69" t="n">
         <v>81</v>
@@ -3565,9 +3447,7 @@
           <t>Trial Version</t>
         </is>
       </c>
-      <c r="G70" s="1" t="n">
-        <v>45889</v>
-      </c>
+      <c r="G70" s="1" t="n"/>
       <c r="H70" t="n">
         <v>188</v>
       </c>
@@ -3609,9 +3489,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G71" s="1" t="n">
-        <v>45890</v>
-      </c>
+      <c r="G71" s="1" t="n"/>
       <c r="H71" t="n">
         <v>83</v>
       </c>
@@ -3653,9 +3531,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G72" s="1" t="n">
-        <v>45891</v>
-      </c>
+      <c r="G72" s="1" t="n"/>
       <c r="H72" t="n">
         <v>84</v>
       </c>
@@ -3698,7 +3574,7 @@
         </is>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45892</v>
+        <v>46236</v>
       </c>
       <c r="H73" t="n">
         <v>85</v>
@@ -3746,9 +3622,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G74" s="1" t="n">
-        <v>45893</v>
-      </c>
+      <c r="G74" s="1" t="n"/>
       <c r="H74" t="n">
         <v>86</v>
       </c>
@@ -3790,9 +3664,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G75" s="1" t="n">
-        <v>45894</v>
-      </c>
+      <c r="G75" s="1" t="n"/>
       <c r="H75" t="n">
         <v>87</v>
       </c>
@@ -3834,9 +3706,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G76" s="1" t="n">
-        <v>45895</v>
-      </c>
+      <c r="G76" s="1" t="n"/>
       <c r="H76" t="n">
         <v>88</v>
       </c>
@@ -3878,9 +3748,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G77" s="1" t="n">
-        <v>45896</v>
-      </c>
+      <c r="G77" s="1" t="n"/>
       <c r="H77" t="n">
         <v>89</v>
       </c>
@@ -3922,9 +3790,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G78" s="1" t="n">
-        <v>45897</v>
-      </c>
+      <c r="G78" s="1" t="n"/>
       <c r="H78" t="n">
         <v>90</v>
       </c>
@@ -3966,9 +3832,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G79" s="1" t="n">
-        <v>45898</v>
-      </c>
+      <c r="G79" s="1" t="n"/>
       <c r="H79" t="n">
         <v>91</v>
       </c>
@@ -4010,9 +3874,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G80" s="1" t="n">
-        <v>45899</v>
-      </c>
+      <c r="G80" s="1" t="n"/>
       <c r="H80" t="n">
         <v>92</v>
       </c>
@@ -4054,9 +3916,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G81" s="1" t="n">
-        <v>45900</v>
-      </c>
+      <c r="G81" s="1" t="n"/>
       <c r="H81" t="n">
         <v>93</v>
       </c>
@@ -4098,9 +3958,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G82" s="1" t="n">
-        <v>45901</v>
-      </c>
+      <c r="G82" s="1" t="n"/>
       <c r="H82" t="n">
         <v>94</v>
       </c>
@@ -4142,9 +4000,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G83" s="1" t="n">
-        <v>45902</v>
-      </c>
+      <c r="G83" s="1" t="n"/>
       <c r="H83" t="n">
         <v>95</v>
       </c>
@@ -4186,9 +4042,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G84" s="1" t="n">
-        <v>45903</v>
-      </c>
+      <c r="G84" s="1" t="n"/>
       <c r="H84" t="n">
         <v>96</v>
       </c>
@@ -4230,9 +4084,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G85" s="1" t="n">
-        <v>45904</v>
-      </c>
+      <c r="G85" s="1" t="n"/>
       <c r="H85" t="n">
         <v>97</v>
       </c>
@@ -4274,9 +4126,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G86" s="1" t="n">
-        <v>45905</v>
-      </c>
+      <c r="G86" s="1" t="n"/>
       <c r="H86" t="n">
         <v>98</v>
       </c>
@@ -4318,9 +4168,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G87" s="1" t="n">
-        <v>45906</v>
-      </c>
+      <c r="G87" s="1" t="n"/>
       <c r="H87" t="n">
         <v>99</v>
       </c>
@@ -4362,9 +4210,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G88" s="1" t="n">
-        <v>45907</v>
-      </c>
+      <c r="G88" s="1" t="n"/>
       <c r="H88" t="n">
         <v>100</v>
       </c>
@@ -4406,9 +4252,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G89" s="1" t="n">
-        <v>45908</v>
-      </c>
+      <c r="G89" s="1" t="n"/>
       <c r="H89" t="n">
         <v>101</v>
       </c>
@@ -4450,9 +4294,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G90" s="1" t="n">
-        <v>45909</v>
-      </c>
+      <c r="G90" s="1" t="n"/>
       <c r="H90" t="n">
         <v>103</v>
       </c>
@@ -4494,9 +4336,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G91" s="1" t="n">
-        <v>45910</v>
-      </c>
+      <c r="G91" s="1" t="n"/>
       <c r="H91" t="n">
         <v>104</v>
       </c>
@@ -4538,9 +4378,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G92" s="1" t="n">
-        <v>45911</v>
-      </c>
+      <c r="G92" s="1" t="n"/>
       <c r="H92" t="n">
         <v>105</v>
       </c>
@@ -4582,9 +4420,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G93" s="1" t="n">
-        <v>45912</v>
-      </c>
+      <c r="G93" s="1" t="n"/>
       <c r="H93" t="n">
         <v>106</v>
       </c>
@@ -4626,9 +4462,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G94" s="1" t="n">
-        <v>45913</v>
-      </c>
+      <c r="G94" s="1" t="n"/>
       <c r="H94" t="n">
         <v>107</v>
       </c>
@@ -4670,9 +4504,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G95" s="1" t="n">
-        <v>45914</v>
-      </c>
+      <c r="G95" s="1" t="n"/>
       <c r="H95" t="n">
         <v>108</v>
       </c>
@@ -4714,9 +4546,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G96" s="1" t="n">
-        <v>45915</v>
-      </c>
+      <c r="G96" s="1" t="n"/>
       <c r="H96" t="n">
         <v>109</v>
       </c>
@@ -4758,9 +4588,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G97" s="1" t="n">
-        <v>45916</v>
-      </c>
+      <c r="G97" s="1" t="n"/>
       <c r="H97" t="n">
         <v>110</v>
       </c>
@@ -4802,9 +4630,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G98" s="1" t="n">
-        <v>45917</v>
-      </c>
+      <c r="G98" s="1" t="n"/>
       <c r="H98" t="n">
         <v>111</v>
       </c>
@@ -4846,9 +4672,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G99" s="1" t="n">
-        <v>45918</v>
-      </c>
+      <c r="G99" s="1" t="n"/>
       <c r="H99" t="n">
         <v>112</v>
       </c>
@@ -4890,9 +4714,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G100" s="1" t="n">
-        <v>45919</v>
-      </c>
+      <c r="G100" s="1" t="n"/>
       <c r="H100" t="n">
         <v>113</v>
       </c>
@@ -4934,9 +4756,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G101" s="1" t="n">
-        <v>45920</v>
-      </c>
+      <c r="G101" s="1" t="n"/>
       <c r="H101" t="n">
         <v>114</v>
       </c>
@@ -4978,9 +4798,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G102" s="1" t="n">
-        <v>45921</v>
-      </c>
+      <c r="G102" s="1" t="n"/>
       <c r="H102" t="n">
         <v>115</v>
       </c>
@@ -5022,9 +4840,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G103" s="1" t="n">
-        <v>45922</v>
-      </c>
+      <c r="G103" s="1" t="n"/>
       <c r="H103" t="n">
         <v>116</v>
       </c>
@@ -5066,9 +4882,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G104" s="1" t="n">
-        <v>45923</v>
-      </c>
+      <c r="G104" s="1" t="n"/>
       <c r="H104" t="n">
         <v>117</v>
       </c>
@@ -5110,9 +4924,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G105" s="1" t="n">
-        <v>45924</v>
-      </c>
+      <c r="G105" s="1" t="n"/>
       <c r="H105" t="n">
         <v>118</v>
       </c>
@@ -5154,9 +4966,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G106" s="1" t="n">
-        <v>45925</v>
-      </c>
+      <c r="G106" s="1" t="n"/>
       <c r="H106" t="n">
         <v>119</v>
       </c>
@@ -5198,9 +5008,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G107" s="1" t="n">
-        <v>45926</v>
-      </c>
+      <c r="G107" s="1" t="n"/>
       <c r="H107" t="n">
         <v>120</v>
       </c>
@@ -5243,7 +5051,7 @@
         </is>
       </c>
       <c r="G108" s="1" t="n">
-        <v>45927</v>
+        <v>46231</v>
       </c>
       <c r="H108" t="n">
         <v>122</v>
@@ -5291,9 +5099,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G109" s="1" t="n">
-        <v>45928</v>
-      </c>
+      <c r="G109" s="1" t="n"/>
       <c r="H109" t="n">
         <v>123</v>
       </c>
@@ -5335,9 +5141,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G110" s="1" t="n">
-        <v>45929</v>
-      </c>
+      <c r="G110" s="1" t="n"/>
       <c r="H110" t="n">
         <v>124</v>
       </c>
@@ -5379,9 +5183,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G111" s="1" t="n">
-        <v>45930</v>
-      </c>
+      <c r="G111" s="1" t="n"/>
       <c r="H111" t="n">
         <v>125</v>
       </c>
@@ -5423,9 +5225,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G112" s="1" t="n">
-        <v>45931</v>
-      </c>
+      <c r="G112" s="1" t="n"/>
       <c r="H112" t="n">
         <v>126</v>
       </c>
@@ -5467,9 +5267,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G113" s="1" t="n">
-        <v>45932</v>
-      </c>
+      <c r="G113" s="1" t="n"/>
       <c r="H113" t="n">
         <v>127</v>
       </c>
@@ -5511,9 +5309,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G114" s="1" t="n">
-        <v>45933</v>
-      </c>
+      <c r="G114" s="1" t="n"/>
       <c r="H114" t="n">
         <v>128</v>
       </c>
@@ -5555,9 +5351,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G115" s="1" t="n">
-        <v>45934</v>
-      </c>
+      <c r="G115" s="1" t="n"/>
       <c r="H115" t="n">
         <v>130</v>
       </c>
@@ -5599,9 +5393,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G116" s="1" t="n">
-        <v>45935</v>
-      </c>
+      <c r="G116" s="1" t="n"/>
       <c r="H116" t="n">
         <v>131</v>
       </c>
@@ -5644,7 +5436,7 @@
         </is>
       </c>
       <c r="G117" s="1" t="n">
-        <v>45936</v>
+        <v>46237</v>
       </c>
       <c r="H117" t="n">
         <v>132</v>
@@ -5692,9 +5484,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G118" s="1" t="n">
-        <v>45937</v>
-      </c>
+      <c r="G118" s="1" t="n"/>
       <c r="H118" t="n">
         <v>133</v>
       </c>
@@ -5736,9 +5526,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G119" s="1" t="n">
-        <v>45938</v>
-      </c>
+      <c r="G119" s="1" t="n"/>
       <c r="H119" t="n">
         <v>134</v>
       </c>
@@ -5780,9 +5568,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G120" s="1" t="n">
-        <v>45939</v>
-      </c>
+      <c r="G120" s="1" t="n"/>
       <c r="H120" t="n">
         <v>135</v>
       </c>
@@ -5825,7 +5611,7 @@
         </is>
       </c>
       <c r="G121" s="1" t="n">
-        <v>45940</v>
+        <v>46246</v>
       </c>
       <c r="H121" t="n">
         <v>136</v>
@@ -5874,7 +5660,7 @@
         </is>
       </c>
       <c r="G122" s="1" t="n">
-        <v>45941</v>
+        <v>46233</v>
       </c>
       <c r="H122" t="n">
         <v>137</v>
@@ -5922,9 +5708,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G123" s="1" t="n">
-        <v>45942</v>
-      </c>
+      <c r="G123" s="1" t="n"/>
       <c r="H123" t="n">
         <v>138</v>
       </c>
@@ -5972,7 +5756,7 @@
         </is>
       </c>
       <c r="G124" s="1" t="n">
-        <v>45943</v>
+        <v>46241</v>
       </c>
       <c r="H124" t="n">
         <v>139</v>
@@ -6020,9 +5804,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G125" s="1" t="n">
-        <v>45944</v>
-      </c>
+      <c r="G125" s="1" t="n"/>
       <c r="H125" t="n">
         <v>140</v>
       </c>
@@ -6064,9 +5846,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G126" s="1" t="n">
-        <v>45945</v>
-      </c>
+      <c r="G126" s="1" t="n"/>
       <c r="H126" t="n">
         <v>141</v>
       </c>
@@ -6108,9 +5888,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G127" s="1" t="n">
-        <v>45946</v>
-      </c>
+      <c r="G127" s="1" t="n"/>
       <c r="H127" t="n">
         <v>142</v>
       </c>
@@ -6152,9 +5930,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G128" s="1" t="n">
-        <v>45947</v>
-      </c>
+      <c r="G128" s="1" t="n"/>
       <c r="H128" t="n">
         <v>143</v>
       </c>
@@ -6196,9 +5972,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G129" s="1" t="n">
-        <v>45948</v>
-      </c>
+      <c r="G129" s="1" t="n"/>
       <c r="H129" t="n">
         <v>144</v>
       </c>
@@ -6240,9 +6014,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G130" s="1" t="n">
-        <v>45949</v>
-      </c>
+      <c r="G130" s="1" t="n"/>
       <c r="H130" t="n">
         <v>145</v>
       </c>
@@ -6284,9 +6056,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G131" s="1" t="n">
-        <v>45950</v>
-      </c>
+      <c r="G131" s="1" t="n"/>
       <c r="H131" t="n">
         <v>146</v>
       </c>
@@ -6328,9 +6098,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G132" s="1" t="n">
-        <v>45951</v>
-      </c>
+      <c r="G132" s="1" t="n"/>
       <c r="H132" t="n">
         <v>147</v>
       </c>
@@ -6372,9 +6140,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G133" s="1" t="n">
-        <v>45952</v>
-      </c>
+      <c r="G133" s="1" t="n"/>
       <c r="H133" t="n">
         <v>148</v>
       </c>
@@ -6416,9 +6182,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G134" s="1" t="n">
-        <v>45953</v>
-      </c>
+      <c r="G134" s="1" t="n"/>
       <c r="H134" t="n">
         <v>149</v>
       </c>
@@ -6460,9 +6224,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G135" s="1" t="n">
-        <v>45954</v>
-      </c>
+      <c r="G135" s="1" t="n"/>
       <c r="H135" t="n">
         <v>150</v>
       </c>
@@ -6504,9 +6266,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G136" s="1" t="n">
-        <v>45955</v>
-      </c>
+      <c r="G136" s="1" t="n"/>
       <c r="H136" t="n">
         <v>151</v>
       </c>
@@ -6548,9 +6308,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G137" s="1" t="n">
-        <v>45956</v>
-      </c>
+      <c r="G137" s="1" t="n"/>
       <c r="H137" t="n">
         <v>152</v>
       </c>
@@ -6592,9 +6350,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G138" s="1" t="n">
-        <v>45957</v>
-      </c>
+      <c r="G138" s="1" t="n"/>
       <c r="H138" t="n">
         <v>153</v>
       </c>
@@ -6636,9 +6392,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G139" s="1" t="n">
-        <v>45958</v>
-      </c>
+      <c r="G139" s="1" t="n"/>
       <c r="H139" t="n">
         <v>154</v>
       </c>
@@ -6680,9 +6434,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G140" s="1" t="n">
-        <v>45959</v>
-      </c>
+      <c r="G140" s="1" t="n"/>
       <c r="H140" t="n">
         <v>155</v>
       </c>
@@ -6724,9 +6476,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G141" s="1" t="n">
-        <v>45960</v>
-      </c>
+      <c r="G141" s="1" t="n"/>
       <c r="H141" t="n">
         <v>156</v>
       </c>
@@ -6768,9 +6518,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G142" s="1" t="n">
-        <v>45961</v>
-      </c>
+      <c r="G142" s="1" t="n"/>
       <c r="H142" t="n">
         <v>157</v>
       </c>
@@ -6813,7 +6561,7 @@
         </is>
       </c>
       <c r="G143" s="1" t="n">
-        <v>45962</v>
+        <v>46235</v>
       </c>
       <c r="H143" t="n">
         <v>158</v>
@@ -6861,9 +6609,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G144" s="1" t="n">
-        <v>45963</v>
-      </c>
+      <c r="G144" s="1" t="n"/>
       <c r="H144" t="n">
         <v>159</v>
       </c>
@@ -6905,9 +6651,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G145" s="1" t="n">
-        <v>45964</v>
-      </c>
+      <c r="G145" s="1" t="n"/>
       <c r="H145" t="n">
         <v>160</v>
       </c>
@@ -6950,7 +6694,7 @@
         </is>
       </c>
       <c r="G146" s="1" t="n">
-        <v>45965</v>
+        <v>46232</v>
       </c>
       <c r="H146" t="n">
         <v>161</v>
@@ -6999,7 +6743,7 @@
         </is>
       </c>
       <c r="G147" s="1" t="n">
-        <v>45966</v>
+        <v>46234</v>
       </c>
       <c r="H147" t="n">
         <v>162</v>
@@ -7047,9 +6791,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G148" s="1" t="n">
-        <v>45967</v>
-      </c>
+      <c r="G148" s="1" t="n"/>
       <c r="H148" t="n">
         <v>163</v>
       </c>
@@ -7091,9 +6833,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G149" s="1" t="n">
-        <v>45968</v>
-      </c>
+      <c r="G149" s="1" t="n"/>
       <c r="H149" t="n">
         <v>164</v>
       </c>
@@ -7136,7 +6876,7 @@
         </is>
       </c>
       <c r="G150" s="1" t="n">
-        <v>45969</v>
+        <v>46238</v>
       </c>
       <c r="H150" t="n">
         <v>165</v>
@@ -7184,9 +6924,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G151" s="1" t="n">
-        <v>45970</v>
-      </c>
+      <c r="G151" s="1" t="n"/>
       <c r="H151" t="n">
         <v>166</v>
       </c>
@@ -7228,9 +6966,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G152" s="1" t="n">
-        <v>45971</v>
-      </c>
+      <c r="G152" s="1" t="n"/>
       <c r="H152" t="n">
         <v>167</v>
       </c>
@@ -7273,7 +7009,7 @@
         </is>
       </c>
       <c r="G153" s="1" t="n">
-        <v>45972</v>
+        <v>46235</v>
       </c>
       <c r="H153" t="n">
         <v>168</v>
@@ -7321,9 +7057,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G154" s="1" t="n">
-        <v>45973</v>
-      </c>
+      <c r="G154" s="1" t="n"/>
       <c r="H154" t="n">
         <v>169</v>
       </c>
@@ -7365,9 +7099,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G155" s="1" t="n">
-        <v>45974</v>
-      </c>
+      <c r="G155" s="1" t="n"/>
       <c r="H155" t="n">
         <v>170</v>
       </c>
@@ -7409,9 +7141,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G156" s="1" t="n">
-        <v>45975</v>
-      </c>
+      <c r="G156" s="1" t="n"/>
       <c r="H156" t="n">
         <v>171</v>
       </c>
@@ -7453,9 +7183,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G157" s="1" t="n">
-        <v>45976</v>
-      </c>
+      <c r="G157" s="1" t="n"/>
       <c r="H157" t="n">
         <v>172</v>
       </c>
@@ -7497,9 +7225,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G158" s="1" t="n">
-        <v>45977</v>
-      </c>
+      <c r="G158" s="1" t="n"/>
       <c r="H158" t="n">
         <v>173</v>
       </c>
@@ -7541,9 +7267,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G159" s="1" t="n">
-        <v>45978</v>
-      </c>
+      <c r="G159" s="1" t="n"/>
       <c r="H159" t="n">
         <v>174</v>
       </c>
@@ -7585,9 +7309,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G160" s="1" t="n">
-        <v>45979</v>
-      </c>
+      <c r="G160" s="1" t="n"/>
       <c r="H160" t="n">
         <v>175</v>
       </c>
@@ -7630,7 +7352,7 @@
         </is>
       </c>
       <c r="G161" s="1" t="n">
-        <v>45980</v>
+        <v>46230</v>
       </c>
       <c r="H161" t="n">
         <v>176</v>
@@ -7678,9 +7400,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G162" s="1" t="n">
-        <v>45981</v>
-      </c>
+      <c r="G162" s="1" t="n"/>
       <c r="H162" t="n">
         <v>177</v>
       </c>
@@ -7722,9 +7442,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G163" s="1" t="n">
-        <v>45982</v>
-      </c>
+      <c r="G163" s="1" t="n"/>
       <c r="H163" t="n">
         <v>178</v>
       </c>
@@ -7766,9 +7484,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G164" s="1" t="n">
-        <v>45983</v>
-      </c>
+      <c r="G164" s="1" t="n"/>
       <c r="H164" t="n">
         <v>179</v>
       </c>
@@ -7810,9 +7526,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G165" s="1" t="n">
-        <v>45984</v>
-      </c>
+      <c r="G165" s="1" t="n"/>
       <c r="H165" t="n">
         <v>180</v>
       </c>
@@ -7854,9 +7568,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G166" s="1" t="n">
-        <v>45985</v>
-      </c>
+      <c r="G166" s="1" t="n"/>
       <c r="H166" t="n">
         <v>181</v>
       </c>
@@ -7898,9 +7610,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G167" s="1" t="n">
-        <v>45986</v>
-      </c>
+      <c r="G167" s="1" t="n"/>
       <c r="H167" t="n">
         <v>182</v>
       </c>
@@ -7947,9 +7657,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G168" s="1" t="n">
-        <v>45987</v>
-      </c>
+      <c r="G168" s="1" t="n"/>
       <c r="H168" t="n">
         <v>183</v>
       </c>
@@ -7991,9 +7699,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G169" s="1" t="n">
-        <v>45988</v>
-      </c>
+      <c r="G169" s="1" t="n"/>
       <c r="H169" t="n">
         <v>184</v>
       </c>
@@ -8035,9 +7741,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G170" s="1" t="n">
-        <v>45989</v>
-      </c>
+      <c r="G170" s="1" t="n"/>
       <c r="H170" t="n">
         <v>187</v>
       </c>
@@ -8079,9 +7783,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G171" s="1" t="n">
-        <v>45990</v>
-      </c>
+      <c r="G171" s="1" t="n"/>
       <c r="H171" t="n">
         <v>185</v>
       </c>
@@ -8123,9 +7825,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G172" s="1" t="n">
-        <v>45991</v>
-      </c>
+      <c r="G172" s="1" t="n"/>
       <c r="H172" t="n">
         <v>186</v>
       </c>
@@ -8167,9 +7867,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G173" s="1" t="n">
-        <v>45992</v>
-      </c>
+      <c r="G173" s="1" t="n"/>
       <c r="H173" t="n">
         <v>193</v>
       </c>
@@ -8216,9 +7914,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G174" s="1" t="n">
-        <v>45993</v>
-      </c>
+      <c r="G174" s="1" t="n"/>
       <c r="H174" t="n">
         <v>191</v>
       </c>
@@ -8260,9 +7956,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G175" s="1" t="n">
-        <v>45994</v>
-      </c>
+      <c r="G175" s="1" t="n"/>
       <c r="H175" t="n">
         <v>192</v>
       </c>
@@ -8304,9 +7998,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G176" s="1" t="n">
-        <v>45995</v>
-      </c>
+      <c r="G176" s="1" t="n"/>
       <c r="H176" t="n">
         <v>194</v>
       </c>
@@ -8348,9 +8040,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G177" s="1" t="n">
-        <v>45996</v>
-      </c>
+      <c r="G177" s="1" t="n"/>
       <c r="H177" t="n">
         <v>190</v>
       </c>
@@ -8392,9 +8082,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G178" s="1" t="n">
-        <v>45997</v>
-      </c>
+      <c r="G178" s="1" t="n"/>
       <c r="H178" t="n">
         <v>195</v>
       </c>
@@ -8436,9 +8124,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G179" s="1" t="n">
-        <v>45998</v>
-      </c>
+      <c r="G179" s="1" t="n"/>
       <c r="H179" t="n">
         <v>196</v>
       </c>
@@ -8480,9 +8166,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G180" s="1" t="n">
-        <v>45999</v>
-      </c>
+      <c r="G180" s="1" t="n"/>
       <c r="H180" t="n">
         <v>197</v>
       </c>
@@ -8524,9 +8208,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G181" s="1" t="n">
-        <v>46000</v>
-      </c>
+      <c r="G181" s="1" t="n"/>
       <c r="H181" t="n">
         <v>198</v>
       </c>
@@ -8569,7 +8251,7 @@
         </is>
       </c>
       <c r="G182" s="1" t="n">
-        <v>46001</v>
+        <v>46241</v>
       </c>
       <c r="H182" t="n">
         <v>199</v>
@@ -8617,9 +8299,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G183" s="1" t="n">
-        <v>46002</v>
-      </c>
+      <c r="G183" s="1" t="n"/>
       <c r="H183" t="n">
         <v>200</v>
       </c>
@@ -8661,9 +8341,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G184" s="1" t="n">
-        <v>46003</v>
-      </c>
+      <c r="G184" s="1" t="n"/>
       <c r="H184" t="n">
         <v>201</v>
       </c>
@@ -8705,9 +8383,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G185" s="1" t="n">
-        <v>46004</v>
-      </c>
+      <c r="G185" s="1" t="n"/>
       <c r="H185" t="n">
         <v>202</v>
       </c>
@@ -8749,9 +8425,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G186" s="1" t="n">
-        <v>46005</v>
-      </c>
+      <c r="G186" s="1" t="n"/>
       <c r="H186" t="n">
         <v>203</v>
       </c>
@@ -8793,9 +8467,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G187" s="1" t="n">
-        <v>46006</v>
-      </c>
+      <c r="G187" s="1" t="n"/>
       <c r="H187" t="n">
         <v>205</v>
       </c>
@@ -8837,9 +8509,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G188" s="1" t="n">
-        <v>46007</v>
-      </c>
+      <c r="G188" s="1" t="n"/>
       <c r="H188" t="n">
         <v>206</v>
       </c>
@@ -8881,9 +8551,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G189" s="1" t="n">
-        <v>46008</v>
-      </c>
+      <c r="G189" s="1" t="n"/>
       <c r="H189" t="n">
         <v>207</v>
       </c>
@@ -8925,9 +8593,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G190" s="1" t="n">
-        <v>46009</v>
-      </c>
+      <c r="G190" s="1" t="n"/>
       <c r="H190" t="n">
         <v>208</v>
       </c>
@@ -8969,9 +8635,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G191" s="1" t="n">
-        <v>46010</v>
-      </c>
+      <c r="G191" s="1" t="n"/>
       <c r="H191" t="n">
         <v>209</v>
       </c>
@@ -9013,9 +8677,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G192" s="1" t="n">
-        <v>46011</v>
-      </c>
+      <c r="G192" s="1" t="n"/>
       <c r="H192" t="n">
         <v>210</v>
       </c>
@@ -9057,9 +8719,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G193" s="1" t="n">
-        <v>46012</v>
-      </c>
+      <c r="G193" s="1" t="n"/>
       <c r="H193" t="n">
         <v>211</v>
       </c>
@@ -9101,9 +8761,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G194" s="1" t="n">
-        <v>46013</v>
-      </c>
+      <c r="G194" s="1" t="n"/>
       <c r="H194" t="n">
         <v>212</v>
       </c>
@@ -9145,9 +8803,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G195" s="1" t="n">
-        <v>46014</v>
-      </c>
+      <c r="G195" s="1" t="n"/>
       <c r="H195" t="n">
         <v>213</v>
       </c>
@@ -9189,9 +8845,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G196" s="1" t="n">
-        <v>46015</v>
-      </c>
+      <c r="G196" s="1" t="n"/>
       <c r="H196" t="n">
         <v>214</v>
       </c>
@@ -9233,9 +8887,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G197" s="1" t="n">
-        <v>46016</v>
-      </c>
+      <c r="G197" s="1" t="n"/>
       <c r="H197" t="n">
         <v>215</v>
       </c>
@@ -9277,9 +8929,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G198" s="1" t="n">
-        <v>46017</v>
-      </c>
+      <c r="G198" s="1" t="n"/>
       <c r="H198" t="n">
         <v>216</v>
       </c>
@@ -9321,9 +8971,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G199" s="1" t="n">
-        <v>46018</v>
-      </c>
+      <c r="G199" s="1" t="n"/>
       <c r="H199" t="n">
         <v>217</v>
       </c>
@@ -9365,9 +9013,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G200" s="1" t="n">
-        <v>46019</v>
-      </c>
+      <c r="G200" s="1" t="n"/>
       <c r="H200" t="n">
         <v>218</v>
       </c>
@@ -9409,9 +9055,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G201" s="1" t="n">
-        <v>46020</v>
-      </c>
+      <c r="G201" s="1" t="n"/>
       <c r="H201" t="n">
         <v>219</v>
       </c>
@@ -9453,9 +9097,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G202" s="1" t="n">
-        <v>46021</v>
-      </c>
+      <c r="G202" s="1" t="n"/>
       <c r="H202" t="n">
         <v>220</v>
       </c>
@@ -9497,9 +9139,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G203" s="1" t="n">
-        <v>46022</v>
-      </c>
+      <c r="G203" s="1" t="n"/>
       <c r="H203" t="n">
         <v>221</v>
       </c>
@@ -9541,9 +9181,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G204" s="1" t="n">
-        <v>46023</v>
-      </c>
+      <c r="G204" s="1" t="n"/>
       <c r="H204" t="n">
         <v>222</v>
       </c>
@@ -9585,9 +9223,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G205" s="1" t="n">
-        <v>46024</v>
-      </c>
+      <c r="G205" s="1" t="n"/>
       <c r="H205" t="n">
         <v>223</v>
       </c>
@@ -9629,9 +9265,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G206" s="1" t="n">
-        <v>46025</v>
-      </c>
+      <c r="G206" s="1" t="n"/>
       <c r="H206" t="n">
         <v>224</v>
       </c>
@@ -9673,9 +9307,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G207" s="1" t="n">
-        <v>46026</v>
-      </c>
+      <c r="G207" s="1" t="n"/>
       <c r="H207" t="n">
         <v>225</v>
       </c>
@@ -9717,9 +9349,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G208" s="1" t="n">
-        <v>46027</v>
-      </c>
+      <c r="G208" s="1" t="n"/>
       <c r="H208" t="n">
         <v>226</v>
       </c>
@@ -9761,9 +9391,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G209" s="1" t="n">
-        <v>46028</v>
-      </c>
+      <c r="G209" s="1" t="n"/>
       <c r="H209" t="n">
         <v>227</v>
       </c>
@@ -9805,9 +9433,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G210" s="1" t="n">
-        <v>46029</v>
-      </c>
+      <c r="G210" s="1" t="n"/>
       <c r="H210" t="n">
         <v>228</v>
       </c>
@@ -9849,9 +9475,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G211" s="1" t="n">
-        <v>46030</v>
-      </c>
+      <c r="G211" s="1" t="n"/>
       <c r="H211" t="n">
         <v>229</v>
       </c>
@@ -9893,9 +9517,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G212" s="1" t="n">
-        <v>46031</v>
-      </c>
+      <c r="G212" s="1" t="n"/>
       <c r="H212" t="n">
         <v>230</v>
       </c>
@@ -9937,9 +9559,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G213" s="1" t="n">
-        <v>46032</v>
-      </c>
+      <c r="G213" s="1" t="n"/>
       <c r="H213" t="n">
         <v>231</v>
       </c>
@@ -9981,9 +9601,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G214" s="1" t="n">
-        <v>46033</v>
-      </c>
+      <c r="G214" s="1" t="n"/>
       <c r="H214" t="n">
         <v>232</v>
       </c>
@@ -10025,9 +9643,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G215" s="1" t="n">
-        <v>46034</v>
-      </c>
+      <c r="G215" s="1" t="n"/>
       <c r="H215" t="n">
         <v>233</v>
       </c>
@@ -10069,9 +9685,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G216" s="1" t="n">
-        <v>46035</v>
-      </c>
+      <c r="G216" s="1" t="n"/>
       <c r="H216" t="n">
         <v>234</v>
       </c>
@@ -10113,9 +9727,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G217" s="1" t="n">
-        <v>46036</v>
-      </c>
+      <c r="G217" s="1" t="n"/>
       <c r="H217" t="n">
         <v>235</v>
       </c>
@@ -10157,9 +9769,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G218" s="1" t="n">
-        <v>46037</v>
-      </c>
+      <c r="G218" s="1" t="n"/>
       <c r="H218" t="n">
         <v>236</v>
       </c>
@@ -10201,9 +9811,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G219" s="1" t="n">
-        <v>46038</v>
-      </c>
+      <c r="G219" s="1" t="n"/>
       <c r="H219" t="n">
         <v>237</v>
       </c>
@@ -10245,9 +9853,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G220" s="1" t="n">
-        <v>46039</v>
-      </c>
+      <c r="G220" s="1" t="n"/>
       <c r="H220" t="n">
         <v>238</v>
       </c>
@@ -10289,9 +9895,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G221" s="1" t="n">
-        <v>46040</v>
-      </c>
+      <c r="G221" s="1" t="n"/>
       <c r="H221" t="n">
         <v>239</v>
       </c>
@@ -10333,9 +9937,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G222" s="1" t="n">
-        <v>46041</v>
-      </c>
+      <c r="G222" s="1" t="n"/>
       <c r="H222" t="n">
         <v>240</v>
       </c>
@@ -10377,9 +9979,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G223" s="1" t="n">
-        <v>46042</v>
-      </c>
+      <c r="G223" s="1" t="n"/>
       <c r="H223" t="n">
         <v>241</v>
       </c>
@@ -10421,9 +10021,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G224" s="1" t="n">
-        <v>46043</v>
-      </c>
+      <c r="G224" s="1" t="n"/>
       <c r="H224" t="n">
         <v>242</v>
       </c>
@@ -10465,9 +10063,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G225" s="1" t="n">
-        <v>46044</v>
-      </c>
+      <c r="G225" s="1" t="n"/>
       <c r="H225" t="n">
         <v>243</v>
       </c>
@@ -10509,9 +10105,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G226" s="1" t="n">
-        <v>46045</v>
-      </c>
+      <c r="G226" s="1" t="n"/>
       <c r="H226" t="n">
         <v>244</v>
       </c>
@@ -10553,9 +10147,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G227" s="1" t="n">
-        <v>46046</v>
-      </c>
+      <c r="G227" s="1" t="n"/>
       <c r="H227" t="n">
         <v>245</v>
       </c>
@@ -10597,9 +10189,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G228" s="1" t="n">
-        <v>46047</v>
-      </c>
+      <c r="G228" s="1" t="n"/>
       <c r="H228" t="n">
         <v>246</v>
       </c>
@@ -10641,9 +10231,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G229" s="1" t="n">
-        <v>46048</v>
-      </c>
+      <c r="G229" s="1" t="n"/>
       <c r="H229" t="n">
         <v>247</v>
       </c>
@@ -10685,9 +10273,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G230" s="1" t="n">
-        <v>46049</v>
-      </c>
+      <c r="G230" s="1" t="n"/>
       <c r="H230" t="n">
         <v>248</v>
       </c>
@@ -10729,9 +10315,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G231" s="1" t="n">
-        <v>46050</v>
-      </c>
+      <c r="G231" s="1" t="n"/>
       <c r="H231" t="n">
         <v>249</v>
       </c>
@@ -10773,9 +10357,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G232" s="1" t="n">
-        <v>46051</v>
-      </c>
+      <c r="G232" s="1" t="n"/>
       <c r="H232" t="n">
         <v>250</v>
       </c>
@@ -10817,9 +10399,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G233" s="1" t="n">
-        <v>46052</v>
-      </c>
+      <c r="G233" s="1" t="n"/>
       <c r="H233" t="n">
         <v>251</v>
       </c>
@@ -10861,9 +10441,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G234" s="1" t="n">
-        <v>46053</v>
-      </c>
+      <c r="G234" s="1" t="n"/>
       <c r="H234" t="n">
         <v>252</v>
       </c>
@@ -10905,9 +10483,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G235" s="1" t="n">
-        <v>46054</v>
-      </c>
+      <c r="G235" s="1" t="n"/>
       <c r="H235" t="n">
         <v>253</v>
       </c>
@@ -10949,9 +10525,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G236" s="1" t="n">
-        <v>46055</v>
-      </c>
+      <c r="G236" s="1" t="n"/>
       <c r="H236" t="n">
         <v>254</v>
       </c>
@@ -10993,9 +10567,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G237" s="1" t="n">
-        <v>46056</v>
-      </c>
+      <c r="G237" s="1" t="n"/>
       <c r="H237" t="n">
         <v>255</v>
       </c>
@@ -11037,9 +10609,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G238" s="1" t="n">
-        <v>46057</v>
-      </c>
+      <c r="G238" s="1" t="n"/>
       <c r="H238" t="n">
         <v>256</v>
       </c>
@@ -11081,9 +10651,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G239" s="1" t="n">
-        <v>46058</v>
-      </c>
+      <c r="G239" s="1" t="n"/>
       <c r="H239" t="n">
         <v>257</v>
       </c>
@@ -11125,9 +10693,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G240" s="1" t="n">
-        <v>46059</v>
-      </c>
+      <c r="G240" s="1" t="n"/>
       <c r="H240" t="n">
         <v>258</v>
       </c>
@@ -11169,9 +10735,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G241" s="1" t="n">
-        <v>46060</v>
-      </c>
+      <c r="G241" s="1" t="n"/>
       <c r="H241" t="n">
         <v>259</v>
       </c>
@@ -11213,9 +10777,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G242" s="1" t="n">
-        <v>46061</v>
-      </c>
+      <c r="G242" s="1" t="n"/>
       <c r="H242" t="n">
         <v>260</v>
       </c>
@@ -11258,7 +10820,7 @@
         </is>
       </c>
       <c r="G243" s="1" t="n">
-        <v>46062</v>
+        <v>46245</v>
       </c>
       <c r="H243" t="n">
         <v>261</v>
@@ -11306,9 +10868,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G244" s="1" t="n">
-        <v>46063</v>
-      </c>
+      <c r="G244" s="1" t="n"/>
       <c r="H244" t="n">
         <v>262</v>
       </c>
@@ -11350,9 +10910,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G245" s="1" t="n">
-        <v>46064</v>
-      </c>
+      <c r="G245" s="1" t="n"/>
       <c r="H245" t="n">
         <v>263</v>
       </c>
@@ -11394,9 +10952,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G246" s="1" t="n">
-        <v>46065</v>
-      </c>
+      <c r="G246" s="1" t="n"/>
       <c r="H246" t="n">
         <v>264</v>
       </c>
@@ -11438,9 +10994,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G247" s="1" t="n">
-        <v>46066</v>
-      </c>
+      <c r="G247" s="1" t="n"/>
       <c r="H247" t="n">
         <v>266</v>
       </c>
@@ -11482,9 +11036,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G248" s="1" t="n">
-        <v>46067</v>
-      </c>
+      <c r="G248" s="1" t="n"/>
       <c r="H248" t="n">
         <v>267</v>
       </c>
@@ -11526,9 +11078,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G249" s="1" t="n">
-        <v>46068</v>
-      </c>
+      <c r="G249" s="1" t="n"/>
       <c r="H249" t="n">
         <v>268</v>
       </c>
@@ -11570,9 +11120,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G250" s="1" t="n">
-        <v>46069</v>
-      </c>
+      <c r="G250" s="1" t="n"/>
       <c r="H250" t="n">
         <v>269</v>
       </c>
@@ -11614,9 +11162,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G251" s="1" t="n">
-        <v>46070</v>
-      </c>
+      <c r="G251" s="1" t="n"/>
       <c r="H251" t="n">
         <v>270</v>
       </c>
@@ -11658,9 +11204,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G252" s="1" t="n">
-        <v>46071</v>
-      </c>
+      <c r="G252" s="1" t="n"/>
       <c r="H252" t="n">
         <v>271</v>
       </c>
@@ -11702,9 +11246,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G253" s="1" t="n">
-        <v>46072</v>
-      </c>
+      <c r="G253" s="1" t="n"/>
       <c r="H253" t="n">
         <v>272</v>
       </c>
@@ -11746,9 +11288,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G254" s="1" t="n">
-        <v>46073</v>
-      </c>
+      <c r="G254" s="1" t="n"/>
       <c r="H254" t="n">
         <v>273</v>
       </c>
@@ -11790,9 +11330,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G255" s="1" t="n">
-        <v>46074</v>
-      </c>
+      <c r="G255" s="1" t="n"/>
       <c r="H255" t="n">
         <v>274</v>
       </c>
@@ -11834,9 +11372,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G256" s="1" t="n">
-        <v>46075</v>
-      </c>
+      <c r="G256" s="1" t="n"/>
       <c r="H256" t="n">
         <v>275</v>
       </c>
@@ -11878,9 +11414,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G257" s="1" t="n">
-        <v>46076</v>
-      </c>
+      <c r="G257" s="1" t="n"/>
       <c r="H257" t="n">
         <v>276</v>
       </c>
@@ -11922,9 +11456,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G258" s="1" t="n">
-        <v>46077</v>
-      </c>
+      <c r="G258" s="1" t="n"/>
       <c r="H258" t="n">
         <v>277</v>
       </c>
@@ -11966,9 +11498,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G259" s="1" t="n">
-        <v>46078</v>
-      </c>
+      <c r="G259" s="1" t="n"/>
       <c r="H259" t="n">
         <v>278</v>
       </c>
@@ -12010,9 +11540,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G260" s="1" t="n">
-        <v>46079</v>
-      </c>
+      <c r="G260" s="1" t="n"/>
       <c r="H260" t="n">
         <v>279</v>
       </c>
@@ -12054,9 +11582,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G261" s="1" t="n">
-        <v>46080</v>
-      </c>
+      <c r="G261" s="1" t="n"/>
       <c r="H261" t="n">
         <v>280</v>
       </c>
@@ -12098,9 +11624,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G262" s="1" t="n">
-        <v>46081</v>
-      </c>
+      <c r="G262" s="1" t="n"/>
       <c r="H262" t="n">
         <v>281</v>
       </c>
@@ -12142,9 +11666,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G263" s="1" t="n">
-        <v>46082</v>
-      </c>
+      <c r="G263" s="1" t="n"/>
       <c r="H263" t="n">
         <v>282</v>
       </c>
@@ -12186,9 +11708,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G264" s="1" t="n">
-        <v>46083</v>
-      </c>
+      <c r="G264" s="1" t="n"/>
       <c r="H264" t="n">
         <v>283</v>
       </c>
@@ -12230,9 +11750,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G265" s="1" t="n">
-        <v>46084</v>
-      </c>
+      <c r="G265" s="1" t="n"/>
       <c r="H265" t="n">
         <v>284</v>
       </c>
@@ -12274,9 +11792,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G266" s="1" t="n">
-        <v>46085</v>
-      </c>
+      <c r="G266" s="1" t="n"/>
       <c r="H266" t="n">
         <v>285</v>
       </c>
@@ -12318,9 +11834,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G267" s="1" t="n">
-        <v>46086</v>
-      </c>
+      <c r="G267" s="1" t="n"/>
       <c r="H267" t="n">
         <v>286</v>
       </c>
@@ -12362,9 +11876,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G268" s="1" t="n">
-        <v>46087</v>
-      </c>
+      <c r="G268" s="1" t="n"/>
       <c r="H268" t="n">
         <v>287</v>
       </c>
@@ -12406,6 +11918,9 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G269" s="1" t="n">
+        <v>46230</v>
+      </c>
       <c r="H269" t="n">
         <v>1</v>
       </c>
@@ -12452,6 +11967,9 @@
           <t>Trial Version</t>
         </is>
       </c>
+      <c r="G270" s="1" t="n">
+        <v>46231</v>
+      </c>
       <c r="H270" t="n">
         <v>2</v>
       </c>
@@ -12498,6 +12016,9 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G271" s="1" t="n">
+        <v>46232</v>
+      </c>
       <c r="H271" t="n">
         <v>3</v>
       </c>
@@ -12544,6 +12065,9 @@
           <t>Trial Version</t>
         </is>
       </c>
+      <c r="G272" s="1" t="n">
+        <v>46233</v>
+      </c>
       <c r="H272" t="n">
         <v>4</v>
       </c>
@@ -12590,6 +12114,9 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G273" s="1" t="n">
+        <v>46234</v>
+      </c>
       <c r="H273" t="n">
         <v>5</v>
       </c>
@@ -12636,6 +12163,9 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G274" s="1" t="n">
+        <v>46235</v>
+      </c>
       <c r="H274" t="n">
         <v>129</v>
       </c>
@@ -12682,6 +12212,9 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G275" s="1" t="n">
+        <v>46237</v>
+      </c>
       <c r="H275" t="n">
         <v>6</v>
       </c>
@@ -12728,6 +12261,9 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G276" s="1" t="n">
+        <v>46238</v>
+      </c>
       <c r="H276" t="n">
         <v>7</v>
       </c>
@@ -12907,6 +12443,9 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G280" s="1" t="n">
+        <v>46239</v>
+      </c>
       <c r="H280" t="n">
         <v>121</v>
       </c>
@@ -13109,6 +12648,9 @@
           <t>rookie</t>
         </is>
       </c>
+      <c r="G285" s="1" t="n">
+        <v>46236</v>
+      </c>
       <c r="I285" t="n">
         <v>2</v>
       </c>
@@ -13147,6 +12689,9 @@
           <t>expert</t>
         </is>
       </c>
+      <c r="G286" s="1" t="n">
+        <v>46236</v>
+      </c>
       <c r="I286" t="n">
         <v>2</v>
       </c>
@@ -13185,6 +12730,9 @@
           <t>novice</t>
         </is>
       </c>
+      <c r="G287" s="1" t="n">
+        <v>46239</v>
+      </c>
       <c r="I287" t="n">
         <v>3</v>
       </c>
@@ -13223,6 +12771,9 @@
           <t>expert</t>
         </is>
       </c>
+      <c r="G288" s="1" t="n">
+        <v>46239</v>
+      </c>
       <c r="I288" t="n">
         <v>2</v>
       </c>
@@ -13261,6 +12812,9 @@
           <t>rookie</t>
         </is>
       </c>
+      <c r="G289" s="1" t="n">
+        <v>46240</v>
+      </c>
       <c r="I289" t="n">
         <v>2</v>
       </c>
@@ -13299,6 +12853,9 @@
           <t>novice</t>
         </is>
       </c>
+      <c r="G290" s="1" t="n">
+        <v>46240</v>
+      </c>
       <c r="I290" t="n">
         <v>2</v>
       </c>
@@ -13337,6 +12894,9 @@
           <t>rookie</t>
         </is>
       </c>
+      <c r="G291" s="1" t="n">
+        <v>46241</v>
+      </c>
       <c r="I291" t="n">
         <v>2</v>
       </c>
@@ -13375,6 +12935,9 @@
           <t>rookie</t>
         </is>
       </c>
+      <c r="G292" s="1" t="n">
+        <v>46242</v>
+      </c>
       <c r="I292" t="n">
         <v>3</v>
       </c>
@@ -13413,6 +12976,9 @@
           <t>novice</t>
         </is>
       </c>
+      <c r="G293" s="1" t="n">
+        <v>46242</v>
+      </c>
       <c r="I293" t="n">
         <v>3</v>
       </c>
@@ -13451,6 +13017,9 @@
           <t>rookie</t>
         </is>
       </c>
+      <c r="G294" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="I294" t="n">
         <v>3</v>
       </c>
@@ -13489,6 +13058,9 @@
           <t>novice</t>
         </is>
       </c>
+      <c r="G295" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="I295" t="n">
         <v>3</v>
       </c>
@@ -13527,6 +13099,9 @@
           <t>expert</t>
         </is>
       </c>
+      <c r="G296" s="1" t="n">
+        <v>46243</v>
+      </c>
       <c r="I296" t="n">
         <v>4</v>
       </c>
@@ -13565,6 +13140,9 @@
           <t>rookie</t>
         </is>
       </c>
+      <c r="G297" s="1" t="n">
+        <v>46244</v>
+      </c>
       <c r="I297" t="n">
         <v>2</v>
       </c>
@@ -13603,6 +13181,9 @@
           <t>novice</t>
         </is>
       </c>
+      <c r="G298" s="1" t="n">
+        <v>46244</v>
+      </c>
       <c r="I298" t="n">
         <v>4</v>
       </c>
@@ -13641,6 +13222,9 @@
           <t>expert</t>
         </is>
       </c>
+      <c r="G299" s="1" t="n">
+        <v>46244</v>
+      </c>
       <c r="I299" t="n">
         <v>3</v>
       </c>
@@ -13679,6 +13263,9 @@
           <t>rookie</t>
         </is>
       </c>
+      <c r="G300" s="1" t="n">
+        <v>46245</v>
+      </c>
       <c r="I300" t="n">
         <v>3</v>
       </c>
@@ -13717,6 +13304,9 @@
           <t>novice</t>
         </is>
       </c>
+      <c r="G301" s="1" t="n">
+        <v>46245</v>
+      </c>
       <c r="I301" t="n">
         <v>3</v>
       </c>
@@ -13755,6 +13345,9 @@
           <t>rookie</t>
         </is>
       </c>
+      <c r="G302" s="1" t="n">
+        <v>46246</v>
+      </c>
       <c r="I302" t="n">
         <v>3</v>
       </c>
@@ -13792,6 +13385,9 @@
         <is>
           <t>expert</t>
         </is>
+      </c>
+      <c r="G303" s="1" t="n">
+        <v>46246</v>
       </c>
       <c r="I303" t="n">
         <v>3</v>

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L303"/>
+  <dimension ref="A1:L305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13058,9 +13058,7 @@
           <t>novice</t>
         </is>
       </c>
-      <c r="G295" s="1" t="n">
-        <v>46243</v>
-      </c>
+      <c r="G295" s="1" t="n"/>
       <c r="I295" t="n">
         <v>3</v>
       </c>
@@ -13181,9 +13179,7 @@
           <t>novice</t>
         </is>
       </c>
-      <c r="G298" s="1" t="n">
-        <v>46244</v>
-      </c>
+      <c r="G298" s="1" t="n"/>
       <c r="I298" t="n">
         <v>4</v>
       </c>
@@ -13223,7 +13219,7 @@
         </is>
       </c>
       <c r="G299" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="I299" t="n">
         <v>3</v>
@@ -13387,7 +13383,7 @@
         </is>
       </c>
       <c r="G303" s="1" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="I303" t="n">
         <v>3</v>
@@ -13402,6 +13398,88 @@
       </c>
       <c r="L303">
         <f>IF(C303="","Excluded (no APD)",IF(C303&lt;1.25,"Easy",IF(C303&lt;=2.8,"Medium",IF(C303&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>assuming</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="D304" t="n">
+        <v>2</v>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="G304" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="I304" t="n">
+        <v>2</v>
+      </c>
+      <c r="J304" t="n">
+        <v>8</v>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>is,sin,sing,using,musing,amusing,assuming</t>
+        </is>
+      </c>
+      <c r="L304">
+        <f>IF(C304="","Excluded (no APD)",IF(C304&lt;1.25,"Easy",IF(C304&lt;=2.8,"Medium",IF(C304&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>an</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>angelic</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>2.0925</v>
+      </c>
+      <c r="D305" t="n">
+        <v>2</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="G305" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="I305" t="n">
+        <v>2</v>
+      </c>
+      <c r="J305" t="n">
+        <v>7</v>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>an,nag,gain,acing,lacing,angelic</t>
+        </is>
+      </c>
+      <c r="L305">
+        <f>IF(C305="","Excluded (no APD)",IF(C305&lt;1.25,"Easy",IF(C305&lt;=2.8,"Medium",IF(C305&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
         <v/>
       </c>
     </row>

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -13078,7 +13078,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>sine</t>
+          <t>mines</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13101,14 +13101,14 @@
         <v>46243</v>
       </c>
       <c r="I296" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J296" t="n">
         <v>10</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>sine,mines,inseam,inmates,semantic,miscreant,cremations</t>
+          <t>mines,inseam,inmates,semantic,miscreant,cremations</t>
         </is>
       </c>
       <c r="L296">

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L305"/>
+  <dimension ref="A1:L317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.319383</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -814,7 +814,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G9" s="1" t="n"/>
+      <c r="G9" s="1" t="n">
+        <v>46251</v>
+      </c>
       <c r="H9" t="n">
         <v>189</v>
       </c>
@@ -823,6 +825,11 @@
       </c>
       <c r="J9" t="n">
         <v>8</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>core,cover,vector,convert,contrive</t>
+        </is>
       </c>
       <c r="L9">
         <f>IF(C9="","Excluded (no APD)",IF(C9&lt;1.25,"Easy",IF(C9&lt;=2.8,"Medium",IF(C9&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
@@ -7684,7 +7691,7 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="D169" t="n">
         <v>4</v>
@@ -7699,7 +7706,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G169" s="1" t="n"/>
+      <c r="G169" s="1" t="n">
+        <v>46250</v>
+      </c>
       <c r="H169" t="n">
         <v>184</v>
       </c>
@@ -7708,6 +7717,11 @@
       </c>
       <c r="J169" t="n">
         <v>11</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>inter,retina,retains,terrains,serration,rainforest,refractions</t>
+        </is>
       </c>
       <c r="L169">
         <f>IF(C170="","Excluded (no APD)",IF(C170&lt;1.25,"Easy",IF(C170&lt;=2.8,"Medium",IF(C170&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
@@ -7810,7 +7824,7 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="D172" t="n">
         <v>3</v>
@@ -7825,7 +7839,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G172" s="1" t="n"/>
+      <c r="G172" s="1" t="n">
+        <v>46252</v>
+      </c>
       <c r="H172" t="n">
         <v>186</v>
       </c>
@@ -7834,6 +7850,11 @@
       </c>
       <c r="J172" t="n">
         <v>9</v>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>tab,bats,boast,batons,obtains,botanist,obstinate</t>
+        </is>
       </c>
       <c r="L172">
         <f>IF(C173="","Excluded (no APD)",IF(C173&lt;1.25,"Easy",IF(C173&lt;=2.8,"Medium",IF(C173&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
@@ -8746,7 +8767,7 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>999.0018999999995</v>
+        <v>2</v>
       </c>
       <c r="D194" t="n">
         <v>999</v>
@@ -8761,7 +8782,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G194" s="1" t="n"/>
+      <c r="G194" s="1" t="n">
+        <v>46249</v>
+      </c>
       <c r="H194" t="n">
         <v>212</v>
       </c>
@@ -8770,6 +8793,11 @@
       </c>
       <c r="J194" t="n">
         <v>9</v>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>ailing,tailing,vigilant,violating</t>
+        </is>
       </c>
       <c r="L194">
         <f>IF(C195="","Excluded (no APD)",IF(C195&lt;1.25,"Easy",IF(C195&lt;=2.8,"Medium",IF(C195&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
@@ -8830,7 +8858,7 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>999.0020999999995</v>
+        <v>2</v>
       </c>
       <c r="D196" t="n">
         <v>999</v>
@@ -8845,7 +8873,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G196" s="1" t="n"/>
+      <c r="G196" s="1" t="n">
+        <v>46250</v>
+      </c>
       <c r="H196" t="n">
         <v>214</v>
       </c>
@@ -8854,6 +8884,11 @@
       </c>
       <c r="J196" t="n">
         <v>8</v>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>sip,tips,spite,sprite,respite,prestige</t>
+        </is>
       </c>
       <c r="L196">
         <f>IF(C197="","Excluded (no APD)",IF(C197&lt;1.25,"Easy",IF(C197&lt;=2.8,"Medium",IF(C197&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
@@ -9292,7 +9327,7 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>999.0031999999992</v>
+        <v>2</v>
       </c>
       <c r="D207" t="n">
         <v>999</v>
@@ -9307,7 +9342,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G207" s="1" t="n"/>
+      <c r="G207" s="1" t="n">
+        <v>46247</v>
+      </c>
       <c r="H207" t="n">
         <v>225</v>
       </c>
@@ -9316,6 +9353,11 @@
       </c>
       <c r="J207" t="n">
         <v>8</v>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>set,rest,terms,muster,mutters,trumpets</t>
+        </is>
       </c>
       <c r="L207">
         <f>IF(C208="","Excluded (no APD)",IF(C208&lt;1.25,"Easy",IF(C208&lt;=2.8,"Medium",IF(C208&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
@@ -13480,6 +13522,498 @@
       </c>
       <c r="L305">
         <f>IF(C305="","Excluded (no APD)",IF(C305&lt;1.25,"Easy",IF(C305&lt;=2.8,"Medium",IF(C305&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>cab</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>scarab</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D306" t="n">
+        <v>1</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>rookie</t>
+        </is>
+      </c>
+      <c r="G306" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="I306" t="n">
+        <v>3</v>
+      </c>
+      <c r="J306" t="n">
+        <v>6</v>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>cab,crab,crabs,scarab</t>
+        </is>
+      </c>
+      <c r="L306">
+        <f>IF(C306="","Excluded (no APD)",IF(C306&lt;1.25,"Easy",IF(C306&lt;=2.8,"Medium",IF(C306&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>vine</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>traveling</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D307" t="n">
+        <v>3</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="G307" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="I307" t="n">
+        <v>4</v>
+      </c>
+      <c r="J307" t="n">
+        <v>9</v>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>vine,naive,native,vintage,valeting,traveling</t>
+        </is>
+      </c>
+      <c r="L307">
+        <f>IF(C307="","Excluded (no APD)",IF(C307&lt;1.25,"Easy",IF(C307&lt;=2.8,"Medium",IF(C307&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>elf</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D308" t="n">
+        <v>1</v>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>rookie</t>
+        </is>
+      </c>
+      <c r="G308" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="I308" t="n">
+        <v>3</v>
+      </c>
+      <c r="J308" t="n">
+        <v>6</v>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>elf,file,filet,filter</t>
+        </is>
+      </c>
+      <c r="L308">
+        <f>IF(C308="","Excluded (no APD)",IF(C308&lt;1.25,"Easy",IF(C308&lt;=2.8,"Medium",IF(C308&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>tide</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>dentistry</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>2</v>
+      </c>
+      <c r="D309" t="n">
+        <v>2</v>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="G309" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="I309" t="n">
+        <v>4</v>
+      </c>
+      <c r="J309" t="n">
+        <v>9</v>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>tide,tried,tinder,trident,tridents,dentistry</t>
+        </is>
+      </c>
+      <c r="L309">
+        <f>IF(C309="","Excluded (no APD)",IF(C309&lt;1.25,"Easy",IF(C309&lt;=2.8,"Medium",IF(C309&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>intent</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>intestine</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D310" t="n">
+        <v>3</v>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="G310" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="I310" t="n">
+        <v>6</v>
+      </c>
+      <c r="J310" t="n">
+        <v>9</v>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>intent,intents,sentient,intestine</t>
+        </is>
+      </c>
+      <c r="L310">
+        <f>IF(C310="","Excluded (no APD)",IF(C310&lt;1.25,"Easy",IF(C310&lt;=2.8,"Medium",IF(C310&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>cap</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>camper</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D311" t="n">
+        <v>1</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>rookie</t>
+        </is>
+      </c>
+      <c r="G311" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="I311" t="n">
+        <v>3</v>
+      </c>
+      <c r="J311" t="n">
+        <v>6</v>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>cap,pace,recap,camper</t>
+        </is>
+      </c>
+      <c r="L311">
+        <f>IF(C311="","Excluded (no APD)",IF(C311&lt;1.25,"Easy",IF(C311&lt;=2.8,"Medium",IF(C311&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>destruction</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D312" t="n">
+        <v>3</v>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="G312" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="I312" t="n">
+        <v>4</v>
+      </c>
+      <c r="J312" t="n">
+        <v>11</v>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>unit,tunic,induct,conduit,discount,seduction,reductions,destruction</t>
+        </is>
+      </c>
+      <c r="L312">
+        <f>IF(C312="","Excluded (no APD)",IF(C312&lt;1.25,"Easy",IF(C312&lt;=2.8,"Medium",IF(C312&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>if</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>finger</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D313" t="n">
+        <v>1</v>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>rookie</t>
+        </is>
+      </c>
+      <c r="G313" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="I313" t="n">
+        <v>2</v>
+      </c>
+      <c r="J313" t="n">
+        <v>6</v>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>if,fin,fine,finer,finger</t>
+        </is>
+      </c>
+      <c r="L313">
+        <f>IF(C313="","Excluded (no APD)",IF(C313&lt;1.25,"Easy",IF(C313&lt;=2.8,"Medium",IF(C313&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>casket</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D314" t="n">
+        <v>1</v>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>rookie</t>
+        </is>
+      </c>
+      <c r="G314" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="I314" t="n">
+        <v>3</v>
+      </c>
+      <c r="J314" t="n">
+        <v>6</v>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>ask,sake,steak,casket</t>
+        </is>
+      </c>
+      <c r="L314">
+        <f>IF(C314="","Excluded (no APD)",IF(C314&lt;1.25,"Easy",IF(C314&lt;=2.8,"Medium",IF(C314&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>volatile</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D315" t="n">
+        <v>3</v>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="G315" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="I315" t="n">
+        <v>4</v>
+      </c>
+      <c r="J315" t="n">
+        <v>8</v>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>love,olive,violet,violate,volatile</t>
+        </is>
+      </c>
+      <c r="L315">
+        <f>IF(C315="","Excluded (no APD)",IF(C315&lt;1.25,"Easy",IF(C315&lt;=2.8,"Medium",IF(C315&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>heard</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D316" t="n">
+        <v>1</v>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>rookie</t>
+        </is>
+      </c>
+      <c r="G316" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="I316" t="n">
+        <v>2</v>
+      </c>
+      <c r="J316" t="n">
+        <v>5</v>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>ad,had,head,heard</t>
+        </is>
+      </c>
+      <c r="L316">
+        <f>IF(C316="","Excluded (no APD)",IF(C316&lt;1.25,"Easy",IF(C316&lt;=2.8,"Medium",IF(C316&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>due</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>unbathed</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>2</v>
+      </c>
+      <c r="D317" t="n">
+        <v>2</v>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="G317" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="I317" t="n">
+        <v>3</v>
+      </c>
+      <c r="J317" t="n">
+        <v>8</v>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>due,dune,tuned,hunted,haunted,unbathed</t>
+        </is>
+      </c>
+      <c r="L317">
+        <f>IF(C317="","Excluded (no APD)",IF(C317&lt;1.25,"Easy",IF(C317&lt;=2.8,"Medium",IF(C317&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
         <v/>
       </c>
     </row>

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L317"/>
+  <dimension ref="A1:L326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14017,6 +14017,375 @@
         <v/>
       </c>
     </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>track</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D318" t="n">
+        <v>1</v>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>rookie</t>
+        </is>
+      </c>
+      <c r="G318" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="I318" t="n">
+        <v>2</v>
+      </c>
+      <c r="J318" t="n">
+        <v>5</v>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>at,cat,cart,track</t>
+        </is>
+      </c>
+      <c r="L318">
+        <f>IF(C318="","Excluded (no APD)",IF(C318&lt;1.25,"Easy",IF(C318&lt;=2.8,"Medium",IF(C318&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>garlics</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>2</v>
+      </c>
+      <c r="D319" t="n">
+        <v>2</v>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="G319" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="I319" t="n">
+        <v>2</v>
+      </c>
+      <c r="J319" t="n">
+        <v>7</v>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>is,sir,airs,rails,grails,garlics</t>
+        </is>
+      </c>
+      <c r="L319">
+        <f>IF(C319="","Excluded (no APD)",IF(C319&lt;1.25,"Easy",IF(C319&lt;=2.8,"Medium",IF(C319&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>terrain</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D320" t="n">
+        <v>3</v>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="G320" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="I320" t="n">
+        <v>3</v>
+      </c>
+      <c r="J320" t="n">
+        <v>7</v>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>air,rain,train,retina,terrain</t>
+        </is>
+      </c>
+      <c r="L320">
+        <f>IF(C320="","Excluded (no APD)",IF(C320&lt;1.25,"Easy",IF(C320&lt;=2.8,"Medium",IF(C320&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>as</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D321" t="n">
+        <v>1</v>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>rookie</t>
+        </is>
+      </c>
+      <c r="G321" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="I321" t="n">
+        <v>2</v>
+      </c>
+      <c r="J321" t="n">
+        <v>5</v>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>as,say,easy,years</t>
+        </is>
+      </c>
+      <c r="L321">
+        <f>IF(C321="","Excluded (no APD)",IF(C321&lt;1.25,"Easy",IF(C321&lt;=2.8,"Medium",IF(C321&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>dime</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>2</v>
+      </c>
+      <c r="D322" t="n">
+        <v>2</v>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="G322" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="I322" t="n">
+        <v>4</v>
+      </c>
+      <c r="J322" t="n">
+        <v>7</v>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>dime,mimed,medium,dummies</t>
+        </is>
+      </c>
+      <c r="L322">
+        <f>IF(C322="","Excluded (no APD)",IF(C322&lt;1.25,"Easy",IF(C322&lt;=2.8,"Medium",IF(C322&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>thrashed</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D323" t="n">
+        <v>3</v>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="G323" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="I323" t="n">
+        <v>2</v>
+      </c>
+      <c r="J323" t="n">
+        <v>8</v>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>ad,had,head,heard,shared,trashed,thrashed</t>
+        </is>
+      </c>
+      <c r="L323">
+        <f>IF(C323="","Excluded (no APD)",IF(C323&lt;1.25,"Easy",IF(C323&lt;=2.8,"Medium",IF(C323&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>clone</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D324" t="n">
+        <v>1</v>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>rookie</t>
+        </is>
+      </c>
+      <c r="G324" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="I324" t="n">
+        <v>2</v>
+      </c>
+      <c r="J324" t="n">
+        <v>5</v>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>on,one,cone,clone</t>
+        </is>
+      </c>
+      <c r="L324">
+        <f>IF(C324="","Excluded (no APD)",IF(C324&lt;1.25,"Easy",IF(C324&lt;=2.8,"Medium",IF(C324&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>cut</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>curate</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>2</v>
+      </c>
+      <c r="D325" t="n">
+        <v>2</v>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="G325" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="I325" t="n">
+        <v>3</v>
+      </c>
+      <c r="J325" t="n">
+        <v>6</v>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>cut,cute,acute,curate</t>
+        </is>
+      </c>
+      <c r="L325">
+        <f>IF(C325="","Excluded (no APD)",IF(C325&lt;1.25,"Easy",IF(C325&lt;=2.8,"Medium",IF(C325&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>son</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>jointers</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D326" t="n">
+        <v>3</v>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="G326" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="I326" t="n">
+        <v>3</v>
+      </c>
+      <c r="J326" t="n">
+        <v>8</v>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>son,nose,noise,nosier,rejoins,jointers</t>
+        </is>
+      </c>
+      <c r="L326">
+        <f>IF(C326="","Excluded (no APD)",IF(C326&lt;1.25,"Easy",IF(C326&lt;=2.8,"Medium",IF(C326&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -7720,7 +7720,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>inter,retina,retains,terrains,serration,rainforest,refractions</t>
+          <t>inter,cretin,noticer,reaction,fornicate,refraction,refractions</t>
         </is>
       </c>
       <c r="L169">

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L326"/>
+  <dimension ref="A1:L338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>ad,had,head,heard,shared,trashed,thrashed</t>
+          <t>ad,had,hard,heard,shared,trashed,thrashed</t>
         </is>
       </c>
       <c r="L323">
@@ -14384,6 +14384,306 @@
       <c r="L326">
         <f>IF(C326="","Excluded (no APD)",IF(C326&lt;1.25,"Easy",IF(C326&lt;=2.8,"Medium",IF(C326&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
         <v/>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>barked</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>1</v>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>bar,bear,bread,barked</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>rot</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>smoother</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>rot,sort,short,others,mothers,smoother</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>me</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>medication</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>me,men,mine,anime,median,mediant,dominate,mediation,medication</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>1</v>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>at,tan,tank,thank</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>sate</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>masteries</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>2</v>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>sate,stare,stream,steamer,steamers,masteries</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>lee</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>reclaimed</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>3</v>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>lee,leer,elder,dealer,emerald,remedial,reclaimed</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>widen</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>1</v>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>in,win,wind,widen</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>ear</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>lateral</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>ear,real,alter,taller,lateral</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>flustering</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>is,sin,sing,sting,string,rusting,rustling,resulting,flustering</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>he</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>heart</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>1</v>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>he,the,heat,heart</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>as</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>sneaky</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>as,sea,sake,snake,sneaky</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>ma</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>inflame</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>ma,man,main,anime,famine,inflame</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L338"/>
+  <dimension ref="A1:L368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14686,6 +14686,756 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>by</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>bossy</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>1</v>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>by,boy,boys,bossy</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>lid</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>bridle</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>lid,deli,riled,bridle</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>unctions</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>unctions,contusion,continuous</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>rid</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>driven</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>1</v>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>rid,ride,diver,driven</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>bristle</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>best,bites,tribes,bristle</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>wig</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>withering</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>wig,wing,wring,wiring,writing,writhing,withering</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>floor</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>1</v>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>of,for,roof,floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>oat</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>flotsam</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>oat,atom,moats,almost,flotsam</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>tire</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>ministries</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>tire,inter,tinier,mintier,minister,ministers,ministries</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>fin</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>1</v>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>fin,find,fined,friend</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>collage</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>all,call,local,locale,collage</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>ruminates</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>sun,stun,tunes,tuners,saunter,urinates,ruminates</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>ski</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>sticky</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>1</v>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>ski,sick,stick,sticky</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>wine</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>swindler</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>wine,swine,widens,rewinds,swindler</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>rise</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>compilers</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>3</v>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>rise,pries,primes,promise,implores,compilers</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>crown</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>1</v>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>on,now,worn,crown</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>me</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>monkey</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>me,men,omen,money,monkey</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>girl</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>ridgeline</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>girl,liger,linger,reeling,lingered,ridgeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>go</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>lodge</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>1</v>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>go,dog,gold,lodge</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>ye</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>pretty</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>ye,yet,type,petty,pretty</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>traveling</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>age,gear,anger,regain,tangier,averting,traveling</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>blink</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>1</v>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>in,ink,link,blink</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>per</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>scooper</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>per,rope,spore,corpse,scooper</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>pyramid</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>air,raid,dairy,myriad,pyramid</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>an</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>1</v>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>an,ban,bank,blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>maul</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>lumbar</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>maul,album,lumbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>nostalgic</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>tag,gait,giant,acting,casting,coasting,nostalgic</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>fishy</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>1</v>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>is,his,fish,fishy</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>mans</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>normals</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>mans,moans,salmon,normals</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>sane</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>readiness</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>3</v>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>sane,nears,snared,sandier,sardines,readiness</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L368"/>
+  <dimension ref="A1:L374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14764,12 +14764,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>rid</t>
+          <t>fin</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>driven</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -14782,23 +14782,23 @@
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>rid,ride,diver,driven</t>
+          <t>fin,find,fined,friend</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>best</t>
+          <t>all</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>bristle</t>
+          <t>collage</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="G343" t="inlineStr">
         <is>
@@ -14807,23 +14807,23 @@
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>best,bites,tribes,bristle</t>
+          <t>all,call,local,locale,collage</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>wig</t>
+          <t>an</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>withering</t>
+          <t>bargeman</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="G344" t="inlineStr">
         <is>
@@ -14832,19 +14832,19 @@
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>wig,wing,wring,wiring,writing,writhing,withering</t>
+          <t>an,ran,rang,anger,manger,manager,bargeman</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>of</t>
+          <t>ski</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>floor</t>
+          <t>sticky</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -14857,23 +14857,23 @@
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>of,for,roof,floor</t>
+          <t>ski,sick,stick,sticky</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>oat</t>
+          <t>wine</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>flotsam</t>
+          <t>swindler</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="G346" t="inlineStr">
         <is>
@@ -14882,23 +14882,23 @@
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>oat,atom,moats,almost,flotsam</t>
+          <t>wine,swine,widens,rewinds,swindler</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>tire</t>
+          <t>rise</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>ministries</t>
+          <t>compilers</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="G347" t="inlineStr">
         <is>
@@ -14907,19 +14907,19 @@
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>tire,inter,tinier,mintier,minister,ministers,ministries</t>
+          <t>rise,pries,primes,promise,implores,compilers</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>fin</t>
+          <t>rid</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>friend</t>
+          <t>driven</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -14932,23 +14932,23 @@
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>fin,find,fined,friend</t>
+          <t>rid,ride,diver,driven</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>best</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>collage</t>
+          <t>bristle</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="G349" t="inlineStr">
         <is>
@@ -14957,23 +14957,23 @@
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>all,call,local,locale,collage</t>
+          <t>best,bites,tribes,bristle</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>wig</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>ruminates</t>
+          <t>withering</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="G350" t="inlineStr">
         <is>
@@ -14982,19 +14982,19 @@
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>sun,stun,tunes,tuners,saunter,urinates,ruminates</t>
+          <t>wig,wing,wring,wiring,writing,writhing,withering</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>ski</t>
+          <t>of</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>sticky</t>
+          <t>floor</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -15007,23 +15007,23 @@
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>ski,sick,stick,sticky</t>
+          <t>of,for,roof,floor</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>wine</t>
+          <t>oat</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>swindler</t>
+          <t>flotsam</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="G352" t="inlineStr">
         <is>
@@ -15032,23 +15032,23 @@
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>wine,swine,widens,rewinds,swindler</t>
+          <t>oat,atom,moats,almost,flotsam</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>tire</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>compilers</t>
+          <t>ministries</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G353" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>rise,pries,primes,promise,implores,compilers</t>
+          <t>tire,inter,tinier,mintier,minister,ministers,ministries</t>
         </is>
       </c>
     </row>
@@ -15289,12 +15289,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>an</t>
+          <t>by</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>tabby</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -15307,23 +15307,23 @@
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>an,ban,bank,blank</t>
+          <t>by,bay,baby,tabby</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>maul</t>
+          <t>lie</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>lumbar</t>
+          <t>literary</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="G364" t="inlineStr">
         <is>
@@ -15332,19 +15332,19 @@
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>maul,album,lumbar</t>
+          <t>lie,rile,relit,retail,trailer,literary</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>tag</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>nostalgic</t>
+          <t>ruminates</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -15357,19 +15357,19 @@
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>tag,gait,giant,acting,casting,coasting,nostalgic</t>
+          <t>sun,stun,tunes,tuners,saunter,urinates,ruminates</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>at</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>fishy</t>
+          <t>chant</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -15382,23 +15382,23 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>is,his,fish,fishy</t>
+          <t>at,cat,chat,chant</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>mans</t>
+          <t>new</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>normals</t>
+          <t>renown</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="G367" t="inlineStr">
         <is>
@@ -15407,30 +15407,180 @@
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>mans,moans,salmon,normals</t>
+          <t>new,wren,owner,renown</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
+          <t>rant</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>decorating</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>rant,train,rating,ingrate,treading,redacting,decorating</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>an</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>1</v>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>an,ban,bank,blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>maul</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>lumbar</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>maul,album,lumbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>nostalgic</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>tag,gait,giant,acting,casting,coasting,nostalgic</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>fishy</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>1</v>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>is,his,fish,fishy</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>mans</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>normals</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>mans,moans,salmon,normals</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
           <t>sane</t>
         </is>
       </c>
-      <c r="B368" t="inlineStr">
+      <c r="B374" t="inlineStr">
         <is>
           <t>readiness</t>
         </is>
       </c>
-      <c r="C368" t="n">
+      <c r="C374" t="n">
         <v>3</v>
       </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="K368" t="inlineStr">
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
         <is>
           <t>sane,nears,snared,sandier,sardines,readiness</t>
         </is>

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L374"/>
+  <dimension ref="A1:L326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>2.319383</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -814,9 +814,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G9" s="1" t="n">
-        <v>46251</v>
-      </c>
+      <c r="G9" s="1" t="n"/>
       <c r="H9" t="n">
         <v>189</v>
       </c>
@@ -825,11 +823,6 @@
       </c>
       <c r="J9" t="n">
         <v>8</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>core,cover,vector,convert,contrive</t>
-        </is>
       </c>
       <c r="L9">
         <f>IF(C9="","Excluded (no APD)",IF(C9&lt;1.25,"Easy",IF(C9&lt;=2.8,"Medium",IF(C9&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
@@ -7691,7 +7684,7 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="D169" t="n">
         <v>4</v>
@@ -7706,9 +7699,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G169" s="1" t="n">
-        <v>46250</v>
-      </c>
+      <c r="G169" s="1" t="n"/>
       <c r="H169" t="n">
         <v>184</v>
       </c>
@@ -7717,11 +7708,6 @@
       </c>
       <c r="J169" t="n">
         <v>11</v>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>inter,cretin,noticer,reaction,fornicate,refraction,refractions</t>
-        </is>
       </c>
       <c r="L169">
         <f>IF(C170="","Excluded (no APD)",IF(C170&lt;1.25,"Easy",IF(C170&lt;=2.8,"Medium",IF(C170&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
@@ -7824,7 +7810,7 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="D172" t="n">
         <v>3</v>
@@ -7839,9 +7825,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G172" s="1" t="n">
-        <v>46252</v>
-      </c>
+      <c r="G172" s="1" t="n"/>
       <c r="H172" t="n">
         <v>186</v>
       </c>
@@ -7850,11 +7834,6 @@
       </c>
       <c r="J172" t="n">
         <v>9</v>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>tab,bats,boast,batons,obtains,botanist,obstinate</t>
-        </is>
       </c>
       <c r="L172">
         <f>IF(C173="","Excluded (no APD)",IF(C173&lt;1.25,"Easy",IF(C173&lt;=2.8,"Medium",IF(C173&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
@@ -8767,7 +8746,7 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>2</v>
+        <v>999.0018999999995</v>
       </c>
       <c r="D194" t="n">
         <v>999</v>
@@ -8782,9 +8761,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G194" s="1" t="n">
-        <v>46249</v>
-      </c>
+      <c r="G194" s="1" t="n"/>
       <c r="H194" t="n">
         <v>212</v>
       </c>
@@ -8793,11 +8770,6 @@
       </c>
       <c r="J194" t="n">
         <v>9</v>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>ailing,tailing,vigilant,violating</t>
-        </is>
       </c>
       <c r="L194">
         <f>IF(C195="","Excluded (no APD)",IF(C195&lt;1.25,"Easy",IF(C195&lt;=2.8,"Medium",IF(C195&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
@@ -8858,7 +8830,7 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>2</v>
+        <v>999.0020999999995</v>
       </c>
       <c r="D196" t="n">
         <v>999</v>
@@ -8873,9 +8845,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G196" s="1" t="n">
-        <v>46250</v>
-      </c>
+      <c r="G196" s="1" t="n"/>
       <c r="H196" t="n">
         <v>214</v>
       </c>
@@ -8884,11 +8854,6 @@
       </c>
       <c r="J196" t="n">
         <v>8</v>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>sip,tips,spite,sprite,respite,prestige</t>
-        </is>
       </c>
       <c r="L196">
         <f>IF(C197="","Excluded (no APD)",IF(C197&lt;1.25,"Easy",IF(C197&lt;=2.8,"Medium",IF(C197&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
@@ -9327,7 +9292,7 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>2</v>
+        <v>999.0031999999992</v>
       </c>
       <c r="D207" t="n">
         <v>999</v>
@@ -9342,9 +9307,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G207" s="1" t="n">
-        <v>46247</v>
-      </c>
+      <c r="G207" s="1" t="n"/>
       <c r="H207" t="n">
         <v>225</v>
       </c>
@@ -9353,11 +9316,6 @@
       </c>
       <c r="J207" t="n">
         <v>8</v>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>set,rest,terms,muster,mutters,trumpets</t>
-        </is>
       </c>
       <c r="L207">
         <f>IF(C208="","Excluded (no APD)",IF(C208&lt;1.25,"Easy",IF(C208&lt;=2.8,"Medium",IF(C208&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
@@ -13528,37 +13486,42 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>cab</t>
+          <t>if</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>scarab</t>
+          <t>fixer</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="D306" t="n">
         <v>1</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>rookie</t>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G306" s="1" t="n">
-        <v>46247</v>
+        <v>46272</v>
       </c>
       <c r="I306" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J306" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>cab,crab,crabs,scarab</t>
+          <t>if,fir,fire,fixer</t>
         </is>
       </c>
       <c r="L306">
@@ -13569,37 +13532,42 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>vine</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>traveling</t>
+          <t>builder</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="D307" t="n">
+        <v>2</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G307" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="I307" t="n">
         <v>3</v>
       </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>expert</t>
-        </is>
-      </c>
-      <c r="G307" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="I307" t="n">
-        <v>4</v>
-      </c>
       <c r="J307" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>vine,naive,native,vintage,valeting,traveling</t>
+          <t>bid,bird,bride,bridle,builder</t>
         </is>
       </c>
       <c r="L307">
@@ -13610,37 +13578,42 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>elf</t>
+          <t>gee</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>filter</t>
+          <t>designer</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="D308" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>rookie</t>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G308" s="1" t="n">
-        <v>46248</v>
+        <v>46272</v>
       </c>
       <c r="I308" t="n">
         <v>3</v>
       </c>
       <c r="J308" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>elf,file,filet,filter</t>
+          <t>gee,gene,green,gender,genders,designer</t>
         </is>
       </c>
       <c r="L308">
@@ -13651,37 +13624,42 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>tide</t>
+          <t>at</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>dentistry</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="D309" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>novice</t>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G309" s="1" t="n">
-        <v>46248</v>
+        <v>46273</v>
       </c>
       <c r="I309" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J309" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>tide,tried,tinder,trident,tridents,dentistry</t>
+          <t>at,tar,tear,water</t>
         </is>
       </c>
       <c r="L309">
@@ -13692,37 +13670,42 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>intent</t>
+          <t>ale</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>intestine</t>
+          <t>clapped</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="D310" t="n">
+        <v>2</v>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G310" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="I310" t="n">
         <v>3</v>
       </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>expert</t>
-        </is>
-      </c>
-      <c r="G310" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="I310" t="n">
-        <v>6</v>
-      </c>
       <c r="J310" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>intent,intents,sentient,intestine</t>
+          <t>ale,pale,apple,lapped,clapped</t>
         </is>
       </c>
       <c r="L310">
@@ -13733,37 +13716,42 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>cap</t>
+          <t>at</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>camper</t>
+          <t>tractor</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="D311" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>rookie</t>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G311" s="1" t="n">
-        <v>46249</v>
+        <v>46273</v>
       </c>
       <c r="I311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J311" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>cap,pace,recap,camper</t>
+          <t>at,rat,cart,actor,carrot,tractor</t>
         </is>
       </c>
       <c r="L311">
@@ -13774,37 +13762,42 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>am</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>destruction</t>
+          <t>tamed</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="D312" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>expert</t>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G312" s="1" t="n">
-        <v>46249</v>
+        <v>46274</v>
       </c>
       <c r="I312" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J312" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>unit,tunic,induct,conduit,discount,seduction,reductions,destruction</t>
+          <t>am,mat,meat,tamed</t>
         </is>
       </c>
       <c r="L312">
@@ -13815,27 +13808,32 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>if</t>
+          <t>so</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>finger</t>
+          <t>rosary</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="D313" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>rookie</t>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G313" s="1" t="n">
-        <v>46250</v>
+        <v>46274</v>
       </c>
       <c r="I313" t="n">
         <v>2</v>
@@ -13845,7 +13843,7 @@
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>if,fin,fine,finer,finger</t>
+          <t>so,soy,rosy,sorry,rosary</t>
         </is>
       </c>
       <c r="L313">
@@ -13856,37 +13854,42 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>ors</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>casket</t>
+          <t>oranges</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="D314" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>rookie</t>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G314" s="1" t="n">
-        <v>46251</v>
+        <v>46274</v>
       </c>
       <c r="I314" t="n">
         <v>3</v>
       </c>
       <c r="J314" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>ask,sake,steak,casket</t>
+          <t>ors,oars,sonar,organs,oranges</t>
         </is>
       </c>
       <c r="L314">
@@ -13897,37 +13900,42 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>love</t>
+          <t>peen</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>volatile</t>
+          <t>penned</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="D315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>expert</t>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G315" s="1" t="n">
-        <v>46251</v>
+        <v>46275</v>
       </c>
       <c r="I315" t="n">
         <v>4</v>
       </c>
       <c r="J315" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>love,olive,violet,violate,volatile</t>
+          <t>peen,penne,penned</t>
         </is>
       </c>
       <c r="L315">
@@ -13938,37 +13946,42 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>duo</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>heard</t>
+          <t>abound</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="D316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>rookie</t>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G316" s="1" t="n">
-        <v>46252</v>
+        <v>46275</v>
       </c>
       <c r="I316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J316" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>ad,had,head,heard</t>
+          <t>duo,udon,bound,abound</t>
         </is>
       </c>
       <c r="L316">
@@ -13979,37 +13992,42 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>due</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>unbathed</t>
+          <t>originate</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="D317" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>novice</t>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G317" s="1" t="n">
-        <v>46252</v>
+        <v>46275</v>
       </c>
       <c r="I317" t="n">
         <v>3</v>
       </c>
       <c r="J317" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>due,dune,tuned,hunted,haunted,unbathed</t>
+          <t>tag,gnat,grant,rating,orating,rigatoni,originate</t>
         </is>
       </c>
       <c r="L317">
@@ -14020,27 +14038,32 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>at</t>
+          <t>pa</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>track</t>
+          <t>clamp</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="D318" t="n">
         <v>1</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>rookie</t>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G318" s="1" t="n">
-        <v>46253</v>
+        <v>46276</v>
       </c>
       <c r="I318" t="n">
         <v>2</v>
@@ -14050,7 +14073,7 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>at,cat,cart,track</t>
+          <t>pa,pal,lamp,clamp</t>
         </is>
       </c>
       <c r="L318">
@@ -14061,16 +14084,16 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>pea</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>garlics</t>
+          <t>pirates</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="D319" t="n">
         <v>2</v>
@@ -14080,18 +14103,23 @@
           <t>novice</t>
         </is>
       </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G319" s="1" t="n">
-        <v>46253</v>
+        <v>46276</v>
       </c>
       <c r="I319" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J319" t="n">
         <v>7</v>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>is,sir,airs,rails,grails,garlics</t>
+          <t>pea,pear,spare,praise,pirates</t>
         </is>
       </c>
       <c r="L319">
@@ -14102,16 +14130,16 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>me</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>terrain</t>
+          <t>heroism</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="D320" t="n">
         <v>3</v>
@@ -14121,18 +14149,23 @@
           <t>expert</t>
         </is>
       </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G320" s="1" t="n">
-        <v>46253</v>
+        <v>46276</v>
       </c>
       <c r="I320" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J320" t="n">
         <v>7</v>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>air,rain,train,retina,terrain</t>
+          <t>me,hem,home,homer,homier,heroism</t>
         </is>
       </c>
       <c r="L320">
@@ -14143,27 +14176,32 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>as</t>
+          <t>go</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>forge</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="D321" t="n">
         <v>1</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>rookie</t>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G321" s="1" t="n">
-        <v>46254</v>
+        <v>46277</v>
       </c>
       <c r="I321" t="n">
         <v>2</v>
@@ -14173,7 +14211,7 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>as,say,easy,years</t>
+          <t>go,fog,frog,forge</t>
         </is>
       </c>
       <c r="L321">
@@ -14184,16 +14222,16 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>dime</t>
+          <t>en</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>dummies</t>
+          <t>tinkle</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="D322" t="n">
         <v>2</v>
@@ -14203,18 +14241,23 @@
           <t>novice</t>
         </is>
       </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G322" s="1" t="n">
-        <v>46254</v>
+        <v>46277</v>
       </c>
       <c r="I322" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J322" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>dime,mimed,medium,dummies</t>
+          <t>en,ten,lent,inlet,tinkle</t>
         </is>
       </c>
       <c r="L322">
@@ -14225,16 +14268,16 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>rue</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>thrashed</t>
+          <t>flounder</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="D323" t="n">
         <v>3</v>
@@ -14244,18 +14287,23 @@
           <t>expert</t>
         </is>
       </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G323" s="1" t="n">
-        <v>46254</v>
+        <v>46277</v>
       </c>
       <c r="I323" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J323" t="n">
         <v>8</v>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>ad,had,hard,heard,shared,trashed,thrashed</t>
+          <t>rue,rude,under,refund,founder,flounder</t>
         </is>
       </c>
       <c r="L323">
@@ -14266,27 +14314,32 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>on</t>
+          <t>or</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>clone</t>
+          <t>boxer</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="D324" t="n">
         <v>1</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>rookie</t>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G324" s="1" t="n">
-        <v>46255</v>
+        <v>46278</v>
       </c>
       <c r="I324" t="n">
         <v>2</v>
@@ -14296,7 +14349,7 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>on,one,cone,clone</t>
+          <t>or,ore,robe,boxer</t>
         </is>
       </c>
       <c r="L324">
@@ -14307,16 +14360,16 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>cut</t>
+          <t>tad</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>curate</t>
+          <t>tadpole</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="D325" t="n">
         <v>2</v>
@@ -14326,18 +14379,23 @@
           <t>novice</t>
         </is>
       </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G325" s="1" t="n">
-        <v>46255</v>
+        <v>46278</v>
       </c>
       <c r="I325" t="n">
         <v>3</v>
       </c>
       <c r="J325" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>cut,cute,acute,curate</t>
+          <t>tad,date,dealt,plated,tadpole</t>
         </is>
       </c>
       <c r="L325">
@@ -14348,16 +14406,16 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>son</t>
+          <t>louden</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>jointers</t>
+          <t>convulsed</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="D326" t="n">
         <v>3</v>
@@ -14367,1223 +14425,28 @@
           <t>expert</t>
         </is>
       </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G326" s="1" t="n">
-        <v>46255</v>
+        <v>46278</v>
       </c>
       <c r="I326" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J326" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>son,nose,noise,nosier,rejoins,jointers</t>
+          <t>louden,unloved,unsolved,convulsed</t>
         </is>
       </c>
       <c r="L326">
         <f>IF(C326="","Excluded (no APD)",IF(C326&lt;1.25,"Easy",IF(C326&lt;=2.8,"Medium",IF(C326&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
         <v/>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>barked</t>
-        </is>
-      </c>
-      <c r="C327" t="n">
-        <v>1</v>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="K327" t="inlineStr">
-        <is>
-          <t>bar,bear,bread,barked</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>rot</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>smoother</t>
-        </is>
-      </c>
-      <c r="C328" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="K328" t="inlineStr">
-        <is>
-          <t>rot,sort,short,others,mothers,smoother</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>me</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>medication</t>
-        </is>
-      </c>
-      <c r="C329" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="K329" t="inlineStr">
-        <is>
-          <t>me,men,mine,anime,median,mediant,dominate,mediation,medication</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>at</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>thank</t>
-        </is>
-      </c>
-      <c r="C330" t="n">
-        <v>1</v>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="K330" t="inlineStr">
-        <is>
-          <t>at,tan,tank,thank</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>sate</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>masteries</t>
-        </is>
-      </c>
-      <c r="C331" t="n">
-        <v>2</v>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="K331" t="inlineStr">
-        <is>
-          <t>sate,stare,stream,steamer,steamers,masteries</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>lee</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>reclaimed</t>
-        </is>
-      </c>
-      <c r="C332" t="n">
-        <v>3</v>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="K332" t="inlineStr">
-        <is>
-          <t>lee,leer,elder,dealer,emerald,remedial,reclaimed</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>widen</t>
-        </is>
-      </c>
-      <c r="C333" t="n">
-        <v>1</v>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="K333" t="inlineStr">
-        <is>
-          <t>in,win,wind,widen</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>ear</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>lateral</t>
-        </is>
-      </c>
-      <c r="C334" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="K334" t="inlineStr">
-        <is>
-          <t>ear,real,alter,taller,lateral</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>flustering</t>
-        </is>
-      </c>
-      <c r="C335" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="K335" t="inlineStr">
-        <is>
-          <t>is,sin,sing,sting,string,rusting,rustling,resulting,flustering</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>he</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>heart</t>
-        </is>
-      </c>
-      <c r="C336" t="n">
-        <v>1</v>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="K336" t="inlineStr">
-        <is>
-          <t>he,the,heat,heart</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>as</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>sneaky</t>
-        </is>
-      </c>
-      <c r="C337" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="K337" t="inlineStr">
-        <is>
-          <t>as,sea,sake,snake,sneaky</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>ma</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>inflame</t>
-        </is>
-      </c>
-      <c r="C338" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="K338" t="inlineStr">
-        <is>
-          <t>ma,man,main,anime,famine,inflame</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>by</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>bossy</t>
-        </is>
-      </c>
-      <c r="C339" t="n">
-        <v>1</v>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="K339" t="inlineStr">
-        <is>
-          <t>by,boy,boys,bossy</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>lid</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>bridle</t>
-        </is>
-      </c>
-      <c r="C340" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="K340" t="inlineStr">
-        <is>
-          <t>lid,deli,riled,bridle</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>unctions</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
-      <c r="C341" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="K341" t="inlineStr">
-        <is>
-          <t>unctions,contusion,continuous</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>fin</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>friend</t>
-        </is>
-      </c>
-      <c r="C342" t="n">
-        <v>1</v>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="K342" t="inlineStr">
-        <is>
-          <t>fin,find,fined,friend</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>collage</t>
-        </is>
-      </c>
-      <c r="C343" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t>all,call,local,locale,collage</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>an</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>bargeman</t>
-        </is>
-      </c>
-      <c r="C344" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="K344" t="inlineStr">
-        <is>
-          <t>an,ran,rang,anger,manger,manager,bargeman</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>ski</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>sticky</t>
-        </is>
-      </c>
-      <c r="C345" t="n">
-        <v>1</v>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K345" t="inlineStr">
-        <is>
-          <t>ski,sick,stick,sticky</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>wine</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>swindler</t>
-        </is>
-      </c>
-      <c r="C346" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K346" t="inlineStr">
-        <is>
-          <t>wine,swine,widens,rewinds,swindler</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>rise</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>compilers</t>
-        </is>
-      </c>
-      <c r="C347" t="n">
-        <v>3</v>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K347" t="inlineStr">
-        <is>
-          <t>rise,pries,primes,promise,implores,compilers</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>rid</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>driven</t>
-        </is>
-      </c>
-      <c r="C348" t="n">
-        <v>1</v>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="K348" t="inlineStr">
-        <is>
-          <t>rid,ride,diver,driven</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>bristle</t>
-        </is>
-      </c>
-      <c r="C349" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="K349" t="inlineStr">
-        <is>
-          <t>best,bites,tribes,bristle</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>wig</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>withering</t>
-        </is>
-      </c>
-      <c r="C350" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="K350" t="inlineStr">
-        <is>
-          <t>wig,wing,wring,wiring,writing,writhing,withering</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>of</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>floor</t>
-        </is>
-      </c>
-      <c r="C351" t="n">
-        <v>1</v>
-      </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="K351" t="inlineStr">
-        <is>
-          <t>of,for,roof,floor</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>oat</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>flotsam</t>
-        </is>
-      </c>
-      <c r="C352" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="K352" t="inlineStr">
-        <is>
-          <t>oat,atom,moats,almost,flotsam</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>tire</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>ministries</t>
-        </is>
-      </c>
-      <c r="C353" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="K353" t="inlineStr">
-        <is>
-          <t>tire,inter,tinier,mintier,minister,ministers,ministries</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>crown</t>
-        </is>
-      </c>
-      <c r="C354" t="n">
-        <v>1</v>
-      </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="K354" t="inlineStr">
-        <is>
-          <t>on,now,worn,crown</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>me</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>monkey</t>
-        </is>
-      </c>
-      <c r="C355" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="K355" t="inlineStr">
-        <is>
-          <t>me,men,omen,money,monkey</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>girl</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>ridgeline</t>
-        </is>
-      </c>
-      <c r="C356" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="K356" t="inlineStr">
-        <is>
-          <t>girl,liger,linger,reeling,lingered,ridgeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>go</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>lodge</t>
-        </is>
-      </c>
-      <c r="C357" t="n">
-        <v>1</v>
-      </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="K357" t="inlineStr">
-        <is>
-          <t>go,dog,gold,lodge</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>ye</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>pretty</t>
-        </is>
-      </c>
-      <c r="C358" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="K358" t="inlineStr">
-        <is>
-          <t>ye,yet,type,petty,pretty</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>traveling</t>
-        </is>
-      </c>
-      <c r="C359" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="K359" t="inlineStr">
-        <is>
-          <t>age,gear,anger,regain,tangier,averting,traveling</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>blink</t>
-        </is>
-      </c>
-      <c r="C360" t="n">
-        <v>1</v>
-      </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="K360" t="inlineStr">
-        <is>
-          <t>in,ink,link,blink</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>per</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>scooper</t>
-        </is>
-      </c>
-      <c r="C361" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="K361" t="inlineStr">
-        <is>
-          <t>per,rope,spore,corpse,scooper</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>air</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>pyramid</t>
-        </is>
-      </c>
-      <c r="C362" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="K362" t="inlineStr">
-        <is>
-          <t>air,raid,dairy,myriad,pyramid</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>by</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>tabby</t>
-        </is>
-      </c>
-      <c r="C363" t="n">
-        <v>1</v>
-      </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="K363" t="inlineStr">
-        <is>
-          <t>by,bay,baby,tabby</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>lie</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>literary</t>
-        </is>
-      </c>
-      <c r="C364" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="K364" t="inlineStr">
-        <is>
-          <t>lie,rile,relit,retail,trailer,literary</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>ruminates</t>
-        </is>
-      </c>
-      <c r="C365" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="K365" t="inlineStr">
-        <is>
-          <t>sun,stun,tunes,tuners,saunter,urinates,ruminates</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>at</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>chant</t>
-        </is>
-      </c>
-      <c r="C366" t="n">
-        <v>1</v>
-      </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="K366" t="inlineStr">
-        <is>
-          <t>at,cat,chat,chant</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>renown</t>
-        </is>
-      </c>
-      <c r="C367" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="K367" t="inlineStr">
-        <is>
-          <t>new,wren,owner,renown</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>rant</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>decorating</t>
-        </is>
-      </c>
-      <c r="C368" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="K368" t="inlineStr">
-        <is>
-          <t>rant,train,rating,ingrate,treading,redacting,decorating</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>an</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-      <c r="C369" t="n">
-        <v>1</v>
-      </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="K369" t="inlineStr">
-        <is>
-          <t>an,ban,bank,blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>maul</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>lumbar</t>
-        </is>
-      </c>
-      <c r="C370" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="K370" t="inlineStr">
-        <is>
-          <t>maul,album,lumbar</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>tag</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>nostalgic</t>
-        </is>
-      </c>
-      <c r="C371" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G371" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="K371" t="inlineStr">
-        <is>
-          <t>tag,gait,giant,acting,casting,coasting,nostalgic</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>fishy</t>
-        </is>
-      </c>
-      <c r="C372" t="n">
-        <v>1</v>
-      </c>
-      <c r="G372" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="K372" t="inlineStr">
-        <is>
-          <t>is,his,fish,fishy</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>mans</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>normals</t>
-        </is>
-      </c>
-      <c r="C373" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G373" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="K373" t="inlineStr">
-        <is>
-          <t>mans,moans,salmon,normals</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>sane</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>readiness</t>
-        </is>
-      </c>
-      <c r="C374" t="n">
-        <v>3</v>
-      </c>
-      <c r="G374" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="K374" t="inlineStr">
-        <is>
-          <t>sane,nears,snared,sandier,sardines,readiness</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/scripts/puzzle_bank.xlsx
+++ b/scripts/puzzle_bank.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L326"/>
+  <dimension ref="A1:L338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13624,12 +13624,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>at</t>
+          <t>ow</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>cower</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>at,tar,tear,water</t>
+          <t>ow,cow,crow,cower</t>
         </is>
       </c>
       <c r="L309">
@@ -13670,12 +13670,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ale</t>
+          <t>he</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>clapped</t>
+          <t>hoarse</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -13698,14 +13698,14 @@
         <v>46273</v>
       </c>
       <c r="I310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J310" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>ale,pale,apple,lapped,clapped</t>
+          <t>he,she,shoe,horse,hoarse</t>
         </is>
       </c>
       <c r="L310">
@@ -14446,6 +14446,558 @@
       </c>
       <c r="L326">
         <f>IF(C326="","Excluded (no APD)",IF(C326&lt;1.25,"Easy",IF(C326&lt;=2.8,"Medium",IF(C326&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D327" t="n">
+        <v>1</v>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G327" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="I327" t="n">
+        <v>2</v>
+      </c>
+      <c r="J327" t="n">
+        <v>5</v>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>at,tar,tear,water</t>
+        </is>
+      </c>
+      <c r="L327">
+        <f>IF(C327="","Excluded (no APD)",IF(C327&lt;1.25,"Easy",IF(C327&lt;=2.8,"Medium",IF(C327&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>ale</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>clapped</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D328" t="n">
+        <v>2</v>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G328" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="I328" t="n">
+        <v>3</v>
+      </c>
+      <c r="J328" t="n">
+        <v>7</v>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>ale,pale,apple,lapped,clapped</t>
+        </is>
+      </c>
+      <c r="L328">
+        <f>IF(C328="","Excluded (no APD)",IF(C328&lt;1.25,"Easy",IF(C328&lt;=2.8,"Medium",IF(C328&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>louden</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>convulsed</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D329" t="n">
+        <v>3</v>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G329" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="I329" t="n">
+        <v>6</v>
+      </c>
+      <c r="J329" t="n">
+        <v>9</v>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>louden,unloved,unsolved,convulsed</t>
+        </is>
+      </c>
+      <c r="L329">
+        <f>IF(C329="","Excluded (no APD)",IF(C329&lt;1.25,"Easy",IF(C329&lt;=2.8,"Medium",IF(C329&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>dread</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D330" t="n">
+        <v>1</v>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G330" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="I330" t="n">
+        <v>2</v>
+      </c>
+      <c r="J330" t="n">
+        <v>5</v>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>ad,add,dead,dread</t>
+        </is>
+      </c>
+      <c r="L330">
+        <f>IF(C330="","Excluded (no APD)",IF(C330&lt;1.25,"Easy",IF(C330&lt;=2.8,"Medium",IF(C330&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>plumes</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D331" t="n">
+        <v>2</v>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G331" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="I331" t="n">
+        <v>2</v>
+      </c>
+      <c r="J331" t="n">
+        <v>6</v>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>us,pus,plus,pulse,plumes</t>
+        </is>
+      </c>
+      <c r="L331">
+        <f>IF(C331="","Excluded (no APD)",IF(C331&lt;1.25,"Easy",IF(C331&lt;=2.8,"Medium",IF(C331&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>supreme</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D332" t="n">
+        <v>3</v>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G332" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="I332" t="n">
+        <v>2</v>
+      </c>
+      <c r="J332" t="n">
+        <v>7</v>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>us,sum,muse,serum,resume,supreme</t>
+        </is>
+      </c>
+      <c r="L332">
+        <f>IF(C332="","Excluded (no APD)",IF(C332&lt;1.25,"Easy",IF(C332&lt;=2.8,"Medium",IF(C332&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>spine</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D333" t="n">
+        <v>1</v>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G333" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="I333" t="n">
+        <v>2</v>
+      </c>
+      <c r="J333" t="n">
+        <v>5</v>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>is,sin,snip,spine</t>
+        </is>
+      </c>
+      <c r="L333">
+        <f>IF(C333="","Excluded (no APD)",IF(C333&lt;1.25,"Easy",IF(C333&lt;=2.8,"Medium",IF(C333&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>stride</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D334" t="n">
+        <v>2</v>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G334" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="I334" t="n">
+        <v>2</v>
+      </c>
+      <c r="J334" t="n">
+        <v>6</v>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>is,sir,sire,rides,stride</t>
+        </is>
+      </c>
+      <c r="L334">
+        <f>IF(C334="","Excluded (no APD)",IF(C334&lt;1.25,"Easy",IF(C334&lt;=2.8,"Medium",IF(C334&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>is</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>perusing</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D335" t="n">
+        <v>3</v>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G335" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="I335" t="n">
+        <v>2</v>
+      </c>
+      <c r="J335" t="n">
+        <v>8</v>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>is,sin,sing,using,genius,reusing,perusing</t>
+        </is>
+      </c>
+      <c r="L335">
+        <f>IF(C335="","Excluded (no APD)",IF(C335&lt;1.25,"Easy",IF(C335&lt;=2.8,"Medium",IF(C335&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>boast</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D336" t="n">
+        <v>1</v>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>beginner</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G336" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="I336" t="n">
+        <v>2</v>
+      </c>
+      <c r="J336" t="n">
+        <v>5</v>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>to,bot,boat,boast</t>
+        </is>
+      </c>
+      <c r="L336">
+        <f>IF(C336="","Excluded (no APD)",IF(C336&lt;1.25,"Easy",IF(C336&lt;=2.8,"Medium",IF(C336&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>so</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>drowns</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D337" t="n">
+        <v>2</v>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>novice</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G337" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="I337" t="n">
+        <v>2</v>
+      </c>
+      <c r="J337" t="n">
+        <v>6</v>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>so,sow,rows,sword,drowns</t>
+        </is>
+      </c>
+      <c r="L337">
+        <f>IF(C337="","Excluded (no APD)",IF(C337&lt;1.25,"Easy",IF(C337&lt;=2.8,"Medium",IF(C337&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>anti</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>fornicate</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D338" t="n">
+        <v>3</v>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>expert</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G338" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="I338" t="n">
+        <v>4</v>
+      </c>
+      <c r="J338" t="n">
+        <v>9</v>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>anti,antic,action,faction,fraction,fornicate</t>
+        </is>
+      </c>
+      <c r="L338">
+        <f>IF(C338="","Excluded (no APD)",IF(C338&lt;1.25,"Easy",IF(C338&lt;=2.8,"Medium",IF(C338&lt;=5,"Hard","Excluded (APD&gt;5)"))))</f>
         <v/>
       </c>
     </row>
